--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -14793,43 +14793,43 @@
       <c r="A316" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="B316" t="n">
+      <c r="B316" s="0" t="n">
         <v>-39</v>
       </c>
-      <c r="C316" t="n">
+      <c r="C316" s="0" t="n">
         <v>-39.9</v>
       </c>
-      <c r="D316" t="n">
+      <c r="D316" s="0" t="n">
         <v>-39.2</v>
       </c>
-      <c r="E316" t="n">
+      <c r="E316" s="0" t="n">
         <v>-34.7</v>
       </c>
-      <c r="F316" t="n">
+      <c r="F316" s="0" t="n">
         <v>-35.5</v>
       </c>
-      <c r="G316" t="n">
+      <c r="G316" s="0" t="n">
         <v>-30.7</v>
       </c>
-      <c r="H316" t="n">
+      <c r="H316" s="0" t="n">
         <v>-27</v>
       </c>
-      <c r="I316" t="n">
+      <c r="I316" s="0" t="n">
         <v>-32.4</v>
       </c>
-      <c r="J316" t="n">
+      <c r="J316" s="0" t="n">
         <v>-41.3</v>
       </c>
-      <c r="K316" t="n">
+      <c r="K316" s="0" t="n">
         <v>-40.7</v>
       </c>
-      <c r="L316" t="n">
+      <c r="L316" s="0" t="n">
         <v>-37.3</v>
       </c>
-      <c r="M316" t="n">
+      <c r="M316" s="0" t="n">
         <v>-27.7</v>
       </c>
-      <c r="N316" t="n">
+      <c r="N316" s="0" t="n">
         <v>-21.6</v>
       </c>
     </row>
@@ -14837,30 +14837,264 @@
       <c r="A317" s="1" t="n">
         <v>46076</v>
       </c>
+      <c r="B317" s="0" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="C317" s="0" t="n">
+        <v>-37.2</v>
+      </c>
+      <c r="D317" s="0" t="n">
+        <v>-38</v>
+      </c>
+      <c r="E317" s="0" t="n">
+        <v>-30.4</v>
+      </c>
+      <c r="F317" s="0" t="n">
+        <v>-33.7</v>
+      </c>
+      <c r="G317" s="0" t="n">
+        <v>-35.7</v>
+      </c>
+      <c r="H317" s="0" t="n">
+        <v>-36.2</v>
+      </c>
+      <c r="I317" s="0" t="n">
+        <v>-33</v>
+      </c>
+      <c r="J317" s="0" t="n">
+        <v>-31.9</v>
+      </c>
+      <c r="K317" s="0" t="n">
+        <v>-34</v>
+      </c>
+      <c r="L317" s="0" t="n">
+        <v>-31.9</v>
+      </c>
+      <c r="M317" s="0" t="n">
+        <v>-37.6</v>
+      </c>
+      <c r="N317" s="0" t="n">
+        <v>-26</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
         <v>46077</v>
       </c>
+      <c r="B318" s="0" t="n">
+        <v>-33.8</v>
+      </c>
+      <c r="C318" s="0" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="D318" s="0" t="n">
+        <v>-33.4</v>
+      </c>
+      <c r="E318" s="0" t="n">
+        <v>-23.8</v>
+      </c>
+      <c r="F318" s="0" t="n">
+        <v>-28</v>
+      </c>
+      <c r="G318" s="0" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="H318" s="0" t="n">
+        <v>-33.3</v>
+      </c>
+      <c r="I318" s="0" t="n">
+        <v>-30.4</v>
+      </c>
+      <c r="J318" s="0" t="n">
+        <v>-28.6</v>
+      </c>
+      <c r="K318" s="0" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="L318" s="0" t="n">
+        <v>-26</v>
+      </c>
+      <c r="M318" s="0" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="N318" s="0" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
         <v>46078</v>
       </c>
+      <c r="B319" s="0" t="n">
+        <v>-36.5</v>
+      </c>
+      <c r="C319" s="0" t="n">
+        <v>-37.6</v>
+      </c>
+      <c r="D319" s="0" t="n">
+        <v>-36.3</v>
+      </c>
+      <c r="E319" s="0" t="n">
+        <v>-30.9</v>
+      </c>
+      <c r="F319" s="0" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="G319" s="0" t="n">
+        <v>-21.5</v>
+      </c>
+      <c r="H319" s="0" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="I319" s="0" t="n">
+        <v>-31.8</v>
+      </c>
+      <c r="J319" s="0" t="n">
+        <v>-34.2</v>
+      </c>
+      <c r="K319" s="0" t="n">
+        <v>-36</v>
+      </c>
+      <c r="L319" s="0" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="M319" s="0" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="N319" s="0" t="n">
+        <v>-21.3</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
         <v>46079</v>
       </c>
+      <c r="B320" s="0" t="n">
+        <v>-38.8</v>
+      </c>
+      <c r="C320" s="0" t="n">
+        <v>-41.5</v>
+      </c>
+      <c r="D320" s="0" t="n">
+        <v>-40.4</v>
+      </c>
+      <c r="E320" s="0" t="n">
+        <v>-33.4</v>
+      </c>
+      <c r="F320" s="0" t="n">
+        <v>-38</v>
+      </c>
+      <c r="G320" s="0" t="n">
+        <v>-33</v>
+      </c>
+      <c r="H320" s="0" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I320" s="0" t="n">
+        <v>-36.9</v>
+      </c>
+      <c r="J320" s="0" t="n">
+        <v>-37.5</v>
+      </c>
+      <c r="K320" s="0" t="n">
+        <v>-37.8</v>
+      </c>
+      <c r="L320" s="0" t="n">
+        <v>-34.4</v>
+      </c>
+      <c r="M320" s="0" t="n">
+        <v>-36.6</v>
+      </c>
+      <c r="N320" s="0" t="n">
+        <v>-24.5</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
         <v>46080</v>
       </c>
+      <c r="B321" s="0" t="n">
+        <v>-41</v>
+      </c>
+      <c r="C321" s="0" t="n">
+        <v>-41.7</v>
+      </c>
+      <c r="D321" s="0" t="n">
+        <v>-40.4</v>
+      </c>
+      <c r="E321" s="0" t="n">
+        <v>-36.7</v>
+      </c>
+      <c r="F321" s="0" t="n">
+        <v>-34.1</v>
+      </c>
+      <c r="G321" s="0" t="n">
+        <v>-36.4</v>
+      </c>
+      <c r="H321" s="0" t="n">
+        <v>-34.8</v>
+      </c>
+      <c r="I321" s="0" t="n">
+        <v>-37.8</v>
+      </c>
+      <c r="J321" s="0" t="n">
+        <v>-37.7</v>
+      </c>
+      <c r="K321" s="0" t="n">
+        <v>-37.3</v>
+      </c>
+      <c r="L321" s="0" t="n">
+        <v>-37.4</v>
+      </c>
+      <c r="M321" s="0" t="n">
+        <v>-39.5</v>
+      </c>
+      <c r="N321" s="0" t="n">
+        <v>-24</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
         <v>46081</v>
+      </c>
+      <c r="B322" t="n">
+        <v>-40.1</v>
+      </c>
+      <c r="C322" t="n">
+        <v>-37.4</v>
+      </c>
+      <c r="D322" t="n">
+        <v>-38.3</v>
+      </c>
+      <c r="E322" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="F322" t="n">
+        <v>-33</v>
+      </c>
+      <c r="G322" t="n">
+        <v>-32.4</v>
+      </c>
+      <c r="H322" t="n">
+        <v>-30.7</v>
+      </c>
+      <c r="I322" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="J322" t="n">
+        <v>-30.9</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="L322" t="n">
+        <v>-32.2</v>
+      </c>
+      <c r="M322" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="N322" t="n">
+        <v>-20.5</v>
       </c>
     </row>
     <row r="323">
@@ -29309,43 +29543,43 @@
       <c r="A316" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="B316" t="n">
+      <c r="B316" s="0" t="n">
         <v>-22.9</v>
       </c>
-      <c r="C316" t="n">
+      <c r="C316" s="0" t="n">
         <v>-20.2</v>
       </c>
-      <c r="D316" t="n">
+      <c r="D316" s="0" t="n">
         <v>-22.1</v>
       </c>
-      <c r="E316" t="n">
+      <c r="E316" s="0" t="n">
         <v>-20</v>
       </c>
-      <c r="F316" t="n">
+      <c r="F316" s="0" t="n">
         <v>-19.3</v>
       </c>
-      <c r="G316" t="n">
+      <c r="G316" s="0" t="n">
         <v>-20.5</v>
       </c>
-      <c r="H316" t="n">
+      <c r="H316" s="0" t="n">
         <v>-11.2</v>
       </c>
-      <c r="I316" t="n">
+      <c r="I316" s="0" t="n">
         <v>-14.4</v>
       </c>
-      <c r="J316" t="n">
+      <c r="J316" s="0" t="n">
         <v>-20.7</v>
       </c>
-      <c r="K316" t="n">
+      <c r="K316" s="0" t="n">
         <v>-17.5</v>
       </c>
-      <c r="L316" t="n">
+      <c r="L316" s="0" t="n">
         <v>-18.6</v>
       </c>
-      <c r="M316" t="n">
+      <c r="M316" s="0" t="n">
         <v>-20.4</v>
       </c>
-      <c r="N316" t="n">
+      <c r="N316" s="0" t="n">
         <v>-16.2</v>
       </c>
     </row>
@@ -29353,30 +29587,264 @@
       <c r="A317" s="1" t="n">
         <v>46076</v>
       </c>
+      <c r="B317" s="0" t="n">
+        <v>-22.5</v>
+      </c>
+      <c r="C317" s="0" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="D317" s="0" t="n">
+        <v>-17</v>
+      </c>
+      <c r="E317" s="0" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="F317" s="0" t="n">
+        <v>-17.9</v>
+      </c>
+      <c r="G317" s="0" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H317" s="0" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="I317" s="0" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="J317" s="0" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="K317" s="0" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="L317" s="0" t="n">
+        <v>-15.6</v>
+      </c>
+      <c r="M317" s="0" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="N317" s="0" t="n">
+        <v>-12.3</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
         <v>46077</v>
       </c>
+      <c r="B318" s="0" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="C318" s="0" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="D318" s="0" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="E318" s="0" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="F318" s="0" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="G318" s="0" t="n">
+        <v>-12.9</v>
+      </c>
+      <c r="H318" s="0" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="I318" s="0" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="J318" s="0" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="K318" s="0" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L318" s="0" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="M318" s="0" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="N318" s="0" t="n">
+        <v>-6.7</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
         <v>46078</v>
       </c>
+      <c r="B319" s="0" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="C319" s="0" t="n">
+        <v>-21.2</v>
+      </c>
+      <c r="D319" s="0" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="E319" s="0" t="n">
+        <v>-17.2</v>
+      </c>
+      <c r="F319" s="0" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="G319" s="0" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H319" s="0" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="I319" s="0" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="J319" s="0" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="K319" s="0" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L319" s="0" t="n">
+        <v>-16.3</v>
+      </c>
+      <c r="M319" s="0" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="N319" s="0" t="n">
+        <v>-8.5</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
         <v>46079</v>
       </c>
+      <c r="B320" s="0" t="n">
+        <v>-26.7</v>
+      </c>
+      <c r="C320" s="0" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="D320" s="0" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="E320" s="0" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="F320" s="0" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="G320" s="0" t="n">
+        <v>-21.8</v>
+      </c>
+      <c r="H320" s="0" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="I320" s="0" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="J320" s="0" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="K320" s="0" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="L320" s="0" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="M320" s="0" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="N320" s="0" t="n">
+        <v>-13.3</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
         <v>46080</v>
       </c>
+      <c r="B321" s="0" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="C321" s="0" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="D321" s="0" t="n">
+        <v>-24</v>
+      </c>
+      <c r="E321" s="0" t="n">
+        <v>-21.1</v>
+      </c>
+      <c r="F321" s="0" t="n">
+        <v>-19.8</v>
+      </c>
+      <c r="G321" s="0" t="n">
+        <v>-22.3</v>
+      </c>
+      <c r="H321" s="0" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="I321" s="0" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="J321" s="0" t="n">
+        <v>-19.7</v>
+      </c>
+      <c r="K321" s="0" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="L321" s="0" t="n">
+        <v>-19.9</v>
+      </c>
+      <c r="M321" s="0" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="N321" s="0" t="n">
+        <v>-11.4</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
         <v>46081</v>
+      </c>
+      <c r="B322" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="C322" t="n">
+        <v>-24.4</v>
+      </c>
+      <c r="D322" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="E322" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="F322" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="G322" t="n">
+        <v>-18.7</v>
+      </c>
+      <c r="H322" t="n">
+        <v>-15.2</v>
+      </c>
+      <c r="I322" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="J322" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="K322" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L322" t="n">
+        <v>-15</v>
+      </c>
+      <c r="M322" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="N322" t="n">
+        <v>-7.9</v>
       </c>
     </row>
     <row r="323">
@@ -33493,53 +33961,53 @@
       <c r="A74" s="1" t="n">
         <v>46075</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="0" t="n">
         <v>-31.98</v>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F74" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H74" s="0" t="n">
         <v>-20.6</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74" s="0" t="n">
         <v>-24.81</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74" s="0" t="n">
         <v>-31.07</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K74" s="0" t="n">
         <v>-28.37</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74" s="0" t="n">
         <v>-30.52</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M74" s="0" t="n">
         <v>-24.36</v>
       </c>
-      <c r="N74" t="n">
+      <c r="N74" s="0" t="n">
         <v>-19.35</v>
       </c>
     </row>
@@ -33547,30 +34015,324 @@
       <c r="A75" s="1" t="n">
         <v>46076</v>
       </c>
+      <c r="B75" s="0" t="n">
+        <v>-26.66</v>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D75" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F75" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G75" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H75" s="0" t="n">
+        <v>-28.03</v>
+      </c>
+      <c r="I75" s="0" t="n">
+        <v>-26.45</v>
+      </c>
+      <c r="J75" s="0" t="n">
+        <v>-26.05</v>
+      </c>
+      <c r="K75" s="0" t="n">
+        <v>-21.16</v>
+      </c>
+      <c r="L75" s="0" t="n">
+        <v>-25.3</v>
+      </c>
+      <c r="M75" s="0" t="n">
+        <v>-31.29</v>
+      </c>
+      <c r="N75" s="0" t="n">
+        <v>-20.55</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
         <v>46077</v>
       </c>
+      <c r="B76" s="0" t="n">
+        <v>-26.05</v>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D76" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F76" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G76" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H76" s="0" t="n">
+        <v>-25.39</v>
+      </c>
+      <c r="I76" s="0" t="n">
+        <v>-23.77</v>
+      </c>
+      <c r="J76" s="0" t="n">
+        <v>-20.85</v>
+      </c>
+      <c r="K76" s="0" t="n">
+        <v>-11.23</v>
+      </c>
+      <c r="L76" s="0" t="n">
+        <v>-18.14</v>
+      </c>
+      <c r="M76" s="0" t="n">
+        <v>-24.26</v>
+      </c>
+      <c r="N76" s="0" t="n">
+        <v>-14.82</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
         <v>46078</v>
       </c>
+      <c r="B77" s="0" t="n">
+        <v>-29.19</v>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F77" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H77" s="0" t="n">
+        <v>-18.04</v>
+      </c>
+      <c r="I77" s="0" t="n">
+        <v>-25.25</v>
+      </c>
+      <c r="J77" s="0" t="n">
+        <v>-26.35</v>
+      </c>
+      <c r="K77" s="0" t="n">
+        <v>-26.95</v>
+      </c>
+      <c r="L77" s="0" t="n">
+        <v>-24.96</v>
+      </c>
+      <c r="M77" s="0" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="N77" s="0" t="n">
+        <v>-17.69</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
         <v>46079</v>
       </c>
+      <c r="B78" s="0" t="n">
+        <v>-32.67</v>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H78" s="0" t="n">
+        <v>-25.31</v>
+      </c>
+      <c r="I78" s="0" t="n">
+        <v>-29.01</v>
+      </c>
+      <c r="J78" s="0" t="n">
+        <v>-29.09</v>
+      </c>
+      <c r="K78" s="0" t="n">
+        <v>-29.18</v>
+      </c>
+      <c r="L78" s="0" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="M78" s="0" t="n">
+        <v>-29.79</v>
+      </c>
+      <c r="N78" s="0" t="n">
+        <v>-19.76</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
         <v>46080</v>
       </c>
+      <c r="B79" s="0" t="n">
+        <v>-34.77</v>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F79" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G79" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H79" s="0" t="n">
+        <v>-26.73</v>
+      </c>
+      <c r="I79" s="0" t="n">
+        <v>-30.01</v>
+      </c>
+      <c r="J79" s="0" t="n">
+        <v>-30.98</v>
+      </c>
+      <c r="K79" s="0" t="n">
+        <v>-29.01</v>
+      </c>
+      <c r="L79" s="0" t="n">
+        <v>-30.19</v>
+      </c>
+      <c r="M79" s="0" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="N79" s="0" t="n">
+        <v>-18.55</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
         <v>46081</v>
+      </c>
+      <c r="B80" t="n">
+        <v>-31.19</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-28.34</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-27</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-24.35</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-24.91</v>
+      </c>
+      <c r="M80" t="n">
+        <v>-28.31</v>
+      </c>
+      <c r="N80" t="n">
+        <v>-15.07</v>
       </c>
     </row>
     <row r="81">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -15239,45 +15239,45 @@
       <c r="A326" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="B326" t="n">
+      <c r="B326" s="0" t="n">
         <v>-33.8</v>
       </c>
-      <c r="C326" t="n">
+      <c r="C326" s="0" t="n">
         <v>-35.8</v>
       </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E326" t="n">
+      <c r="D326" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E326" s="0" t="n">
         <v>-26.2</v>
       </c>
-      <c r="F326" t="n">
+      <c r="F326" s="0" t="n">
         <v>-26.7</v>
       </c>
-      <c r="G326" t="n">
+      <c r="G326" s="0" t="n">
         <v>-30.4</v>
       </c>
-      <c r="H326" t="n">
+      <c r="H326" s="0" t="n">
         <v>-34.3</v>
       </c>
-      <c r="I326" t="n">
+      <c r="I326" s="0" t="n">
         <v>-33.7</v>
       </c>
-      <c r="J326" t="n">
+      <c r="J326" s="0" t="n">
         <v>-27</v>
       </c>
-      <c r="K326" t="n">
+      <c r="K326" s="0" t="n">
         <v>-28.6</v>
       </c>
-      <c r="L326" t="n">
+      <c r="L326" s="0" t="n">
         <v>-28.8</v>
       </c>
-      <c r="M326" t="n">
+      <c r="M326" s="0" t="n">
         <v>-34.2</v>
       </c>
-      <c r="N326" t="n">
+      <c r="N326" s="0" t="n">
         <v>-21.3</v>
       </c>
     </row>
@@ -15285,15 +15285,138 @@
       <c r="A327" s="1" t="n">
         <v>46086</v>
       </c>
+      <c r="B327" s="0" t="n">
+        <v>-35.2</v>
+      </c>
+      <c r="C327" s="0" t="n">
+        <v>-36.7</v>
+      </c>
+      <c r="D327" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E327" s="0" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F327" s="0" t="n">
+        <v>-34.1</v>
+      </c>
+      <c r="G327" s="0" t="n">
+        <v>-31.6</v>
+      </c>
+      <c r="H327" s="0" t="n">
+        <v>-34.3</v>
+      </c>
+      <c r="I327" s="0" t="n">
+        <v>-31</v>
+      </c>
+      <c r="J327" s="0" t="n">
+        <v>-32.4</v>
+      </c>
+      <c r="K327" s="0" t="n">
+        <v>-32.2</v>
+      </c>
+      <c r="L327" s="0" t="n">
+        <v>-31.2</v>
+      </c>
+      <c r="M327" s="0" t="n">
+        <v>-33.4</v>
+      </c>
+      <c r="N327" s="0" t="n">
+        <v>-21.7</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
         <v>46087</v>
       </c>
+      <c r="B328" s="0" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="C328" s="0" t="n">
+        <v>-31.8</v>
+      </c>
+      <c r="D328" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E328" s="0" t="n">
+        <v>-26.7</v>
+      </c>
+      <c r="F328" s="0" t="n">
+        <v>-30.1</v>
+      </c>
+      <c r="G328" s="0" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="H328" s="0" t="n">
+        <v>-30.3</v>
+      </c>
+      <c r="I328" s="0" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="J328" s="0" t="n">
+        <v>-26</v>
+      </c>
+      <c r="K328" s="0" t="n">
+        <v>-25</v>
+      </c>
+      <c r="L328" s="0" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="M328" s="0" t="n">
+        <v>-27.3</v>
+      </c>
+      <c r="N328" s="0" t="n">
+        <v>-17.6</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
         <v>46088</v>
+      </c>
+      <c r="B329" t="n">
+        <v>-31</v>
+      </c>
+      <c r="C329" t="n">
+        <v>-33.4</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>-24.8</v>
+      </c>
+      <c r="F329" t="n">
+        <v>-28.5</v>
+      </c>
+      <c r="G329" t="n">
+        <v>-24.2</v>
+      </c>
+      <c r="H329" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="I329" t="n">
+        <v>-30</v>
+      </c>
+      <c r="J329" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="K329" t="n">
+        <v>-27</v>
+      </c>
+      <c r="L329" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="M329" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="N329" t="n">
+        <v>-12.7</v>
       </c>
     </row>
     <row r="330">
@@ -30153,45 +30276,45 @@
       <c r="A326" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="B326" t="n">
+      <c r="B326" s="0" t="n">
         <v>-21.4</v>
       </c>
-      <c r="C326" t="n">
+      <c r="C326" s="0" t="n">
         <v>-19.8</v>
       </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E326" t="n">
+      <c r="D326" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E326" s="0" t="n">
         <v>-12</v>
       </c>
-      <c r="F326" t="n">
+      <c r="F326" s="0" t="n">
         <v>-11.2</v>
       </c>
-      <c r="G326" t="n">
+      <c r="G326" s="0" t="n">
         <v>-16.4</v>
       </c>
-      <c r="H326" t="n">
+      <c r="H326" s="0" t="n">
         <v>-16.2</v>
       </c>
-      <c r="I326" t="n">
+      <c r="I326" s="0" t="n">
         <v>-18.2</v>
       </c>
-      <c r="J326" t="n">
+      <c r="J326" s="0" t="n">
         <v>-15.3</v>
       </c>
-      <c r="K326" t="n">
+      <c r="K326" s="0" t="n">
         <v>-13</v>
       </c>
-      <c r="L326" t="n">
+      <c r="L326" s="0" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M326" t="n">
+      <c r="M326" s="0" t="n">
         <v>-18.6</v>
       </c>
-      <c r="N326" t="n">
+      <c r="N326" s="0" t="n">
         <v>-9.300000000000001</v>
       </c>
     </row>
@@ -30199,15 +30322,138 @@
       <c r="A327" s="1" t="n">
         <v>46086</v>
       </c>
+      <c r="B327" s="0" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="C327" s="0" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="D327" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E327" s="0" t="n">
+        <v>-15</v>
+      </c>
+      <c r="F327" s="0" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="G327" s="0" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="H327" s="0" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="I327" s="0" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="J327" s="0" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="K327" s="0" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="L327" s="0" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="M327" s="0" t="n">
+        <v>-19.2</v>
+      </c>
+      <c r="N327" s="0" t="n">
+        <v>-8.800000000000001</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
         <v>46087</v>
       </c>
+      <c r="B328" s="0" t="n">
+        <v>-19.3</v>
+      </c>
+      <c r="C328" s="0" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="D328" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E328" s="0" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="F328" s="0" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G328" s="0" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="H328" s="0" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="I328" s="0" t="n">
+        <v>-16.2</v>
+      </c>
+      <c r="J328" s="0" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="K328" s="0" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="L328" s="0" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="M328" s="0" t="n">
+        <v>-11</v>
+      </c>
+      <c r="N328" s="0" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
         <v>46088</v>
+      </c>
+      <c r="B329" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="C329" t="n">
+        <v>-16.8</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="F329" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="G329" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="H329" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="I329" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J329" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="K329" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="L329" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="M329" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="N329" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="330">
@@ -34829,53 +35075,53 @@
       <c r="A84" s="1" t="n">
         <v>46085</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="0" t="n">
         <v>-26.2</v>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H84" t="n">
+      <c r="C84" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D84" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F84" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H84" s="0" t="n">
         <v>-26.34</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84" s="0" t="n">
         <v>-25.38</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J84" s="0" t="n">
         <v>-22</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K84" s="0" t="n">
         <v>-21.35</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84" s="0" t="n">
         <v>-21.64</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M84" s="0" t="n">
         <v>-27.46</v>
       </c>
-      <c r="N84" t="n">
+      <c r="N84" s="0" t="n">
         <v>-16.03</v>
       </c>
     </row>
@@ -34883,15 +35129,162 @@
       <c r="A85" s="1" t="n">
         <v>46086</v>
       </c>
+      <c r="B85" s="0" t="n">
+        <v>-28.07</v>
+      </c>
+      <c r="C85" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D85" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E85" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F85" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H85" s="0" t="n">
+        <v>-26.51</v>
+      </c>
+      <c r="I85" s="0" t="n">
+        <v>-23.74</v>
+      </c>
+      <c r="J85" s="0" t="n">
+        <v>-22.46</v>
+      </c>
+      <c r="K85" s="0" t="n">
+        <v>-21.84</v>
+      </c>
+      <c r="L85" s="0" t="n">
+        <v>-23.09</v>
+      </c>
+      <c r="M85" s="0" t="n">
+        <v>-26.52</v>
+      </c>
+      <c r="N85" s="0" t="n">
+        <v>-15.66</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
         <v>46087</v>
       </c>
+      <c r="B86" s="0" t="n">
+        <v>-25.98</v>
+      </c>
+      <c r="C86" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D86" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E86" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F86" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G86" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H86" s="0" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I86" s="0" t="n">
+        <v>-23.65</v>
+      </c>
+      <c r="J86" s="0" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="K86" s="0" t="n">
+        <v>-14.85</v>
+      </c>
+      <c r="L86" s="0" t="n">
+        <v>-20.53</v>
+      </c>
+      <c r="M86" s="0" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="N86" s="0" t="n">
+        <v>-11.25</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
         <v>46088</v>
+      </c>
+      <c r="B87" t="n">
+        <v>-24.39</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>-17.66</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-21.81</v>
+      </c>
+      <c r="J87" t="n">
+        <v>-18.02</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-17.17</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-18.39</v>
+      </c>
+      <c r="M87" t="n">
+        <v>-18.3</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-7.48</v>
       </c>
     </row>
     <row r="88">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -15377,51 +15377,92 @@
       <c r="A329" s="1" t="n">
         <v>46088</v>
       </c>
-      <c r="B329" t="n">
+      <c r="B329" s="0" t="n">
         <v>-31</v>
       </c>
-      <c r="C329" t="n">
+      <c r="C329" s="0" t="n">
         <v>-33.4</v>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E329" t="n">
+      <c r="D329" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E329" s="0" t="n">
         <v>-24.8</v>
       </c>
-      <c r="F329" t="n">
+      <c r="F329" s="0" t="n">
         <v>-28.5</v>
       </c>
-      <c r="G329" t="n">
+      <c r="G329" s="0" t="n">
         <v>-24.2</v>
       </c>
-      <c r="H329" t="n">
+      <c r="H329" s="0" t="n">
         <v>-23.9</v>
       </c>
-      <c r="I329" t="n">
+      <c r="I329" s="0" t="n">
         <v>-30</v>
       </c>
-      <c r="J329" t="n">
+      <c r="J329" s="0" t="n">
         <v>-26.9</v>
       </c>
-      <c r="K329" t="n">
+      <c r="K329" s="0" t="n">
         <v>-27</v>
       </c>
-      <c r="L329" t="n">
+      <c r="L329" s="0" t="n">
         <v>-26.1</v>
       </c>
-      <c r="M329" t="n">
+      <c r="M329" s="0" t="n">
         <v>-24.9</v>
       </c>
-      <c r="N329" t="n">
+      <c r="N329" s="0" t="n">
         <v>-12.7</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
         <v>46089</v>
+      </c>
+      <c r="B330" t="n">
+        <v>-31.7</v>
+      </c>
+      <c r="C330" t="n">
+        <v>-33.1</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>-26.4</v>
+      </c>
+      <c r="F330" t="n">
+        <v>-30.4</v>
+      </c>
+      <c r="G330" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H330" t="n">
+        <v>-26.7</v>
+      </c>
+      <c r="I330" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="J330" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="K330" t="n">
+        <v>-28.2</v>
+      </c>
+      <c r="L330" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="M330" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="N330" t="n">
+        <v>-13.8</v>
       </c>
     </row>
     <row r="331">
@@ -30414,51 +30455,92 @@
       <c r="A329" s="1" t="n">
         <v>46088</v>
       </c>
-      <c r="B329" t="n">
+      <c r="B329" s="0" t="n">
         <v>-18.3</v>
       </c>
-      <c r="C329" t="n">
+      <c r="C329" s="0" t="n">
         <v>-16.8</v>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E329" t="n">
+      <c r="D329" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E329" s="0" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="F329" t="n">
+      <c r="F329" s="0" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="G329" t="n">
+      <c r="G329" s="0" t="n">
         <v>-11.6</v>
       </c>
-      <c r="H329" t="n">
+      <c r="H329" s="0" t="n">
         <v>-8.1</v>
       </c>
-      <c r="I329" t="n">
+      <c r="I329" s="0" t="n">
         <v>-13</v>
       </c>
-      <c r="J329" t="n">
+      <c r="J329" s="0" t="n">
         <v>-11.3</v>
       </c>
-      <c r="K329" t="n">
+      <c r="K329" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="L329" t="n">
+      <c r="L329" s="0" t="n">
         <v>-6.5</v>
       </c>
-      <c r="M329" t="n">
+      <c r="M329" s="0" t="n">
         <v>-7.9</v>
       </c>
-      <c r="N329" t="n">
+      <c r="N329" s="0" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
         <v>46089</v>
+      </c>
+      <c r="B330" t="n">
+        <v>-17.9</v>
+      </c>
+      <c r="C330" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="F330" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="G330" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="H330" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="I330" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="J330" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="K330" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="L330" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="M330" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="N330" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="331">
@@ -35237,59 +35319,108 @@
       <c r="A87" s="1" t="n">
         <v>46088</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="0" t="n">
         <v>-24.39</v>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H87" t="n">
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H87" s="0" t="n">
         <v>-17.66</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87" s="0" t="n">
         <v>-21.81</v>
       </c>
-      <c r="J87" t="n">
+      <c r="J87" s="0" t="n">
         <v>-18.02</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K87" s="0" t="n">
         <v>-17.17</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87" s="0" t="n">
         <v>-18.39</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M87" s="0" t="n">
         <v>-18.3</v>
       </c>
-      <c r="N87" t="n">
+      <c r="N87" s="0" t="n">
         <v>-7.48</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
         <v>46089</v>
+      </c>
+      <c r="B88" t="n">
+        <v>-24.75</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>-17.05</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-21.29</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-18.56</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-15.72</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-19.19</v>
+      </c>
+      <c r="M88" t="n">
+        <v>-20.21</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-6.71</v>
       </c>
     </row>
     <row r="89">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -15611,47 +15611,47 @@
       <c r="A334" s="1" t="n">
         <v>46093</v>
       </c>
-      <c r="B334" t="n">
+      <c r="B334" s="0" t="n">
         <v>-27.9</v>
       </c>
-      <c r="C334" t="n">
+      <c r="C334" s="0" t="n">
         <v>-23.6</v>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F334" t="n">
+      <c r="D334" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E334" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F334" s="0" t="n">
         <v>-18.2</v>
       </c>
-      <c r="G334" t="n">
+      <c r="G334" s="0" t="n">
         <v>-22</v>
       </c>
-      <c r="H334" t="n">
+      <c r="H334" s="0" t="n">
         <v>-11.6</v>
       </c>
-      <c r="I334" t="n">
+      <c r="I334" s="0" t="n">
         <v>-24.4</v>
       </c>
-      <c r="J334" t="n">
+      <c r="J334" s="0" t="n">
         <v>-17.1</v>
       </c>
-      <c r="K334" t="n">
+      <c r="K334" s="0" t="n">
         <v>-21.3</v>
       </c>
-      <c r="L334" t="n">
+      <c r="L334" s="0" t="n">
         <v>-14.6</v>
       </c>
-      <c r="M334" t="n">
+      <c r="M334" s="0" t="n">
         <v>-20.7</v>
       </c>
-      <c r="N334" t="n">
+      <c r="N334" s="0" t="n">
         <v>-9.199999999999999</v>
       </c>
     </row>
@@ -15659,15 +15659,144 @@
       <c r="A335" s="1" t="n">
         <v>46094</v>
       </c>
+      <c r="B335" s="0" t="n">
+        <v>-29</v>
+      </c>
+      <c r="C335" s="0" t="n">
+        <v>-33</v>
+      </c>
+      <c r="D335" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E335" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F335" s="0" t="n">
+        <v>-30.4</v>
+      </c>
+      <c r="G335" s="0" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="H335" s="0" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I335" s="0" t="n">
+        <v>-24.3</v>
+      </c>
+      <c r="J335" s="0" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="K335" s="0" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="L335" s="0" t="n">
+        <v>-29.3</v>
+      </c>
+      <c r="M335" s="0" t="n">
+        <v>-31.8</v>
+      </c>
+      <c r="N335" s="0" t="n">
+        <v>-17.5</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
         <v>46095</v>
       </c>
+      <c r="B336" s="0" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="C336" s="0" t="n">
+        <v>-29</v>
+      </c>
+      <c r="D336" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E336" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F336" s="0" t="n">
+        <v>-26.5</v>
+      </c>
+      <c r="G336" s="0" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="H336" s="0" t="n">
+        <v>-22.8</v>
+      </c>
+      <c r="I336" s="0" t="n">
+        <v>-24</v>
+      </c>
+      <c r="J336" s="0" t="n">
+        <v>-21.7</v>
+      </c>
+      <c r="K336" s="0" t="n">
+        <v>-20.5</v>
+      </c>
+      <c r="L336" s="0" t="n">
+        <v>-23.7</v>
+      </c>
+      <c r="M336" s="0" t="n">
+        <v>-23.3</v>
+      </c>
+      <c r="N336" s="0" t="n">
+        <v>-14.3</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
         <v>46096</v>
+      </c>
+      <c r="B337" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="C337" t="n">
+        <v>-31</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="G337" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="H337" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="I337" t="n">
+        <v>-23.4</v>
+      </c>
+      <c r="J337" t="n">
+        <v>-23</v>
+      </c>
+      <c r="K337" t="n">
+        <v>-25.8</v>
+      </c>
+      <c r="L337" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="M337" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="N337" t="n">
+        <v>-11.7</v>
       </c>
     </row>
     <row r="338">
@@ -30857,47 +30986,47 @@
       <c r="A334" s="1" t="n">
         <v>46093</v>
       </c>
-      <c r="B334" t="n">
+      <c r="B334" s="0" t="n">
         <v>-10.4</v>
       </c>
-      <c r="C334" t="n">
+      <c r="C334" s="0" t="n">
         <v>-11.8</v>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F334" t="n">
+      <c r="D334" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E334" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F334" s="0" t="n">
         <v>-1.4</v>
       </c>
-      <c r="G334" t="n">
+      <c r="G334" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="H334" t="n">
+      <c r="H334" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="I334" t="n">
+      <c r="I334" s="0" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="J334" t="n">
+      <c r="J334" s="0" t="n">
         <v>-4.3</v>
       </c>
-      <c r="K334" t="n">
+      <c r="K334" s="0" t="n">
         <v>-4.5</v>
       </c>
-      <c r="L334" t="n">
+      <c r="L334" s="0" t="n">
         <v>-1.4</v>
       </c>
-      <c r="M334" t="n">
+      <c r="M334" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="N334" t="n">
+      <c r="N334" s="0" t="n">
         <v>9.9</v>
       </c>
     </row>
@@ -30905,15 +31034,144 @@
       <c r="A335" s="1" t="n">
         <v>46094</v>
       </c>
+      <c r="B335" s="0" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="C335" s="0" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="D335" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E335" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F335" s="0" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="G335" s="0" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="H335" s="0" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="I335" s="0" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="J335" s="0" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="K335" s="0" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L335" s="0" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="M335" s="0" t="n">
+        <v>-13</v>
+      </c>
+      <c r="N335" s="0" t="n">
+        <v>-5.5</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
         <v>46095</v>
       </c>
+      <c r="B336" s="0" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="C336" s="0" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="D336" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E336" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F336" s="0" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G336" s="0" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="H336" s="0" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I336" s="0" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="J336" s="0" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="K336" s="0" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="L336" s="0" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="M336" s="0" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="N336" s="0" t="n">
+        <v>2.1</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
         <v>46096</v>
+      </c>
+      <c r="B337" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="C337" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G337" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="H337" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I337" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="J337" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="K337" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L337" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="M337" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="N337" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="338">
@@ -35927,53 +36185,53 @@
       <c r="A92" s="1" t="n">
         <v>46093</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="0" t="n">
         <v>-18.19</v>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F92" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H92" s="0" t="n">
         <v>-4.37</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92" s="0" t="n">
         <v>-15.03</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J92" s="0" t="n">
         <v>-13.11</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K92" s="0" t="n">
         <v>-13.79</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92" s="0" t="n">
         <v>-9.91</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M92" s="0" t="n">
         <v>-17.24</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N92" s="0" t="n">
         <v>-0.39</v>
       </c>
     </row>
@@ -35981,15 +36239,164 @@
       <c r="A93" s="1" t="n">
         <v>46094</v>
       </c>
+      <c r="B93" s="0" t="n">
+        <v>-21.61</v>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F93" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H93" s="0" t="n">
+        <v>-17.54</v>
+      </c>
+      <c r="I93" s="0" t="n">
+        <v>-18.48</v>
+      </c>
+      <c r="J93" s="0" t="n">
+        <v>-20.71</v>
+      </c>
+      <c r="K93" s="0" t="n">
+        <v>-16.54</v>
+      </c>
+      <c r="L93" s="0" t="n">
+        <v>-19.59</v>
+      </c>
+      <c r="M93" s="0" t="n">
+        <v>-23.62</v>
+      </c>
+      <c r="N93" s="0" t="n">
+        <v>-10.71</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
         <v>46095</v>
       </c>
+      <c r="B94" s="0" t="n">
+        <v>-20.73</v>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H94" s="0" t="n">
+        <v>-11.75</v>
+      </c>
+      <c r="I94" s="0" t="n">
+        <v>-17.77</v>
+      </c>
+      <c r="J94" s="0" t="n">
+        <v>-14.74</v>
+      </c>
+      <c r="K94" s="0" t="n">
+        <v>-9.710000000000001</v>
+      </c>
+      <c r="L94" s="0" t="n">
+        <v>-14.53</v>
+      </c>
+      <c r="M94" s="0" t="n">
+        <v>-14.29</v>
+      </c>
+      <c r="N94" s="0" t="n">
+        <v>-7.28</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
         <v>46096</v>
+      </c>
+      <c r="B95" t="n">
+        <v>-20.39</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>-8.49</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-17.48</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>-12.76</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-14.15</v>
+      </c>
+      <c r="M95" t="n">
+        <v>-17.54</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-4.59</v>
       </c>
     </row>
     <row r="96">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -15755,47 +15755,47 @@
       <c r="A337" s="1" t="n">
         <v>46096</v>
       </c>
-      <c r="B337" t="n">
+      <c r="B337" s="0" t="n">
         <v>-26.9</v>
       </c>
-      <c r="C337" t="n">
+      <c r="C337" s="0" t="n">
         <v>-31</v>
       </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F337" t="n">
+      <c r="D337" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E337" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F337" s="0" t="n">
         <v>-26.2</v>
       </c>
-      <c r="G337" t="n">
+      <c r="G337" s="0" t="n">
         <v>-23.2</v>
       </c>
-      <c r="H337" t="n">
+      <c r="H337" s="0" t="n">
         <v>-19.5</v>
       </c>
-      <c r="I337" t="n">
+      <c r="I337" s="0" t="n">
         <v>-23.4</v>
       </c>
-      <c r="J337" t="n">
+      <c r="J337" s="0" t="n">
         <v>-23</v>
       </c>
-      <c r="K337" t="n">
+      <c r="K337" s="0" t="n">
         <v>-25.8</v>
       </c>
-      <c r="L337" t="n">
+      <c r="L337" s="0" t="n">
         <v>-23.2</v>
       </c>
-      <c r="M337" t="n">
+      <c r="M337" s="0" t="n">
         <v>-26.9</v>
       </c>
-      <c r="N337" t="n">
+      <c r="N337" s="0" t="n">
         <v>-11.7</v>
       </c>
     </row>
@@ -15803,10 +15803,96 @@
       <c r="A338" s="1" t="n">
         <v>46097</v>
       </c>
+      <c r="B338" s="0" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="C338" s="0" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="D338" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E338" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F338" s="0" t="n">
+        <v>-21.6</v>
+      </c>
+      <c r="G338" s="0" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="H338" s="0" t="n">
+        <v>-15.1</v>
+      </c>
+      <c r="I338" s="0" t="n">
+        <v>-21.3</v>
+      </c>
+      <c r="J338" s="0" t="n">
+        <v>-20.6</v>
+      </c>
+      <c r="K338" s="0" t="n">
+        <v>-19.6</v>
+      </c>
+      <c r="L338" s="0" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="M338" s="0" t="n">
+        <v>-15.7</v>
+      </c>
+      <c r="N338" s="0" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
         <v>46098</v>
+      </c>
+      <c r="B339" t="n">
+        <v>-24.4</v>
+      </c>
+      <c r="C339" t="n">
+        <v>-23.1</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>-15.9</v>
+      </c>
+      <c r="G339" t="n">
+        <v>-26</v>
+      </c>
+      <c r="H339" t="n">
+        <v>-23.3</v>
+      </c>
+      <c r="I339" t="n">
+        <v>-20.4</v>
+      </c>
+      <c r="J339" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="K339" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="L339" t="n">
+        <v>-18.6</v>
+      </c>
+      <c r="M339" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="N339" t="n">
+        <v>-16.8</v>
       </c>
     </row>
     <row r="340">
@@ -31130,47 +31216,47 @@
       <c r="A337" s="1" t="n">
         <v>46096</v>
       </c>
-      <c r="B337" t="n">
+      <c r="B337" s="0" t="n">
         <v>-12.5</v>
       </c>
-      <c r="C337" t="n">
+      <c r="C337" s="0" t="n">
         <v>-8.5</v>
       </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F337" t="n">
+      <c r="D337" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E337" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F337" s="0" t="n">
         <v>-2.8</v>
       </c>
-      <c r="G337" t="n">
+      <c r="G337" s="0" t="n">
         <v>-5.7</v>
       </c>
-      <c r="H337" t="n">
+      <c r="H337" s="0" t="n">
         <v>3.9</v>
       </c>
-      <c r="I337" t="n">
+      <c r="I337" s="0" t="n">
         <v>-10.5</v>
       </c>
-      <c r="J337" t="n">
+      <c r="J337" s="0" t="n">
         <v>-4.2</v>
       </c>
-      <c r="K337" t="n">
+      <c r="K337" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="L337" t="n">
+      <c r="L337" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="M337" t="n">
+      <c r="M337" s="0" t="n">
         <v>-6.2</v>
       </c>
-      <c r="N337" t="n">
+      <c r="N337" s="0" t="n">
         <v>2.7</v>
       </c>
     </row>
@@ -31178,10 +31264,96 @@
       <c r="A338" s="1" t="n">
         <v>46097</v>
       </c>
+      <c r="B338" s="0" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="C338" s="0" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="D338" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E338" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F338" s="0" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="G338" s="0" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="H338" s="0" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="I338" s="0" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="J338" s="0" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="K338" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L338" s="0" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="M338" s="0" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="N338" s="0" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
         <v>46098</v>
+      </c>
+      <c r="B339" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="C339" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="G339" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H339" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="I339" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="J339" t="n">
+        <v>-7</v>
+      </c>
+      <c r="K339" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="L339" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="M339" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="N339" t="n">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="340">
@@ -36347,55 +36519,55 @@
       <c r="A95" s="1" t="n">
         <v>46096</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="0" t="n">
         <v>-20.39</v>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H95" t="n">
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F95" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H95" s="0" t="n">
         <v>-8.49</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95" s="0" t="n">
         <v>-17.48</v>
       </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
+      <c r="J95" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="K95" s="0" t="n">
         <v>-12.76</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95" s="0" t="n">
         <v>-14.15</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M95" s="0" t="n">
         <v>-17.54</v>
       </c>
-      <c r="N95" t="n">
+      <c r="N95" s="0" t="n">
         <v>-4.59</v>
       </c>
     </row>
@@ -36403,10 +36575,108 @@
       <c r="A96" s="1" t="n">
         <v>46097</v>
       </c>
+      <c r="B96" s="0" t="n">
+        <v>-19.33</v>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H96" s="0" t="n">
+        <v>-9.08</v>
+      </c>
+      <c r="I96" s="0" t="n">
+        <v>-15.59</v>
+      </c>
+      <c r="J96" s="0" t="n">
+        <v>-11.47</v>
+      </c>
+      <c r="K96" s="0" t="n">
+        <v>-10.94</v>
+      </c>
+      <c r="L96" s="0" t="n">
+        <v>-10.08</v>
+      </c>
+      <c r="M96" s="0" t="n">
+        <v>-12.96</v>
+      </c>
+      <c r="N96" s="0" t="n">
+        <v>-3.66</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
         <v>46098</v>
+      </c>
+      <c r="B97" t="n">
+        <v>-17.46</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>-13.99</v>
+      </c>
+      <c r="I97" t="n">
+        <v>-13.24</v>
+      </c>
+      <c r="J97" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-11.13</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-11.61</v>
+      </c>
+      <c r="M97" t="n">
+        <v>-19.26</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-12.03</v>
       </c>
     </row>
     <row r="98">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -15851,53 +15851,96 @@
       <c r="A339" s="1" t="n">
         <v>46098</v>
       </c>
-      <c r="B339" t="n">
+      <c r="B339" s="0" t="n">
         <v>-24.4</v>
       </c>
-      <c r="C339" t="n">
+      <c r="C339" s="0" t="n">
         <v>-23.1</v>
       </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F339" t="n">
+      <c r="D339" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E339" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F339" s="0" t="n">
         <v>-15.9</v>
       </c>
-      <c r="G339" t="n">
+      <c r="G339" s="0" t="n">
         <v>-26</v>
       </c>
-      <c r="H339" t="n">
+      <c r="H339" s="0" t="n">
         <v>-23.3</v>
       </c>
-      <c r="I339" t="n">
+      <c r="I339" s="0" t="n">
         <v>-20.4</v>
       </c>
-      <c r="J339" t="n">
+      <c r="J339" s="0" t="n">
         <v>-22.2</v>
       </c>
-      <c r="K339" t="n">
+      <c r="K339" s="0" t="n">
         <v>-17.4</v>
       </c>
-      <c r="L339" t="n">
+      <c r="L339" s="0" t="n">
         <v>-18.6</v>
       </c>
-      <c r="M339" t="n">
+      <c r="M339" s="0" t="n">
         <v>-31.5</v>
       </c>
-      <c r="N339" t="n">
+      <c r="N339" s="0" t="n">
         <v>-16.8</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
         <v>46099</v>
+      </c>
+      <c r="B340" t="n">
+        <v>-24.2</v>
+      </c>
+      <c r="C340" t="n">
+        <v>-27.9</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>-25.5</v>
+      </c>
+      <c r="G340" t="n">
+        <v>-24.5</v>
+      </c>
+      <c r="H340" t="n">
+        <v>-21.4</v>
+      </c>
+      <c r="I340" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="J340" t="n">
+        <v>-24.9</v>
+      </c>
+      <c r="K340" t="n">
+        <v>-25.4</v>
+      </c>
+      <c r="L340" t="n">
+        <v>-22.1</v>
+      </c>
+      <c r="M340" t="n">
+        <v>-27.4</v>
+      </c>
+      <c r="N340" t="n">
+        <v>-14</v>
       </c>
     </row>
     <row r="341">
@@ -31312,53 +31355,96 @@
       <c r="A339" s="1" t="n">
         <v>46098</v>
       </c>
-      <c r="B339" t="n">
+      <c r="B339" s="0" t="n">
         <v>-10.7</v>
       </c>
-      <c r="C339" t="n">
+      <c r="C339" s="0" t="n">
         <v>-9.9</v>
       </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E339" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F339" t="n">
+      <c r="D339" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E339" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F339" s="0" t="n">
         <v>-5.9</v>
       </c>
-      <c r="G339" t="n">
+      <c r="G339" s="0" t="n">
         <v>-12.5</v>
       </c>
-      <c r="H339" t="n">
+      <c r="H339" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="I339" t="n">
+      <c r="I339" s="0" t="n">
         <v>-5.5</v>
       </c>
-      <c r="J339" t="n">
+      <c r="J339" s="0" t="n">
         <v>-7</v>
       </c>
-      <c r="K339" t="n">
+      <c r="K339" s="0" t="n">
         <v>-6.8</v>
       </c>
-      <c r="L339" t="n">
+      <c r="L339" s="0" t="n">
         <v>-7.2</v>
       </c>
-      <c r="M339" t="n">
+      <c r="M339" s="0" t="n">
         <v>-10.6</v>
       </c>
-      <c r="N339" t="n">
+      <c r="N339" s="0" t="n">
         <v>-7.5</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
         <v>46099</v>
+      </c>
+      <c r="B340" t="n">
+        <v>-11.4</v>
+      </c>
+      <c r="C340" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G340" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="H340" t="n">
+        <v>0</v>
+      </c>
+      <c r="I340" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="J340" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="K340" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L340" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="M340" t="n">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="N340" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -36629,59 +36715,108 @@
       <c r="A97" s="1" t="n">
         <v>46098</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="0" t="n">
         <v>-17.46</v>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H97" t="n">
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F97" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G97" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H97" s="0" t="n">
         <v>-13.99</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97" s="0" t="n">
         <v>-13.24</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J97" s="0" t="n">
         <v>-12.7</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K97" s="0" t="n">
         <v>-11.13</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97" s="0" t="n">
         <v>-11.61</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M97" s="0" t="n">
         <v>-19.26</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N97" s="0" t="n">
         <v>-12.03</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
         <v>46099</v>
+      </c>
+      <c r="B98" t="n">
+        <v>-18.81</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>-12.11</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-13.15</v>
+      </c>
+      <c r="J98" t="n">
+        <v>-15.4</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-13.64</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-12.89</v>
+      </c>
+      <c r="M98" t="n">
+        <v>-18.44</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-7.65</v>
       </c>
     </row>
     <row r="99">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_C7398BD659FA20664B8CDD34B7C4826D8E129986" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E05254-F0F4-4A6B-8E0E-D4C4A0B2333F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="16">
   <si>
     <t>日期</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>无</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	-7.79</t>
   </si>
 </sst>
 </file>
@@ -485,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N351"/>
+  <dimension ref="A1:N444"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="2" customWidth="1"/>
@@ -15631,35 +15634,773 @@
       <c r="A345" s="1">
         <v>46104</v>
       </c>
+      <c r="B345">
+        <v>-15.4</v>
+      </c>
+      <c r="C345">
+        <v>-17.399999999999999</v>
+      </c>
+      <c r="D345" t="s">
+        <v>14</v>
+      </c>
+      <c r="E345" t="s">
+        <v>14</v>
+      </c>
+      <c r="F345">
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="G345" t="s">
+        <v>14</v>
+      </c>
+      <c r="H345">
+        <v>-5.2</v>
+      </c>
+      <c r="I345">
+        <v>-10.199999999999999</v>
+      </c>
+      <c r="J345">
+        <v>-14.5</v>
+      </c>
+      <c r="K345">
+        <v>-8</v>
+      </c>
+      <c r="L345">
+        <v>-12.7</v>
+      </c>
+      <c r="M345">
+        <v>-17</v>
+      </c>
+      <c r="N345">
+        <v>-2.6</v>
+      </c>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A346" s="1">
         <v>46105</v>
       </c>
+      <c r="B346">
+        <v>-12.8</v>
+      </c>
+      <c r="C346">
+        <v>-16.600000000000001</v>
+      </c>
+      <c r="D346" t="s">
+        <v>14</v>
+      </c>
+      <c r="E346" t="s">
+        <v>14</v>
+      </c>
+      <c r="F346">
+        <v>-18</v>
+      </c>
+      <c r="G346">
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="H346">
+        <v>-1.4</v>
+      </c>
+      <c r="I346">
+        <v>-12.9</v>
+      </c>
+      <c r="J346">
+        <v>-16</v>
+      </c>
+      <c r="K346">
+        <v>-17.5</v>
+      </c>
+      <c r="L346">
+        <v>-14.3</v>
+      </c>
+      <c r="M346">
+        <v>-18.3</v>
+      </c>
+      <c r="N346">
+        <v>-3.3</v>
+      </c>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A347" s="1">
         <v>46106</v>
       </c>
+      <c r="B347">
+        <v>-16.600000000000001</v>
+      </c>
+      <c r="C347">
+        <v>-11.5</v>
+      </c>
+      <c r="D347" t="s">
+        <v>14</v>
+      </c>
+      <c r="E347" t="s">
+        <v>14</v>
+      </c>
+      <c r="F347">
+        <v>-10.5</v>
+      </c>
+      <c r="G347">
+        <v>-8.1999999999999993</v>
+      </c>
+      <c r="H347">
+        <v>-3.2</v>
+      </c>
+      <c r="I347">
+        <v>-6.7</v>
+      </c>
+      <c r="J347">
+        <v>-5.9</v>
+      </c>
+      <c r="K347">
+        <v>-8.1</v>
+      </c>
+      <c r="L347">
+        <v>-5.5</v>
+      </c>
+      <c r="M347">
+        <v>-9.6999999999999993</v>
+      </c>
+      <c r="N347">
+        <v>-3.3</v>
+      </c>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A348" s="1">
         <v>46107</v>
       </c>
+      <c r="B348">
+        <v>-17</v>
+      </c>
+      <c r="C348">
+        <v>-22.2</v>
+      </c>
+      <c r="D348" t="s">
+        <v>14</v>
+      </c>
+      <c r="E348" t="s">
+        <v>14</v>
+      </c>
+      <c r="F348">
+        <v>-16.100000000000001</v>
+      </c>
+      <c r="G348">
+        <v>-15.2</v>
+      </c>
+      <c r="H348">
+        <v>-6.1</v>
+      </c>
+      <c r="I348">
+        <v>-9.8000000000000007</v>
+      </c>
+      <c r="J348">
+        <v>-18.5</v>
+      </c>
+      <c r="K348">
+        <v>-23.3</v>
+      </c>
+      <c r="L348">
+        <v>-14.1</v>
+      </c>
+      <c r="M348">
+        <v>-18.600000000000001</v>
+      </c>
+      <c r="N348">
+        <v>-7.9</v>
+      </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A349" s="1">
         <v>46108</v>
       </c>
+      <c r="B349">
+        <v>-10.7</v>
+      </c>
+      <c r="C349">
+        <v>-17.2</v>
+      </c>
+      <c r="D349" t="s">
+        <v>14</v>
+      </c>
+      <c r="E349" t="s">
+        <v>14</v>
+      </c>
+      <c r="F349">
+        <v>-14.6</v>
+      </c>
+      <c r="G349">
+        <v>-11.6</v>
+      </c>
+      <c r="H349">
+        <v>-3.7</v>
+      </c>
+      <c r="I349">
+        <v>-5.5</v>
+      </c>
+      <c r="J349">
+        <v>-14.7</v>
+      </c>
+      <c r="K349">
+        <v>-17.2</v>
+      </c>
+      <c r="L349">
+        <v>-11.1</v>
+      </c>
+      <c r="M349">
+        <v>-16.899999999999999</v>
+      </c>
+      <c r="N349">
+        <v>-4.4000000000000004</v>
+      </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A350" s="1">
         <v>46109</v>
       </c>
+      <c r="B350">
+        <v>-13</v>
+      </c>
+      <c r="C350">
+        <v>-13.5</v>
+      </c>
+      <c r="D350" t="s">
+        <v>14</v>
+      </c>
+      <c r="E350" t="s">
+        <v>14</v>
+      </c>
+      <c r="F350">
+        <v>-7.3</v>
+      </c>
+      <c r="G350">
+        <v>-5.2</v>
+      </c>
+      <c r="H350">
+        <v>0.8</v>
+      </c>
+      <c r="I350">
+        <v>-4.2</v>
+      </c>
+      <c r="J350">
+        <v>-6.8</v>
+      </c>
+      <c r="K350">
+        <v>-8.6</v>
+      </c>
+      <c r="L350">
+        <v>-4.2</v>
+      </c>
+      <c r="M350">
+        <v>-6</v>
+      </c>
+      <c r="N350">
+        <v>-3.9</v>
+      </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A351" s="1">
         <v>46110</v>
+      </c>
+      <c r="B351">
+        <v>-11.9</v>
+      </c>
+      <c r="C351">
+        <v>-18.899999999999999</v>
+      </c>
+      <c r="D351" t="s">
+        <v>14</v>
+      </c>
+      <c r="E351" t="s">
+        <v>14</v>
+      </c>
+      <c r="F351">
+        <v>-14.7</v>
+      </c>
+      <c r="G351">
+        <v>-11.2</v>
+      </c>
+      <c r="H351">
+        <v>-6</v>
+      </c>
+      <c r="I351">
+        <v>-5.7</v>
+      </c>
+      <c r="J351">
+        <v>-10.199999999999999</v>
+      </c>
+      <c r="K351">
+        <v>-15.6</v>
+      </c>
+      <c r="L351">
+        <v>-8.5</v>
+      </c>
+      <c r="M351">
+        <v>-11.9</v>
+      </c>
+      <c r="N351">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A352" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A353" s="1">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A354" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A355" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A356" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A357" s="1">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A358" s="1">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A359" s="1">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A360" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A361" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A362" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A363" s="1">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A364" s="1">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A365" s="1">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A366" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A367" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A368" s="1">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A369" s="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A370" s="1">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A371" s="1">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A372" s="1">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A373" s="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A374" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A375" s="1">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A376" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A377" s="1">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A378" s="1">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A379" s="1">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A380" s="1">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A381" s="1">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A382" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A383" s="1">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A384" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A385" s="1">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A386" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A387" s="1">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A388" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A389" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A390" s="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A391" s="1">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A392" s="1">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A393" s="1">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A394" s="1">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A395" s="1">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A396" s="1">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A397" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A398" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A399" s="1">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A400" s="1">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A401" s="1">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A402" s="1">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A403" s="1">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A404" s="1">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A405" s="1">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A406" s="1">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A407" s="1">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A408" s="1">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A409" s="1">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A410" s="1">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A411" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A412" s="1">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A413" s="1">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A414" s="1">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A415" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A416" s="1">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A417" s="1">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A418" s="1">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A419" s="1">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A420" s="1">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A421" s="1">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A422" s="1">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A423" s="1">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A424" s="1">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A425" s="1">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A426" s="1">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A427" s="1">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A428" s="1">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A429" s="1">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A430" s="1">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A431" s="1">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A432" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A433" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A434" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A435" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A436" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A437" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A438" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A439" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A440" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A441" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A442" s="1">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A443" s="1">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A444" s="1">
+        <v>46203</v>
       </c>
     </row>
   </sheetData>
@@ -15670,7 +16411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N351"/>
+  <dimension ref="A1:N444"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="2" customWidth="1"/>
@@ -30816,35 +31557,773 @@
       <c r="A345" s="1">
         <v>46104</v>
       </c>
+      <c r="B345">
+        <v>-5</v>
+      </c>
+      <c r="C345">
+        <v>-3.9</v>
+      </c>
+      <c r="D345" t="s">
+        <v>14</v>
+      </c>
+      <c r="E345" t="s">
+        <v>14</v>
+      </c>
+      <c r="F345">
+        <v>3.1</v>
+      </c>
+      <c r="G345">
+        <v>0.7</v>
+      </c>
+      <c r="H345">
+        <v>11.5</v>
+      </c>
+      <c r="I345">
+        <v>-5.4</v>
+      </c>
+      <c r="J345">
+        <v>2.8</v>
+      </c>
+      <c r="K345">
+        <v>1.9</v>
+      </c>
+      <c r="L345">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M345">
+        <v>0.1</v>
+      </c>
+      <c r="N345">
+        <v>12.9</v>
+      </c>
     </row>
     <row r="346" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A346" s="1">
         <v>46105</v>
       </c>
+      <c r="B346">
+        <v>-5.3</v>
+      </c>
+      <c r="C346">
+        <v>-3.1</v>
+      </c>
+      <c r="D346" t="s">
+        <v>14</v>
+      </c>
+      <c r="E346" t="s">
+        <v>14</v>
+      </c>
+      <c r="F346">
+        <v>3.6</v>
+      </c>
+      <c r="G346">
+        <v>0.2</v>
+      </c>
+      <c r="H346">
+        <v>7.7</v>
+      </c>
+      <c r="I346">
+        <v>-5.9</v>
+      </c>
+      <c r="J346">
+        <v>3.3</v>
+      </c>
+      <c r="K346">
+        <v>2.8</v>
+      </c>
+      <c r="L346">
+        <v>4.8</v>
+      </c>
+      <c r="M346">
+        <v>3.7</v>
+      </c>
+      <c r="N346">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="347" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A347" s="1">
         <v>46106</v>
       </c>
+      <c r="B347">
+        <v>-1.4</v>
+      </c>
+      <c r="C347">
+        <v>-1.7</v>
+      </c>
+      <c r="D347" t="s">
+        <v>14</v>
+      </c>
+      <c r="E347" t="s">
+        <v>14</v>
+      </c>
+      <c r="F347">
+        <v>0.9</v>
+      </c>
+      <c r="G347">
+        <v>-1.3</v>
+      </c>
+      <c r="H347">
+        <v>6.2</v>
+      </c>
+      <c r="I347">
+        <v>1.7</v>
+      </c>
+      <c r="J347">
+        <v>-1.8</v>
+      </c>
+      <c r="K347">
+        <v>1.6</v>
+      </c>
+      <c r="L347">
+        <v>1.9</v>
+      </c>
+      <c r="M347">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="N347">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="348" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A348" s="1">
         <v>46107</v>
       </c>
+      <c r="B348">
+        <v>-3.8</v>
+      </c>
+      <c r="C348">
+        <v>-2.4</v>
+      </c>
+      <c r="D348" t="s">
+        <v>14</v>
+      </c>
+      <c r="E348" t="s">
+        <v>14</v>
+      </c>
+      <c r="F348">
+        <v>2.7</v>
+      </c>
+      <c r="G348">
+        <v>0.9</v>
+      </c>
+      <c r="H348">
+        <v>10.3</v>
+      </c>
+      <c r="I348">
+        <v>0.3</v>
+      </c>
+      <c r="J348">
+        <v>-2.4</v>
+      </c>
+      <c r="K348">
+        <v>-0.1</v>
+      </c>
+      <c r="L348">
+        <v>1.4</v>
+      </c>
+      <c r="M348">
+        <v>1.7</v>
+      </c>
+      <c r="N348">
+        <v>7.9</v>
+      </c>
     </row>
     <row r="349" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A349" s="1">
         <v>46108</v>
       </c>
+      <c r="B349">
+        <v>-2</v>
+      </c>
+      <c r="C349">
+        <v>-0.6</v>
+      </c>
+      <c r="D349" t="s">
+        <v>14</v>
+      </c>
+      <c r="E349" t="s">
+        <v>14</v>
+      </c>
+      <c r="F349">
+        <v>5.8</v>
+      </c>
+      <c r="G349">
+        <v>3.3</v>
+      </c>
+      <c r="H349">
+        <v>11.5</v>
+      </c>
+      <c r="I349">
+        <v>0.3</v>
+      </c>
+      <c r="J349">
+        <v>-0.1</v>
+      </c>
+      <c r="K349">
+        <v>3.2</v>
+      </c>
+      <c r="L349">
+        <v>3.8</v>
+      </c>
+      <c r="M349">
+        <v>2.7</v>
+      </c>
+      <c r="N349">
+        <v>10.4</v>
+      </c>
     </row>
     <row r="350" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A350" s="1">
         <v>46109</v>
       </c>
+      <c r="B350">
+        <v>0.1</v>
+      </c>
+      <c r="C350">
+        <v>-1.8</v>
+      </c>
+      <c r="D350" t="s">
+        <v>14</v>
+      </c>
+      <c r="E350" t="s">
+        <v>14</v>
+      </c>
+      <c r="F350">
+        <v>1.4</v>
+      </c>
+      <c r="G350">
+        <v>1.6</v>
+      </c>
+      <c r="H350">
+        <v>6.5</v>
+      </c>
+      <c r="I350">
+        <v>1.7</v>
+      </c>
+      <c r="J350">
+        <v>-1.6</v>
+      </c>
+      <c r="K350">
+        <v>-0.9</v>
+      </c>
+      <c r="L350">
+        <v>2.7</v>
+      </c>
+      <c r="M350">
+        <v>1.7</v>
+      </c>
+      <c r="N350">
+        <v>4.5</v>
+      </c>
     </row>
     <row r="351" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A351" s="1">
         <v>46110</v>
+      </c>
+      <c r="B351">
+        <v>-1.4</v>
+      </c>
+      <c r="C351">
+        <v>-0.4</v>
+      </c>
+      <c r="D351" t="s">
+        <v>14</v>
+      </c>
+      <c r="E351" t="s">
+        <v>14</v>
+      </c>
+      <c r="F351">
+        <v>2.5</v>
+      </c>
+      <c r="G351">
+        <v>2.7</v>
+      </c>
+      <c r="H351">
+        <v>11.3</v>
+      </c>
+      <c r="I351">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="J351">
+        <v>0.9</v>
+      </c>
+      <c r="K351">
+        <v>3</v>
+      </c>
+      <c r="L351">
+        <v>4.7</v>
+      </c>
+      <c r="M351">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="N351">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A352" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A353" s="1">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A354" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A355" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A356" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A357" s="1">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A358" s="1">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A359" s="1">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A360" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A361" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A362" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A363" s="1">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A364" s="1">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A365" s="1">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A366" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A367" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A368" s="1">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A369" s="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A370" s="1">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A371" s="1">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A372" s="1">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A373" s="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A374" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A375" s="1">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A376" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A377" s="1">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A378" s="1">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A379" s="1">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A380" s="1">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A381" s="1">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A382" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A383" s="1">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A384" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A385" s="1">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A386" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A387" s="1">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A388" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A389" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A390" s="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A391" s="1">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A392" s="1">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A393" s="1">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A394" s="1">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A395" s="1">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A396" s="1">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A397" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A398" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A399" s="1">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A400" s="1">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A401" s="1">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A402" s="1">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A403" s="1">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A404" s="1">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A405" s="1">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A406" s="1">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A407" s="1">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A408" s="1">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A409" s="1">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A410" s="1">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A411" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A412" s="1">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A413" s="1">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A414" s="1">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A415" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A416" s="1">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A417" s="1">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A418" s="1">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A419" s="1">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A420" s="1">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A421" s="1">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A422" s="1">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A423" s="1">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A424" s="1">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A425" s="1">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A426" s="1">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A427" s="1">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A428" s="1">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A429" s="1">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A430" s="1">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A431" s="1">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A432" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A433" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A434" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A435" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A436" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A437" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A438" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A439" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A440" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A441" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A442" s="1">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A443" s="1">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A444" s="1">
+        <v>46203</v>
       </c>
     </row>
   </sheetData>
@@ -30855,7 +32334,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N109"/>
+  <dimension ref="A1:N212"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="2" customWidth="1"/>
@@ -35353,36 +36832,804 @@
       <c r="A103" s="1">
         <v>46104</v>
       </c>
+      <c r="B103">
+        <v>-9.9499999999999993</v>
+      </c>
+      <c r="C103" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103" t="s">
+        <v>14</v>
+      </c>
+      <c r="E103" t="s">
+        <v>14</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103" t="s">
+        <v>14</v>
+      </c>
+      <c r="H103">
+        <v>1.74</v>
+      </c>
+      <c r="I103">
+        <v>-8.18</v>
+      </c>
+      <c r="J103">
+        <v>-6.97</v>
+      </c>
+      <c r="K103">
+        <v>-0.41</v>
+      </c>
+      <c r="L103">
+        <v>-4.33</v>
+      </c>
+      <c r="M103">
+        <v>-7.96</v>
+      </c>
+      <c r="N103">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A104" s="1">
         <v>46105</v>
       </c>
+      <c r="B104">
+        <v>-10</v>
+      </c>
+      <c r="C104" t="s">
+        <v>14</v>
+      </c>
+      <c r="D104" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" t="s">
+        <v>14</v>
+      </c>
+      <c r="H104">
+        <v>3.06</v>
+      </c>
+      <c r="I104">
+        <v>-9.25</v>
+      </c>
+      <c r="J104">
+        <v>-6.88</v>
+      </c>
+      <c r="K104">
+        <v>-5.79</v>
+      </c>
+      <c r="L104">
+        <v>-4.71</v>
+      </c>
+      <c r="M104">
+        <v>-9.34</v>
+      </c>
+      <c r="N104">
+        <v>3.11</v>
+      </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A105" s="1">
         <v>46106</v>
       </c>
+      <c r="B105" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" t="s">
+        <v>14</v>
+      </c>
+      <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105" t="s">
+        <v>14</v>
+      </c>
+      <c r="H105">
+        <v>0.19</v>
+      </c>
+      <c r="I105">
+        <v>-1.59</v>
+      </c>
+      <c r="J105">
+        <v>-4.03</v>
+      </c>
+      <c r="K105">
+        <v>-5.46</v>
+      </c>
+      <c r="L105">
+        <v>-2.95</v>
+      </c>
+      <c r="M105">
+        <v>-5.34</v>
+      </c>
+      <c r="N105">
+        <v>0.86</v>
+      </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A106" s="1">
         <v>46107</v>
       </c>
+      <c r="B106">
+        <v>-9.42</v>
+      </c>
+      <c r="C106" t="s">
+        <v>14</v>
+      </c>
+      <c r="D106" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106" t="s">
+        <v>14</v>
+      </c>
+      <c r="H106">
+        <v>0.79</v>
+      </c>
+      <c r="I106">
+        <v>-4.6100000000000003</v>
+      </c>
+      <c r="J106">
+        <v>-10.14</v>
+      </c>
+      <c r="K106">
+        <v>-12.85</v>
+      </c>
+      <c r="L106">
+        <v>-6.55</v>
+      </c>
+      <c r="M106" t="s">
+        <v>14</v>
+      </c>
+      <c r="N106">
+        <v>-0.72</v>
+      </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A107" s="1">
         <v>46108</v>
       </c>
+      <c r="B107">
+        <v>-6.66</v>
+      </c>
+      <c r="C107" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" t="s">
+        <v>14</v>
+      </c>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107" t="s">
+        <v>14</v>
+      </c>
+      <c r="H107">
+        <v>2.96</v>
+      </c>
+      <c r="I107">
+        <v>-3.44</v>
+      </c>
+      <c r="J107">
+        <v>-7.03</v>
+      </c>
+      <c r="K107">
+        <v>-7.16</v>
+      </c>
+      <c r="L107">
+        <v>-3.66</v>
+      </c>
+      <c r="M107">
+        <v>-6.26</v>
+      </c>
+      <c r="N107">
+        <v>2.67</v>
+      </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A108" s="1">
         <v>46109</v>
       </c>
+      <c r="B108">
+        <v>-5.39</v>
+      </c>
+      <c r="C108" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" t="s">
+        <v>14</v>
+      </c>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108" t="s">
+        <v>14</v>
+      </c>
+      <c r="H108">
+        <v>2.97</v>
+      </c>
+      <c r="I108">
+        <v>-1.9</v>
+      </c>
+      <c r="J108">
+        <v>-4.33</v>
+      </c>
+      <c r="K108">
+        <v>-4.55</v>
+      </c>
+      <c r="L108">
+        <v>-1.54</v>
+      </c>
+      <c r="M108">
+        <v>-2.83</v>
+      </c>
+      <c r="N108">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A109" s="1">
         <v>46110</v>
       </c>
+      <c r="B109">
+        <v>-7.1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>14</v>
+      </c>
+      <c r="D109" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" t="s">
+        <v>14</v>
+      </c>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109">
+        <v>1.26</v>
+      </c>
+      <c r="I109">
+        <v>-1.89</v>
+      </c>
+      <c r="J109">
+        <v>-5.18</v>
+      </c>
+      <c r="K109">
+        <v>-5.81</v>
+      </c>
+      <c r="L109">
+        <v>-2.83</v>
+      </c>
+      <c r="M109">
+        <v>-4.6100000000000003</v>
+      </c>
+      <c r="N109">
+        <v>-1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A110" s="1">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A111" s="1">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A112" s="1">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A113" s="1">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A114" s="1">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A115" s="1">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A116" s="1">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A117" s="1">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A118" s="1">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A119" s="1">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A120" s="1">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A121" s="1">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A122" s="1">
+        <v>46123</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A123" s="1">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A124" s="1">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A125" s="1">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A126" s="1">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A127" s="1">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A128" s="1">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A129" s="1">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A130" s="1">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A131" s="1">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A132" s="1">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A133" s="1">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A134" s="1">
+        <v>46135</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A135" s="1">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A136" s="1">
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A137" s="1">
+        <v>46138</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A138" s="1">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A139" s="1">
+        <v>46140</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A140" s="1">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A141" s="1">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A142" s="1">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A143" s="1">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A144" s="1">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A145" s="1">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A146" s="1">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A147" s="1">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A148" s="1">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A149" s="1">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A150" s="1">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A151" s="1">
+        <v>46152</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A152" s="1">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A153" s="1">
+        <v>46154</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A154" s="1">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A155" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A156" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A157" s="1">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A158" s="1">
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A159" s="1">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A160" s="1">
+        <v>46161</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A161" s="1">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A162" s="1">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A163" s="1">
+        <v>46164</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A164" s="1">
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A165" s="1">
+        <v>46166</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A166" s="1">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A167" s="1">
+        <v>46168</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A168" s="1">
+        <v>46169</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A169" s="1">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A170" s="1">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A171" s="1">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A172" s="1">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A173" s="1">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A174" s="1">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A175" s="1">
+        <v>46176</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A176" s="1">
+        <v>46177</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A177" s="1">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A178" s="1">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A179" s="1">
+        <v>46180</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A180" s="1">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A181" s="1">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A182" s="1">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A183" s="1">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A184" s="1">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A185" s="1">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A186" s="1">
+        <v>46187</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A187" s="1">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A188" s="1">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A189" s="1">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A190" s="1">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A191" s="1">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A192" s="1">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A193" s="1">
+        <v>46194</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A194" s="1">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A195" s="1">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A196" s="1">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A197" s="1">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A198" s="1">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A199" s="1">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A200" s="1">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A201" s="1">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A202" s="1">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A203" s="1"/>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A204" s="1"/>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A205" s="1"/>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A206" s="1"/>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A207" s="1"/>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A208" s="1"/>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A209" s="1"/>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A210" s="1"/>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A211" s="1"/>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A212" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -17033,45 +17033,45 @@
       <c r="A364" s="1" t="n">
         <v>46123</v>
       </c>
-      <c r="B364" t="n">
+      <c r="B364" s="0" t="n">
         <v>1.9</v>
       </c>
-      <c r="C364" t="n">
+      <c r="C364" s="0" t="n">
         <v>3.3</v>
       </c>
-      <c r="D364" t="n">
+      <c r="D364" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F364" t="n">
+      <c r="E364" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F364" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="G364" t="n">
+      <c r="G364" s="0" t="n">
         <v>-5</v>
       </c>
-      <c r="H364" t="n">
+      <c r="H364" s="0" t="n">
         <v>-2.3</v>
       </c>
-      <c r="I364" t="n">
+      <c r="I364" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="J364" t="n">
+      <c r="J364" s="0" t="n">
         <v>0.9</v>
       </c>
-      <c r="K364" t="n">
+      <c r="K364" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="L364" t="n">
+      <c r="L364" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="M364" t="n">
+      <c r="M364" s="0" t="n">
         <v>-4.6</v>
       </c>
-      <c r="N364" t="n">
+      <c r="N364" s="0" t="n">
         <v>-1.8</v>
       </c>
     </row>
@@ -17079,35 +17079,322 @@
       <c r="A365" s="1" t="n">
         <v>46124</v>
       </c>
+      <c r="B365" s="0" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="C365" s="0" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="D365" s="0" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="E365" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F365" s="0" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="G365" s="0" t="n">
+        <v>-12.4</v>
+      </c>
+      <c r="H365" s="0" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="I365" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J365" s="0" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="K365" s="0" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="L365" s="0" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="M365" s="0" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="N365" s="0" t="n">
+        <v>-8.1</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
         <v>46125</v>
       </c>
+      <c r="B366" s="0" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="C366" s="0" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="D366" s="0" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E366" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F366" s="0" t="n">
+        <v>-10.8</v>
+      </c>
+      <c r="G366" s="0" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H366" s="0" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="I366" s="0" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J366" s="0" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="K366" s="0" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="L366" s="0" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="M366" s="0" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="N366" s="0" t="n">
+        <v>-5.6</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
         <v>46126</v>
       </c>
+      <c r="B367" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C367" s="0" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D367" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E367" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F367" s="0" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="G367" s="0" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="H367" s="0" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="I367" s="0" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J367" s="0" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="K367" s="0" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L367" s="0" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="M367" s="0" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="N367" s="0" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
         <v>46127</v>
       </c>
+      <c r="B368" s="0" t="n">
+        <v>-7</v>
+      </c>
+      <c r="C368" s="0" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="D368" s="0" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="E368" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F368" s="0" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="G368" s="0" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="H368" s="0" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="I368" s="0" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="J368" s="0" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="K368" s="0" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="L368" s="0" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="M368" s="0" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="N368" s="0" t="n">
+        <v>-2.7</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
         <v>46128</v>
       </c>
+      <c r="B369" s="0" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="C369" s="0" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="D369" s="0" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="E369" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F369" s="0" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G369" s="0" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="H369" s="0" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="I369" s="0" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J369" s="0" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="K369" s="0" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L369" s="0" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="M369" s="0" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="N369" s="0" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
         <v>46129</v>
       </c>
+      <c r="B370" s="0" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="C370" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D370" s="0" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E370" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F370" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G370" s="0" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H370" s="0" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="I370" s="0" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="J370" s="0" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="K370" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L370" s="0" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="M370" s="0" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="N370" s="0" t="n">
+        <v>-2.6</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
         <v>46130</v>
+      </c>
+      <c r="B371" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="C371" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="D371" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="G371" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="H371" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I371" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="J371" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="K371" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="L371" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="M371" t="n">
+        <v>-10</v>
+      </c>
+      <c r="N371" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="372">
@@ -34010,45 +34297,45 @@
       <c r="A364" s="1" t="n">
         <v>46123</v>
       </c>
-      <c r="B364" t="n">
+      <c r="B364" s="0" t="n">
         <v>12.8</v>
       </c>
-      <c r="C364" t="n">
+      <c r="C364" s="0" t="n">
         <v>12.7</v>
       </c>
-      <c r="D364" t="n">
+      <c r="D364" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F364" t="n">
+      <c r="E364" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F364" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="G364" t="n">
+      <c r="G364" s="0" t="n">
         <v>2.6</v>
       </c>
-      <c r="H364" t="n">
+      <c r="H364" s="0" t="n">
         <v>6.8</v>
       </c>
-      <c r="I364" t="n">
+      <c r="I364" s="0" t="n">
         <v>13.1</v>
       </c>
-      <c r="J364" t="n">
+      <c r="J364" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="K364" t="n">
+      <c r="K364" s="0" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="L364" t="n">
+      <c r="L364" s="0" t="n">
         <v>12.4</v>
       </c>
-      <c r="M364" t="n">
+      <c r="M364" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="N364" t="n">
+      <c r="N364" s="0" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -34056,35 +34343,322 @@
       <c r="A365" s="1" t="n">
         <v>46124</v>
       </c>
+      <c r="B365" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C365" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D365" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E365" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F365" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G365" s="0" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H365" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I365" s="0" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J365" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K365" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L365" s="0" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M365" s="0" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="N365" s="0" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
         <v>46125</v>
       </c>
+      <c r="B366" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C366" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D366" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E366" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F366" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="G366" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H366" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I366" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="J366" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K366" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L366" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="M366" s="0" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N366" s="0" t="n">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
         <v>46126</v>
       </c>
+      <c r="B367" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="C367" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D367" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E367" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F367" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G367" s="0" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="H367" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I367" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J367" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K367" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L367" s="0" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M367" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N367" s="0" t="n">
+        <v>13.6</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
         <v>46127</v>
       </c>
+      <c r="B368" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C368" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="D368" s="0" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E368" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F368" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G368" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H368" s="0" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I368" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J368" s="0" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K368" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L368" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M368" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N368" s="0" t="n">
+        <v>10.2</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
         <v>46128</v>
       </c>
+      <c r="B369" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C369" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D369" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E369" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F369" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G369" s="0" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H369" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I369" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J369" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K369" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L369" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M369" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N369" s="0" t="n">
+        <v>11.9</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
         <v>46129</v>
       </c>
+      <c r="B370" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C370" s="0" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D370" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E370" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F370" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G370" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H370" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I370" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J370" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K370" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="L370" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M370" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N370" s="0" t="n">
+        <v>18.3</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
         <v>46130</v>
+      </c>
+      <c r="B371" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="C371" t="n">
+        <v>16</v>
+      </c>
+      <c r="D371" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G371" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H371" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I371" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J371" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K371" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L371" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M371" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N371" t="n">
+        <v>17.2</v>
       </c>
     </row>
     <row r="372">
@@ -41019,53 +41593,53 @@
       <c r="A122" s="1" t="n">
         <v>46123</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
+      <c r="C122" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D122" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E122" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F122" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G122" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H122" s="0" t="n">
         <v>1.36</v>
       </c>
-      <c r="I122" t="n">
+      <c r="I122" s="0" t="n">
         <v>9.16</v>
       </c>
-      <c r="J122" t="n">
+      <c r="J122" s="0" t="n">
         <v>4.41</v>
       </c>
-      <c r="K122" t="n">
+      <c r="K122" s="0" t="n">
         <v>4.15</v>
       </c>
-      <c r="L122" t="n">
+      <c r="L122" s="0" t="n">
         <v>5.25</v>
       </c>
-      <c r="M122" t="n">
+      <c r="M122" s="0" t="n">
         <v>-1.49</v>
       </c>
-      <c r="N122" t="n">
+      <c r="N122" s="0" t="n">
         <v>4.27</v>
       </c>
     </row>
@@ -41073,35 +41647,380 @@
       <c r="A123" s="1" t="n">
         <v>46124</v>
       </c>
+      <c r="B123" s="0" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="C123" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D123" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E123" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F123" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G123" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H123" s="0" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I123" s="0" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="J123" s="0" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="K123" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L123" s="0" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M123" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N123" s="0" t="n">
+        <v>-2.05</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
         <v>46125</v>
       </c>
+      <c r="B124" s="0" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="C124" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D124" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E124" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F124" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G124" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H124" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I124" s="0" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="J124" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K124" s="0" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="L124" s="0" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="M124" s="0" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="N124" s="0" t="n">
+        <v>-0.26</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
         <v>46126</v>
       </c>
+      <c r="B125" s="0" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="C125" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D125" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E125" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F125" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G125" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H125" s="0" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="I125" s="0" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="J125" s="0" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K125" s="0" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L125" s="0" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M125" s="0" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="N125" s="0" t="n">
+        <v>6.64</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
         <v>46127</v>
       </c>
+      <c r="B126" s="0" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="C126" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D126" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E126" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F126" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G126" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H126" s="0" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I126" s="0" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="J126" s="0" t="n">
+        <v>-2.91</v>
+      </c>
+      <c r="K126" s="0" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="L126" s="0" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="M126" s="0" t="n">
+        <v>-6.78</v>
+      </c>
+      <c r="N126" s="0" t="n">
+        <v>1.14</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
         <v>46128</v>
       </c>
+      <c r="B127" s="0" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="C127" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D127" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E127" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F127" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G127" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H127" s="0" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I127" s="0" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="J127" s="0" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K127" s="0" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L127" s="0" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M127" s="0" t="n">
+        <v>-3.19</v>
+      </c>
+      <c r="N127" s="0" t="n">
+        <v>3.66</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
         <v>46129</v>
       </c>
+      <c r="B128" s="0" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="C128" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D128" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E128" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F128" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G128" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H128" s="0" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="I128" s="0" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="J128" s="0" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K128" s="0" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="L128" s="0" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M128" s="0" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N128" s="0" t="n">
+        <v>7.76</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
         <v>46130</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I129" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L129" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="N129" t="n">
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="130">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -17355,45 +17355,45 @@
       <c r="A371" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="B371" t="n">
+      <c r="B371" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="C371" t="n">
+      <c r="C371" s="0" t="n">
         <v>-6.9</v>
       </c>
-      <c r="D371" t="n">
+      <c r="D371" s="0" t="n">
         <v>-5.4</v>
       </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F371" t="n">
+      <c r="E371" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F371" s="0" t="n">
         <v>-7.8</v>
       </c>
-      <c r="G371" t="n">
+      <c r="G371" s="0" t="n">
         <v>-9.800000000000001</v>
       </c>
-      <c r="H371" t="n">
+      <c r="H371" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="I371" t="n">
+      <c r="I371" s="0" t="n">
         <v>-6.3</v>
       </c>
-      <c r="J371" t="n">
+      <c r="J371" s="0" t="n">
         <v>-6.1</v>
       </c>
-      <c r="K371" t="n">
+      <c r="K371" s="0" t="n">
         <v>-11.2</v>
       </c>
-      <c r="L371" t="n">
+      <c r="L371" s="0" t="n">
         <v>-7.8</v>
       </c>
-      <c r="M371" t="n">
+      <c r="M371" s="0" t="n">
         <v>-10</v>
       </c>
-      <c r="N371" t="n">
+      <c r="N371" s="0" t="n">
         <v>-2</v>
       </c>
     </row>
@@ -17401,10 +17401,90 @@
       <c r="A372" s="1" t="n">
         <v>46131</v>
       </c>
+      <c r="B372" s="0" t="n">
+        <v>-8</v>
+      </c>
+      <c r="C372" s="0" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="D372" s="0" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="E372" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F372" s="0" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="G372" s="0" t="n">
+        <v>-16</v>
+      </c>
+      <c r="H372" s="0" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="I372" s="0" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="J372" s="0" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="K372" s="0" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="L372" s="0" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="M372" s="0" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="N372" s="0" t="n">
+        <v>-11.3</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
         <v>46132</v>
+      </c>
+      <c r="B373" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="C373" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="D373" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="E373" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="F373" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="G373" t="n">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="H373" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="I373" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="J373" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="K373" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L373" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="M373" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="N373" t="n">
+        <v>-7.5</v>
       </c>
     </row>
     <row r="374">
@@ -34619,45 +34699,45 @@
       <c r="A371" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="B371" t="n">
+      <c r="B371" s="0" t="n">
         <v>13.3</v>
       </c>
-      <c r="C371" t="n">
+      <c r="C371" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="D371" t="n">
+      <c r="D371" s="0" t="n">
         <v>13.6</v>
       </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F371" t="n">
+      <c r="E371" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F371" s="0" t="n">
         <v>3.8</v>
       </c>
-      <c r="G371" t="n">
+      <c r="G371" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="H371" t="n">
+      <c r="H371" s="0" t="n">
         <v>16.5</v>
       </c>
-      <c r="I371" t="n">
+      <c r="I371" s="0" t="n">
         <v>11.4</v>
       </c>
-      <c r="J371" t="n">
+      <c r="J371" s="0" t="n">
         <v>11.6</v>
       </c>
-      <c r="K371" t="n">
+      <c r="K371" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="L371" t="n">
+      <c r="L371" s="0" t="n">
         <v>4.9</v>
       </c>
-      <c r="M371" t="n">
+      <c r="M371" s="0" t="n">
         <v>4.1</v>
       </c>
-      <c r="N371" t="n">
+      <c r="N371" s="0" t="n">
         <v>17.2</v>
       </c>
     </row>
@@ -34665,10 +34745,90 @@
       <c r="A372" s="1" t="n">
         <v>46131</v>
       </c>
+      <c r="B372" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C372" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="D372" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E372" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F372" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G372" s="0" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H372" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I372" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J372" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K372" s="0" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L372" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M372" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N372" s="0" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
         <v>46132</v>
+      </c>
+      <c r="B373" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="C373" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D373" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E373" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F373" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G373" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H373" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I373" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J373" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K373" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L373" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M373" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="N373" t="n">
+        <v>12.5</v>
       </c>
     </row>
     <row r="374">
@@ -41973,53 +42133,53 @@
       <c r="A129" s="1" t="n">
         <v>46130</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="0" t="n">
         <v>0.89</v>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
+      <c r="C129" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D129" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E129" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F129" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G129" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H129" s="0" t="n">
         <v>5.1</v>
       </c>
-      <c r="I129" t="n">
+      <c r="I129" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="J129" t="n">
+      <c r="J129" s="0" t="n">
         <v>-0.52</v>
       </c>
-      <c r="K129" t="n">
+      <c r="K129" s="0" t="n">
         <v>-4.66</v>
       </c>
-      <c r="L129" t="n">
+      <c r="L129" s="0" t="n">
         <v>-1.95</v>
       </c>
-      <c r="M129" t="n">
+      <c r="M129" s="0" t="n">
         <v>-4.45</v>
       </c>
-      <c r="N129" t="n">
+      <c r="N129" s="0" t="n">
         <v>8.539999999999999</v>
       </c>
     </row>
@@ -42027,10 +42187,108 @@
       <c r="A130" s="1" t="n">
         <v>46131</v>
       </c>
+      <c r="B130" s="0" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="C130" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D130" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E130" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F130" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G130" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H130" s="0" t="n">
+        <v>-2.29</v>
+      </c>
+      <c r="I130" s="0" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="J130" s="0" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="K130" s="0" t="n">
+        <v>-6.82</v>
+      </c>
+      <c r="L130" s="0" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M130" s="0" t="n">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="N130" s="0" t="n">
+        <v>-6.41</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
         <v>46132</v>
+      </c>
+      <c r="B131" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="I131" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L131" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M131" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="N131" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="132">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -17447,43 +17447,43 @@
       <c r="A373" s="1" t="n">
         <v>46132</v>
       </c>
-      <c r="B373" t="n">
+      <c r="B373" s="0" t="n">
         <v>-8.1</v>
       </c>
-      <c r="C373" t="n">
+      <c r="C373" s="0" t="n">
         <v>-5.6</v>
       </c>
-      <c r="D373" t="n">
+      <c r="D373" s="0" t="n">
         <v>-8.1</v>
       </c>
-      <c r="E373" t="n">
+      <c r="E373" s="0" t="n">
         <v>-5.9</v>
       </c>
-      <c r="F373" t="n">
+      <c r="F373" s="0" t="n">
         <v>-14.9</v>
       </c>
-      <c r="G373" t="n">
+      <c r="G373" s="0" t="n">
         <v>-9.699999999999999</v>
       </c>
-      <c r="H373" t="n">
+      <c r="H373" s="0" t="n">
         <v>-8.9</v>
       </c>
-      <c r="I373" t="n">
+      <c r="I373" s="0" t="n">
         <v>-5.9</v>
       </c>
-      <c r="J373" t="n">
+      <c r="J373" s="0" t="n">
         <v>-9.5</v>
       </c>
-      <c r="K373" t="n">
+      <c r="K373" s="0" t="n">
         <v>-9</v>
       </c>
-      <c r="L373" t="n">
+      <c r="L373" s="0" t="n">
         <v>-8.6</v>
       </c>
-      <c r="M373" t="n">
+      <c r="M373" s="0" t="n">
         <v>-8.5</v>
       </c>
-      <c r="N373" t="n">
+      <c r="N373" s="0" t="n">
         <v>-7.5</v>
       </c>
     </row>
@@ -17491,60 +17491,552 @@
       <c r="A374" s="1" t="n">
         <v>46133</v>
       </c>
+      <c r="B374" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="C374" s="0" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="D374" s="0" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="E374" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F374" s="0" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="G374" s="0" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H374" s="0" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="I374" s="0" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="J374" s="0" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="K374" s="0" t="n">
+        <v>-8.6</v>
+      </c>
+      <c r="L374" s="0" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="M374" s="0" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="N374" s="0" t="n">
+        <v>-1.1</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46134</v>
       </c>
+      <c r="B375" s="0" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="C375" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D375" s="0" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="E375" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F375" s="0" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="G375" s="0" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="H375" s="0" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I375" s="0" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J375" s="0" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="K375" s="0" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="L375" s="0" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="M375" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N375" s="0" t="n">
+        <v>2.8</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46135</v>
       </c>
+      <c r="B376" s="0" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="C376" s="0" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="D376" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="E376" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F376" s="0" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="G376" s="0" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="H376" s="0" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I376" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J376" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K376" s="0" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="L376" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="M376" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="N376" s="0" t="n">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
         <v>46136</v>
       </c>
+      <c r="B377" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="C377" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D377" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E377" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F377" s="0" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="G377" s="0" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H377" s="0" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I377" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J377" s="0" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="K377" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L377" s="0" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="M377" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="N377" s="0" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
         <v>46137</v>
       </c>
+      <c r="B378" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C378" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D378" s="0" t="n">
+        <v>-3</v>
+      </c>
+      <c r="E378" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F378" s="0" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="G378" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H378" s="0" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I378" s="0" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J378" s="0" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K378" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L378" s="0" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="M378" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N378" s="0" t="n">
+        <v>5.7</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
         <v>46138</v>
       </c>
+      <c r="B379" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C379" s="0" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="D379" s="0" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="E379" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F379" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G379" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H379" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I379" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J379" s="0" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="K379" s="0" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="L379" s="0" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="M379" s="0" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="N379" s="0" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
         <v>46139</v>
       </c>
+      <c r="B380" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C380" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D380" s="0" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="E380" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F380" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G380" s="0" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="H380" s="0" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="I380" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J380" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="K380" s="0" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="L380" s="0" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M380" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="N380" s="0" t="n">
+        <v>-2.6</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
         <v>46140</v>
       </c>
+      <c r="B381" s="0" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C381" s="0" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D381" s="0" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E381" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F381" s="0" t="n">
+        <v>-6.9</v>
+      </c>
+      <c r="G381" s="0" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="H381" s="0" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="I381" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J381" s="0" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="K381" s="0" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="L381" s="0" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="M381" s="0" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="N381" s="0" t="n">
+        <v>-2.7</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
         <v>46141</v>
       </c>
+      <c r="B382" s="0" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C382" s="0" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D382" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E382" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F382" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G382" s="0" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H382" s="0" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I382" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J382" s="0" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="K382" s="0" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L382" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M382" s="0" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="N382" s="0" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
         <v>46142</v>
       </c>
+      <c r="B383" s="0" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="C383" s="0" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="D383" s="0" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="E383" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F383" s="0" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="G383" s="0" t="n">
+        <v>-7.1</v>
+      </c>
+      <c r="H383" s="0" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I383" s="0" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="J383" s="0" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="K383" s="0" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="L383" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M383" s="0" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="N383" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
         <v>46143</v>
       </c>
+      <c r="B384" s="0" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="C384" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D384" s="0" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="E384" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F384" s="0" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G384" s="0" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H384" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I384" s="0" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="J384" s="0" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="K384" s="0" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="L384" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="M384" s="0" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="N384" s="0" t="n">
+        <v>-1.5</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
         <v>46144</v>
+      </c>
+      <c r="B385" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C385" t="n">
+        <v>3</v>
+      </c>
+      <c r="D385" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G385" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H385" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I385" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J385" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="K385" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L385" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="M385" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="N385" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="386">
@@ -34791,43 +35283,43 @@
       <c r="A373" s="1" t="n">
         <v>46132</v>
       </c>
-      <c r="B373" t="n">
+      <c r="B373" s="0" t="n">
         <v>13.9</v>
       </c>
-      <c r="C373" t="n">
+      <c r="C373" s="0" t="n">
         <v>13.8</v>
       </c>
-      <c r="D373" t="n">
+      <c r="D373" s="0" t="n">
         <v>12.4</v>
       </c>
-      <c r="E373" t="n">
+      <c r="E373" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="F373" t="n">
+      <c r="F373" s="0" t="n">
         <v>9.5</v>
       </c>
-      <c r="G373" t="n">
+      <c r="G373" s="0" t="n">
         <v>6.6</v>
       </c>
-      <c r="H373" t="n">
+      <c r="H373" s="0" t="n">
         <v>15.7</v>
       </c>
-      <c r="I373" t="n">
+      <c r="I373" s="0" t="n">
         <v>12.5</v>
       </c>
-      <c r="J373" t="n">
+      <c r="J373" s="0" t="n">
         <v>10.4</v>
       </c>
-      <c r="K373" t="n">
+      <c r="K373" s="0" t="n">
         <v>9.1</v>
       </c>
-      <c r="L373" t="n">
+      <c r="L373" s="0" t="n">
         <v>11.2</v>
       </c>
-      <c r="M373" t="n">
+      <c r="M373" s="0" t="n">
         <v>7.7</v>
       </c>
-      <c r="N373" t="n">
+      <c r="N373" s="0" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -34835,60 +35327,552 @@
       <c r="A374" s="1" t="n">
         <v>46133</v>
       </c>
+      <c r="B374" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="C374" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="D374" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E374" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F374" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G374" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H374" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I374" s="0" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J374" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K374" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L374" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M374" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N374" s="0" t="n">
+        <v>10.6</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
         <v>46134</v>
       </c>
+      <c r="B375" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C375" s="0" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="D375" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E375" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F375" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G375" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H375" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I375" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J375" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K375" s="0" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L375" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M375" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="N375" s="0" t="n">
+        <v>15.3</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
         <v>46135</v>
       </c>
+      <c r="B376" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="C376" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D376" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E376" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F376" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G376" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H376" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="I376" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J376" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="K376" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L376" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M376" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N376" s="0" t="n">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
         <v>46136</v>
       </c>
+      <c r="B377" s="0" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C377" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D377" s="0" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E377" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F377" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="G377" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H377" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I377" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="J377" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K377" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="L377" s="0" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M377" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="N377" s="0" t="n">
+        <v>17.3</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
         <v>46137</v>
       </c>
+      <c r="B378" s="0" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C378" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="D378" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="E378" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F378" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G378" s="0" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H378" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="I378" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J378" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K378" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L378" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="M378" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N378" s="0" t="n">
+        <v>13.7</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
         <v>46138</v>
       </c>
+      <c r="B379" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C379" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D379" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="E379" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F379" s="0" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G379" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H379" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I379" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J379" s="0" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="K379" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="L379" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M379" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N379" s="0" t="n">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
         <v>46139</v>
       </c>
+      <c r="B380" s="0" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="C380" s="0" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D380" s="0" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E380" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F380" s="0" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="G380" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H380" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I380" s="0" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J380" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K380" s="0" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="L380" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M380" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N380" s="0" t="n">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
         <v>46140</v>
       </c>
+      <c r="B381" s="0" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C381" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D381" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E381" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F381" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G381" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H381" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I381" s="0" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J381" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K381" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="L381" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M381" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N381" s="0" t="n">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
         <v>46141</v>
       </c>
+      <c r="B382" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="C382" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D382" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="E382" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F382" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G382" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H382" s="0" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I382" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J382" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K382" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L382" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M382" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N382" s="0" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
         <v>46142</v>
       </c>
+      <c r="B383" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="C383" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="D383" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E383" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F383" s="0" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G383" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H383" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I383" s="0" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="J383" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K383" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="L383" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M383" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N383" s="0" t="n">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
         <v>46143</v>
       </c>
+      <c r="B384" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="C384" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="D384" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E384" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F384" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G384" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H384" s="0" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="I384" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J384" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K384" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L384" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M384" s="0" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N384" s="0" t="n">
+        <v>11.5</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
         <v>46144</v>
+      </c>
+      <c r="B385" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="C385" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D385" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G385" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H385" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I385" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J385" t="n">
+        <v>21</v>
+      </c>
+      <c r="K385" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="L385" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M385" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="N385" t="n">
+        <v>14.5</v>
       </c>
     </row>
     <row r="386">
@@ -42241,53 +43225,53 @@
       <c r="A131" s="1" t="n">
         <v>46132</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="0" t="n">
         <v>3.68</v>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H131" t="n">
+      <c r="C131" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D131" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E131" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F131" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G131" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H131" s="0" t="n">
         <v>2.74</v>
       </c>
-      <c r="I131" t="n">
+      <c r="I131" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J131" t="n">
+      <c r="J131" s="0" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K131" t="n">
+      <c r="K131" s="0" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L131" t="n">
+      <c r="L131" s="0" t="n">
         <v>1.29</v>
       </c>
-      <c r="M131" t="n">
+      <c r="M131" s="0" t="n">
         <v>-0.24</v>
       </c>
-      <c r="N131" t="n">
+      <c r="N131" s="0" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -42295,60 +43279,648 @@
       <c r="A132" s="1" t="n">
         <v>46133</v>
       </c>
+      <c r="B132" s="0" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="C132" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D132" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E132" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F132" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G132" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H132" s="0" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="I132" s="0" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="J132" s="0" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="K132" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L132" s="0" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M132" s="0" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N132" s="0" t="n">
+        <v>4.98</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
         <v>46134</v>
       </c>
+      <c r="B133" s="0" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="C133" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D133" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E133" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F133" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G133" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H133" s="0" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="I133" s="0" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="J133" s="0" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="K133" s="0" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L133" s="0" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M133" s="0" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="N133" s="0" t="n">
+        <v>8.59</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
         <v>46135</v>
       </c>
+      <c r="B134" s="0" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="C134" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D134" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E134" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F134" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G134" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H134" s="0" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="I134" s="0" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="J134" s="0" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="K134" s="0" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="L134" s="0" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="M134" s="0" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N134" s="0" t="n">
+        <v>6.89</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
         <v>46136</v>
       </c>
+      <c r="B135" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="C135" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D135" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E135" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F135" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G135" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H135" s="0" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="I135" s="0" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="J135" s="0" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K135" s="0" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="L135" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M135" s="0" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="N135" s="0" t="n">
+        <v>7.68</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
         <v>46137</v>
       </c>
+      <c r="B136" s="0" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="C136" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D136" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E136" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F136" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G136" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H136" s="0" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="I136" s="0" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J136" s="0" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="K136" s="0" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="L136" s="0" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="M136" s="0" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="N136" s="0" t="n">
+        <v>9.949999999999999</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
         <v>46138</v>
       </c>
+      <c r="B137" s="0" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="C137" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D137" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E137" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F137" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G137" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H137" s="0" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="I137" s="0" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="J137" s="0" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="K137" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L137" s="0" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="M137" s="0" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="N137" s="0" t="n">
+        <v>4.45</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
         <v>46139</v>
       </c>
+      <c r="B138" s="0" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="C138" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D138" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E138" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F138" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G138" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H138" s="0" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="I138" s="0" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="J138" s="0" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="K138" s="0" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="L138" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M138" s="0" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="N138" s="0" t="n">
+        <v>4.09</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
         <v>46140</v>
       </c>
+      <c r="B139" s="0" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="C139" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D139" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E139" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F139" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G139" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H139" s="0" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="I139" s="0" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="J139" s="0" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="K139" s="0" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="L139" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M139" s="0" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="N139" s="0" t="n">
+        <v>7.53</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
         <v>46141</v>
       </c>
+      <c r="B140" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C140" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D140" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E140" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F140" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G140" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H140" s="0" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="I140" s="0" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="J140" s="0" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="K140" s="0" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L140" s="0" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="M140" s="0" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N140" s="0" t="n">
+        <v>11.34</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
         <v>46142</v>
       </c>
+      <c r="B141" s="0" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="C141" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D141" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E141" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F141" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G141" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H141" s="0" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="I141" s="0" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="J141" s="0" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K141" s="0" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L141" s="0" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M141" s="0" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N141" s="0" t="n">
+        <v>5.76</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
         <v>46143</v>
       </c>
+      <c r="B142" s="0" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="C142" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D142" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E142" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F142" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G142" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H142" s="0" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="I142" s="0" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="J142" s="0" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="K142" s="0" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L142" s="0" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="M142" s="0" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="N142" s="0" t="n">
+        <v>6.19</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
         <v>46144</v>
+      </c>
+      <c r="B143" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="I143" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="K143" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="L143" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="M143" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="N143" t="n">
+        <v>7.98</v>
       </c>
     </row>
     <row r="144">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -17997,51 +17997,92 @@
       <c r="A385" s="1" t="n">
         <v>46144</v>
       </c>
-      <c r="B385" t="n">
+      <c r="B385" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="C385" t="n">
+      <c r="C385" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D385" t="n">
+      <c r="D385" s="0" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F385" t="n">
+      <c r="E385" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F385" s="0" t="n">
         <v>-5</v>
       </c>
-      <c r="G385" t="n">
+      <c r="G385" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="H385" t="n">
+      <c r="H385" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="I385" t="n">
+      <c r="I385" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="J385" t="n">
+      <c r="J385" s="0" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K385" t="n">
+      <c r="K385" s="0" t="n">
         <v>-5.1</v>
       </c>
-      <c r="L385" t="n">
+      <c r="L385" s="0" t="n">
         <v>-3.1</v>
       </c>
-      <c r="M385" t="n">
+      <c r="M385" s="0" t="n">
         <v>-4.7</v>
       </c>
-      <c r="N385" t="n">
+      <c r="N385" s="0" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
         <v>46145</v>
+      </c>
+      <c r="B386" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C386" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="G386" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H386" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I386" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J386" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="K386" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="L386" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="M386" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="N386" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="387">
@@ -35833,51 +35874,92 @@
       <c r="A385" s="1" t="n">
         <v>46144</v>
       </c>
-      <c r="B385" t="n">
+      <c r="B385" s="0" t="n">
         <v>24.7</v>
       </c>
-      <c r="C385" t="n">
+      <c r="C385" s="0" t="n">
         <v>24.5</v>
       </c>
-      <c r="D385" t="n">
+      <c r="D385" s="0" t="n">
         <v>22.9</v>
       </c>
-      <c r="E385" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F385" t="n">
+      <c r="E385" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F385" s="0" t="n">
         <v>14.4</v>
       </c>
-      <c r="G385" t="n">
+      <c r="G385" s="0" t="n">
         <v>18.1</v>
       </c>
-      <c r="H385" t="n">
+      <c r="H385" s="0" t="n">
         <v>18.6</v>
       </c>
-      <c r="I385" t="n">
+      <c r="I385" s="0" t="n">
         <v>22.3</v>
       </c>
-      <c r="J385" t="n">
+      <c r="J385" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="K385" t="n">
+      <c r="K385" s="0" t="n">
         <v>15.9</v>
       </c>
-      <c r="L385" t="n">
+      <c r="L385" s="0" t="n">
         <v>18.8</v>
       </c>
-      <c r="M385" t="n">
+      <c r="M385" s="0" t="n">
         <v>17.7</v>
       </c>
-      <c r="N385" t="n">
+      <c r="N385" s="0" t="n">
         <v>14.5</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
         <v>46145</v>
+      </c>
+      <c r="B386" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="C386" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D386" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G386" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H386" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I386" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="J386" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="K386" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="L386" t="n">
+        <v>21</v>
+      </c>
+      <c r="M386" t="n">
+        <v>21</v>
+      </c>
+      <c r="N386" t="n">
+        <v>21.1</v>
       </c>
     </row>
     <row r="387">
@@ -43873,59 +43955,108 @@
       <c r="A143" s="1" t="n">
         <v>46144</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" s="0" t="n">
         <v>13.85</v>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
+      <c r="C143" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D143" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E143" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F143" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G143" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H143" s="0" t="n">
         <v>9.59</v>
       </c>
-      <c r="I143" t="n">
+      <c r="I143" s="0" t="n">
         <v>13.1</v>
       </c>
-      <c r="J143" t="n">
+      <c r="J143" s="0" t="n">
         <v>10.36</v>
       </c>
-      <c r="K143" t="n">
+      <c r="K143" s="0" t="n">
         <v>6.58</v>
       </c>
-      <c r="L143" t="n">
+      <c r="L143" s="0" t="n">
         <v>8.34</v>
       </c>
-      <c r="M143" t="n">
+      <c r="M143" s="0" t="n">
         <v>6.75</v>
       </c>
-      <c r="N143" t="n">
+      <c r="N143" s="0" t="n">
         <v>7.98</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
         <v>46145</v>
+      </c>
+      <c r="B144" t="n">
+        <v>15.64</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="I144" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="J144" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="K144" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="L144" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="M144" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="N144" t="n">
+        <v>11.31</v>
       </c>
     </row>
     <row r="145">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -18043,45 +18043,45 @@
       <c r="A386" s="1" t="n">
         <v>46145</v>
       </c>
-      <c r="B386" t="n">
+      <c r="B386" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="C386" t="n">
+      <c r="C386" s="0" t="n">
         <v>4.7</v>
       </c>
-      <c r="D386" t="n">
+      <c r="D386" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F386" t="n">
+      <c r="E386" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F386" s="0" t="n">
         <v>-4.4</v>
       </c>
-      <c r="G386" t="n">
+      <c r="G386" s="0" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H386" t="n">
+      <c r="H386" s="0" t="n">
         <v>-1.6</v>
       </c>
-      <c r="I386" t="n">
+      <c r="I386" s="0" t="n">
         <v>5.5</v>
       </c>
-      <c r="J386" t="n">
+      <c r="J386" s="0" t="n">
         <v>-1.8</v>
       </c>
-      <c r="K386" t="n">
+      <c r="K386" s="0" t="n">
         <v>-3.2</v>
       </c>
-      <c r="L386" t="n">
+      <c r="L386" s="0" t="n">
         <v>-1.3</v>
       </c>
-      <c r="M386" t="n">
+      <c r="M386" s="0" t="n">
         <v>-2.5</v>
       </c>
-      <c r="N386" t="n">
+      <c r="N386" s="0" t="n">
         <v>2.1</v>
       </c>
     </row>
@@ -18089,20 +18089,184 @@
       <c r="A387" s="1" t="n">
         <v>46146</v>
       </c>
+      <c r="B387" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C387" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="D387" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E387" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F387" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="G387" s="0" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H387" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I387" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J387" s="0" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K387" s="0" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L387" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M387" s="0" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N387" s="0" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
         <v>46147</v>
       </c>
+      <c r="B388" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C388" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D388" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E388" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F388" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G388" s="0" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="H388" s="0" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I388" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J388" s="0" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K388" s="0" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="L388" s="0" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M388" s="0" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="N388" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
         <v>46148</v>
       </c>
+      <c r="B389" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C389" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D389" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E389" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F389" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G389" s="0" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H389" s="0" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I389" s="0" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J389" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K389" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="L389" s="0" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="M389" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N389" s="0" t="n">
+        <v>-2.3</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
         <v>46149</v>
+      </c>
+      <c r="B390" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C390" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D390" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="G390" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H390" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="I390" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J390" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K390" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L390" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="M390" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="N390" t="n">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="391">
@@ -35920,45 +36084,45 @@
       <c r="A386" s="1" t="n">
         <v>46145</v>
       </c>
-      <c r="B386" t="n">
+      <c r="B386" s="0" t="n">
         <v>27.3</v>
       </c>
-      <c r="C386" t="n">
+      <c r="C386" s="0" t="n">
         <v>25.4</v>
       </c>
-      <c r="D386" t="n">
+      <c r="D386" s="0" t="n">
         <v>24.8</v>
       </c>
-      <c r="E386" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F386" t="n">
+      <c r="E386" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F386" s="0" t="n">
         <v>17.5</v>
       </c>
-      <c r="G386" t="n">
+      <c r="G386" s="0" t="n">
         <v>20.7</v>
       </c>
-      <c r="H386" t="n">
+      <c r="H386" s="0" t="n">
         <v>24.8</v>
       </c>
-      <c r="I386" t="n">
+      <c r="I386" s="0" t="n">
         <v>26.8</v>
       </c>
-      <c r="J386" t="n">
+      <c r="J386" s="0" t="n">
         <v>23.3</v>
       </c>
-      <c r="K386" t="n">
+      <c r="K386" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="L386" t="n">
+      <c r="L386" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="M386" t="n">
+      <c r="M386" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="N386" t="n">
+      <c r="N386" s="0" t="n">
         <v>21.1</v>
       </c>
     </row>
@@ -35966,20 +36130,184 @@
       <c r="A387" s="1" t="n">
         <v>46146</v>
       </c>
+      <c r="B387" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="C387" s="0" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D387" s="0" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E387" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F387" s="0" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G387" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H387" s="0" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I387" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J387" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K387" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="L387" s="0" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M387" s="0" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N387" s="0" t="n">
+        <v>19.9</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
         <v>46147</v>
       </c>
+      <c r="B388" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C388" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D388" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="E388" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F388" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G388" s="0" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H388" s="0" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I388" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J388" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K388" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L388" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M388" s="0" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N388" s="0" t="n">
+        <v>13.5</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
         <v>46148</v>
       </c>
+      <c r="B389" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="C389" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="D389" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E389" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F389" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G389" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H389" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I389" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="J389" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K389" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="L389" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M389" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="N389" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
         <v>46149</v>
+      </c>
+      <c r="B390" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="C390" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D390" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>19</v>
+      </c>
+      <c r="G390" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="H390" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I390" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J390" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K390" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L390" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="M390" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N390" t="n">
+        <v>17.4</v>
       </c>
     </row>
     <row r="391">
@@ -44009,53 +44337,53 @@
       <c r="A144" s="1" t="n">
         <v>46145</v>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" s="0" t="n">
         <v>15.64</v>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
+      <c r="C144" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D144" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E144" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F144" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G144" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H144" s="0" t="n">
         <v>11.88</v>
       </c>
-      <c r="I144" t="n">
+      <c r="I144" s="0" t="n">
         <v>16.65</v>
       </c>
-      <c r="J144" t="n">
+      <c r="J144" s="0" t="n">
         <v>11.71</v>
       </c>
-      <c r="K144" t="n">
+      <c r="K144" s="0" t="n">
         <v>9.44</v>
       </c>
-      <c r="L144" t="n">
+      <c r="L144" s="0" t="n">
         <v>10.75</v>
       </c>
-      <c r="M144" t="n">
+      <c r="M144" s="0" t="n">
         <v>9.960000000000001</v>
       </c>
-      <c r="N144" t="n">
+      <c r="N144" s="0" t="n">
         <v>11.31</v>
       </c>
     </row>
@@ -44063,20 +44391,212 @@
       <c r="A145" s="1" t="n">
         <v>46146</v>
       </c>
+      <c r="B145" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C145" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D145" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E145" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F145" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G145" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H145" s="0" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="I145" s="0" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="J145" s="0" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="K145" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L145" s="0" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="M145" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N145" s="0" t="n">
+        <v>12.42</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
         <v>46147</v>
       </c>
+      <c r="B146" s="0" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="C146" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D146" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E146" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F146" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G146" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H146" s="0" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="I146" s="0" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="J146" s="0" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="K146" s="0" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="L146" s="0" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M146" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N146" s="0" t="n">
+        <v>7.65</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
         <v>46148</v>
       </c>
+      <c r="B147" s="0" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="C147" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D147" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E147" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F147" s="0" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="G147" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H147" s="0" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="I147" s="0" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="J147" s="0" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="K147" s="0" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="L147" s="0" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="M147" s="0" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="N147" s="0" t="n">
+        <v>3.26</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
         <v>46149</v>
+      </c>
+      <c r="B148" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="I148" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="J148" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="K148" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="L148" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="M148" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="N148" t="n">
+        <v>8.15</v>
       </c>
     </row>
     <row r="149">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -18227,51 +18227,92 @@
       <c r="A390" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="B390" t="n">
+      <c r="B390" s="0" t="n">
         <v>6.3</v>
       </c>
-      <c r="C390" t="n">
+      <c r="C390" s="0" t="n">
         <v>3.7</v>
       </c>
-      <c r="D390" t="n">
+      <c r="D390" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F390" t="n">
+      <c r="E390" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F390" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G390" t="n">
+      <c r="G390" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H390" t="n">
+      <c r="H390" s="0" t="n">
         <v>-4.2</v>
       </c>
-      <c r="I390" t="n">
+      <c r="I390" s="0" t="n">
         <v>5.3</v>
       </c>
-      <c r="J390" t="n">
+      <c r="J390" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="K390" t="n">
+      <c r="K390" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="L390" t="n">
+      <c r="L390" s="0" t="n">
         <v>-1.6</v>
       </c>
-      <c r="M390" t="n">
+      <c r="M390" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="N390" t="n">
+      <c r="N390" s="0" t="n">
         <v>-1.5</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
         <v>46150</v>
+      </c>
+      <c r="B391" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C391" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D391" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G391" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H391" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I391" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J391" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K391" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="L391" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M391" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N391" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="392">
@@ -36268,51 +36309,92 @@
       <c r="A390" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="B390" t="n">
+      <c r="B390" s="0" t="n">
         <v>24.2</v>
       </c>
-      <c r="C390" t="n">
+      <c r="C390" s="0" t="n">
         <v>22.5</v>
       </c>
-      <c r="D390" t="n">
+      <c r="D390" s="0" t="n">
         <v>23.2</v>
       </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F390" t="n">
+      <c r="E390" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F390" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="G390" t="n">
+      <c r="G390" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="H390" t="n">
+      <c r="H390" s="0" t="n">
         <v>21.5</v>
       </c>
-      <c r="I390" t="n">
+      <c r="I390" s="0" t="n">
         <v>23.9</v>
       </c>
-      <c r="J390" t="n">
+      <c r="J390" s="0" t="n">
         <v>22.3</v>
       </c>
-      <c r="K390" t="n">
+      <c r="K390" s="0" t="n">
         <v>18.6</v>
       </c>
-      <c r="L390" t="n">
+      <c r="L390" s="0" t="n">
         <v>21.5</v>
       </c>
-      <c r="M390" t="n">
+      <c r="M390" s="0" t="n">
         <v>18.5</v>
       </c>
-      <c r="N390" t="n">
+      <c r="N390" s="0" t="n">
         <v>17.4</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
         <v>46150</v>
+      </c>
+      <c r="B391" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C391" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="D391" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G391" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="H391" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I391" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J391" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="K391" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="L391" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M391" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N391" t="n">
+        <v>20.4</v>
       </c>
     </row>
     <row r="392">
@@ -44551,57 +44633,104 @@
       <c r="A148" s="1" t="n">
         <v>46149</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" s="0" t="n">
         <v>15.07</v>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
+      <c r="C148" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D148" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E148" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F148" s="0" t="n">
         <v>7.46</v>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
+      <c r="G148" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H148" s="0" t="n">
         <v>9.25</v>
       </c>
-      <c r="I148" t="n">
+      <c r="I148" s="0" t="n">
         <v>14.59</v>
       </c>
-      <c r="J148" t="n">
+      <c r="J148" s="0" t="n">
         <v>12.02</v>
       </c>
-      <c r="K148" t="n">
+      <c r="K148" s="0" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="L148" t="n">
+      <c r="L148" s="0" t="n">
         <v>10.56</v>
       </c>
-      <c r="M148" t="n">
+      <c r="M148" s="0" t="n">
         <v>8.34</v>
       </c>
-      <c r="N148" t="n">
+      <c r="N148" s="0" t="n">
         <v>8.15</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
         <v>46150</v>
+      </c>
+      <c r="B149" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="I149" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="J149" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="K149" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="L149" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="M149" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="N149" t="n">
+        <v>11.67</v>
       </c>
     </row>
     <row r="150">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -18273,51 +18273,92 @@
       <c r="A391" s="1" t="n">
         <v>46150</v>
       </c>
-      <c r="B391" t="n">
+      <c r="B391" s="0" t="n">
         <v>4.4</v>
       </c>
-      <c r="C391" t="n">
+      <c r="C391" s="0" t="n">
         <v>3.4</v>
       </c>
-      <c r="D391" t="n">
+      <c r="D391" s="0" t="n">
         <v>5.7</v>
       </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F391" t="n">
+      <c r="E391" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F391" s="0" t="n">
         <v>1.7</v>
       </c>
-      <c r="G391" t="n">
+      <c r="G391" s="0" t="n">
         <v>1.8</v>
       </c>
-      <c r="H391" t="n">
+      <c r="H391" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="I391" t="n">
+      <c r="I391" s="0" t="n">
         <v>4.3</v>
       </c>
-      <c r="J391" t="n">
+      <c r="J391" s="0" t="n">
         <v>3.2</v>
       </c>
-      <c r="K391" t="n">
+      <c r="K391" s="0" t="n">
         <v>-2.1</v>
       </c>
-      <c r="L391" t="n">
+      <c r="L391" s="0" t="n">
         <v>3.8</v>
       </c>
-      <c r="M391" t="n">
+      <c r="M391" s="0" t="n">
         <v>3.1</v>
       </c>
-      <c r="N391" t="n">
+      <c r="N391" s="0" t="n">
         <v>4.9</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
         <v>46151</v>
+      </c>
+      <c r="B392" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="C392" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D392" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="G392" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H392" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I392" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J392" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K392" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L392" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M392" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="N392" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="393">
@@ -36355,51 +36396,92 @@
       <c r="A391" s="1" t="n">
         <v>46150</v>
       </c>
-      <c r="B391" t="n">
+      <c r="B391" s="0" t="n">
         <v>23.9</v>
       </c>
-      <c r="C391" t="n">
+      <c r="C391" s="0" t="n">
         <v>22.3</v>
       </c>
-      <c r="D391" t="n">
+      <c r="D391" s="0" t="n">
         <v>20.1</v>
       </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F391" t="n">
+      <c r="E391" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F391" s="0" t="n">
         <v>16.4</v>
       </c>
-      <c r="G391" t="n">
+      <c r="G391" s="0" t="n">
         <v>14.9</v>
       </c>
-      <c r="H391" t="n">
+      <c r="H391" s="0" t="n">
         <v>18.3</v>
       </c>
-      <c r="I391" t="n">
+      <c r="I391" s="0" t="n">
         <v>22.3</v>
       </c>
-      <c r="J391" t="n">
+      <c r="J391" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="K391" t="n">
+      <c r="K391" s="0" t="n">
         <v>16.3</v>
       </c>
-      <c r="L391" t="n">
+      <c r="L391" s="0" t="n">
         <v>19.4</v>
       </c>
-      <c r="M391" t="n">
+      <c r="M391" s="0" t="n">
         <v>15.2</v>
       </c>
-      <c r="N391" t="n">
+      <c r="N391" s="0" t="n">
         <v>20.4</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
         <v>46151</v>
+      </c>
+      <c r="B392" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C392" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="D392" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G392" t="n">
+        <v>15</v>
+      </c>
+      <c r="H392" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="I392" t="n">
+        <v>25</v>
+      </c>
+      <c r="J392" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K392" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="L392" t="n">
+        <v>20</v>
+      </c>
+      <c r="M392" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N392" t="n">
+        <v>17.4</v>
       </c>
     </row>
     <row r="393">
@@ -44685,57 +44767,104 @@
       <c r="A149" s="1" t="n">
         <v>46150</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" s="0" t="n">
         <v>15.45</v>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
+      <c r="C149" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D149" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E149" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F149" s="0" t="n">
         <v>10.55</v>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
+      <c r="G149" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H149" s="0" t="n">
         <v>10.34</v>
       </c>
-      <c r="I149" t="n">
+      <c r="I149" s="0" t="n">
         <v>14.37</v>
       </c>
-      <c r="J149" t="n">
+      <c r="J149" s="0" t="n">
         <v>12.49</v>
       </c>
-      <c r="K149" t="n">
+      <c r="K149" s="0" t="n">
         <v>9.460000000000001</v>
       </c>
-      <c r="L149" t="n">
+      <c r="L149" s="0" t="n">
         <v>12.49</v>
       </c>
-      <c r="M149" t="n">
+      <c r="M149" s="0" t="n">
         <v>9.67</v>
       </c>
-      <c r="N149" t="n">
+      <c r="N149" s="0" t="n">
         <v>11.67</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
         <v>46151</v>
+      </c>
+      <c r="B150" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="I150" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="J150" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="K150" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="L150" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="M150" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="N150" t="n">
+        <v>10.85</v>
       </c>
     </row>
     <row r="151">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -18319,45 +18319,45 @@
       <c r="A392" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="B392" t="n">
+      <c r="B392" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="C392" t="n">
+      <c r="C392" s="0" t="n">
         <v>11.5</v>
       </c>
-      <c r="D392" t="n">
+      <c r="D392" s="0" t="n">
         <v>6.4</v>
       </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F392" t="n">
+      <c r="E392" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F392" s="0" t="n">
         <v>-1.9</v>
       </c>
-      <c r="G392" t="n">
+      <c r="G392" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="H392" t="n">
+      <c r="H392" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="I392" t="n">
+      <c r="I392" s="0" t="n">
         <v>10.1</v>
       </c>
-      <c r="J392" t="n">
+      <c r="J392" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="K392" t="n">
+      <c r="K392" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="L392" t="n">
+      <c r="L392" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="M392" t="n">
+      <c r="M392" s="0" t="n">
         <v>-0.4</v>
       </c>
-      <c r="N392" t="n">
+      <c r="N392" s="0" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -18365,10 +18365,92 @@
       <c r="A393" s="1" t="n">
         <v>46152</v>
       </c>
+      <c r="B393" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C393" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D393" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E393" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F393" s="0" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G393" s="0" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="H393" s="0" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I393" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J393" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K393" s="0" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="L393" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M393" s="0" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="N393" s="0" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
         <v>46153</v>
+      </c>
+      <c r="B394" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C394" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D394" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G394" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H394" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I394" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J394" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K394" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L394" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M394" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N394" t="n">
+        <v>12.8</v>
       </c>
     </row>
     <row r="395">
@@ -36442,45 +36524,45 @@
       <c r="A392" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="B392" t="n">
+      <c r="B392" s="0" t="n">
         <v>25.7</v>
       </c>
-      <c r="C392" t="n">
+      <c r="C392" s="0" t="n">
         <v>23.6</v>
       </c>
-      <c r="D392" t="n">
+      <c r="D392" s="0" t="n">
         <v>21.8</v>
       </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F392" t="n">
+      <c r="E392" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F392" s="0" t="n">
         <v>18.3</v>
       </c>
-      <c r="G392" t="n">
+      <c r="G392" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="H392" t="n">
+      <c r="H392" s="0" t="n">
         <v>21.6</v>
       </c>
-      <c r="I392" t="n">
+      <c r="I392" s="0" t="n">
         <v>25</v>
       </c>
-      <c r="J392" t="n">
+      <c r="J392" s="0" t="n">
         <v>20.3</v>
       </c>
-      <c r="K392" t="n">
+      <c r="K392" s="0" t="n">
         <v>16.9</v>
       </c>
-      <c r="L392" t="n">
+      <c r="L392" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="M392" t="n">
+      <c r="M392" s="0" t="n">
         <v>14.6</v>
       </c>
-      <c r="N392" t="n">
+      <c r="N392" s="0" t="n">
         <v>17.4</v>
       </c>
     </row>
@@ -36488,10 +36570,92 @@
       <c r="A393" s="1" t="n">
         <v>46152</v>
       </c>
+      <c r="B393" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="C393" s="0" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D393" s="0" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E393" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F393" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G393" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H393" s="0" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="I393" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="J393" s="0" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="K393" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="L393" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="M393" s="0" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="N393" s="0" t="n">
+        <v>21.1</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
         <v>46153</v>
+      </c>
+      <c r="B394" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="C394" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="D394" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G394" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H394" t="n">
+        <v>27</v>
+      </c>
+      <c r="I394" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J394" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="K394" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="L394" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M394" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="N394" t="n">
+        <v>28.1</v>
       </c>
     </row>
     <row r="395">
@@ -44819,51 +44983,51 @@
       <c r="A150" s="1" t="n">
         <v>46151</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" s="0" t="n">
         <v>18.1</v>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
+      <c r="C150" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D150" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E150" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F150" s="0" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H150" t="n">
+      <c r="G150" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H150" s="0" t="n">
         <v>11.88</v>
       </c>
-      <c r="I150" t="n">
+      <c r="I150" s="0" t="n">
         <v>17.91</v>
       </c>
-      <c r="J150" t="n">
+      <c r="J150" s="0" t="n">
         <v>13.27</v>
       </c>
-      <c r="K150" t="n">
+      <c r="K150" s="0" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="L150" t="n">
+      <c r="L150" s="0" t="n">
         <v>11.34</v>
       </c>
-      <c r="M150" t="n">
+      <c r="M150" s="0" t="n">
         <v>6.79</v>
       </c>
-      <c r="N150" t="n">
+      <c r="N150" s="0" t="n">
         <v>10.85</v>
       </c>
     </row>
@@ -44871,10 +45035,104 @@
       <c r="A151" s="1" t="n">
         <v>46152</v>
       </c>
+      <c r="B151" s="0" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="C151" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D151" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E151" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F151" s="0" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="G151" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H151" s="0" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="I151" s="0" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="J151" s="0" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="K151" s="0" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="L151" s="0" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M151" s="0" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="N151" s="0" t="n">
+        <v>13.66</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
         <v>46153</v>
+      </c>
+      <c r="B152" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="I152" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="J152" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="K152" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L152" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="M152" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="N152" t="n">
+        <v>20.34</v>
       </c>
     </row>
     <row r="153">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -18411,45 +18411,45 @@
       <c r="A394" s="1" t="n">
         <v>46153</v>
       </c>
-      <c r="B394" t="n">
+      <c r="B394" s="0" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="C394" t="n">
+      <c r="C394" s="0" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="D394" t="n">
+      <c r="D394" s="0" t="n">
         <v>12.6</v>
       </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F394" t="n">
+      <c r="E394" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F394" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="G394" t="n">
+      <c r="G394" s="0" t="n">
         <v>7.1</v>
       </c>
-      <c r="H394" t="n">
+      <c r="H394" s="0" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="I394" t="n">
+      <c r="I394" s="0" t="n">
         <v>8.9</v>
       </c>
-      <c r="J394" t="n">
+      <c r="J394" s="0" t="n">
         <v>11.2</v>
       </c>
-      <c r="K394" t="n">
+      <c r="K394" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="L394" t="n">
+      <c r="L394" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="M394" t="n">
+      <c r="M394" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="N394" t="n">
+      <c r="N394" s="0" t="n">
         <v>12.8</v>
       </c>
     </row>
@@ -18457,35 +18457,324 @@
       <c r="A395" s="1" t="n">
         <v>46154</v>
       </c>
+      <c r="B395" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C395" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D395" s="0" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E395" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F395" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G395" s="0" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H395" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I395" s="0" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J395" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K395" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L395" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M395" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N395" s="0" t="n">
+        <v>12.4</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
         <v>46155</v>
       </c>
+      <c r="B396" s="0" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="C396" s="0" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="D396" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="E396" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F396" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G396" s="0" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="H396" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I396" s="0" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J396" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K396" s="0" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="L396" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M396" s="0" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="N396" s="0" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
         <v>46156</v>
       </c>
+      <c r="B397" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C397" s="0" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="D397" s="0" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="E397" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F397" s="0" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="G397" s="0" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="H397" s="0" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="I397" s="0" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="J397" s="0" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="K397" s="0" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="L397" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="M397" s="0" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="N397" s="0" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
         <v>46157</v>
       </c>
+      <c r="B398" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C398" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D398" s="0" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E398" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F398" s="0" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="G398" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H398" s="0" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I398" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J398" s="0" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K398" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L398" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M398" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N398" s="0" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
         <v>46158</v>
       </c>
+      <c r="B399" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C399" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D399" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E399" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F399" s="0" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G399" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H399" s="0" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I399" s="0" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J399" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="K399" s="0" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="L399" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M399" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="N399" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
         <v>46159</v>
       </c>
+      <c r="B400" s="0" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C400" s="0" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D400" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E400" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F400" s="0" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="G400" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H400" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I400" s="0" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J400" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K400" s="0" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="L400" s="0" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M400" s="0" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N400" s="0" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
         <v>46160</v>
+      </c>
+      <c r="B401" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C401" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="G401" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H401" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="I401" t="n">
+        <v>1</v>
+      </c>
+      <c r="J401" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K401" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L401" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="M401" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N401" t="n">
+        <v>0.7</v>
       </c>
     </row>
     <row r="402">
@@ -36616,45 +36905,45 @@
       <c r="A394" s="1" t="n">
         <v>46153</v>
       </c>
-      <c r="B394" t="n">
+      <c r="B394" s="0" t="n">
         <v>26.1</v>
       </c>
-      <c r="C394" t="n">
+      <c r="C394" s="0" t="n">
         <v>25.5</v>
       </c>
-      <c r="D394" t="n">
+      <c r="D394" s="0" t="n">
         <v>23.7</v>
       </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F394" t="n">
+      <c r="E394" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F394" s="0" t="n">
         <v>21.5</v>
       </c>
-      <c r="G394" t="n">
+      <c r="G394" s="0" t="n">
         <v>17.5</v>
       </c>
-      <c r="H394" t="n">
+      <c r="H394" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="I394" t="n">
+      <c r="I394" s="0" t="n">
         <v>23.1</v>
       </c>
-      <c r="J394" t="n">
+      <c r="J394" s="0" t="n">
         <v>21.6</v>
       </c>
-      <c r="K394" t="n">
+      <c r="K394" s="0" t="n">
         <v>18.1</v>
       </c>
-      <c r="L394" t="n">
+      <c r="L394" s="0" t="n">
         <v>20.7</v>
       </c>
-      <c r="M394" t="n">
+      <c r="M394" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="N394" t="n">
+      <c r="N394" s="0" t="n">
         <v>28.1</v>
       </c>
     </row>
@@ -36662,35 +36951,324 @@
       <c r="A395" s="1" t="n">
         <v>46154</v>
       </c>
+      <c r="B395" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C395" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="D395" s="0" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E395" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F395" s="0" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G395" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H395" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I395" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="J395" s="0" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K395" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="L395" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="M395" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="N395" s="0" t="n">
+        <v>30.9</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
         <v>46155</v>
       </c>
+      <c r="B396" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C396" s="0" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D396" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E396" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F396" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="G396" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H396" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I396" s="0" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J396" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K396" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L396" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M396" s="0" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="N396" s="0" t="n">
+        <v>21.2</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
         <v>46156</v>
       </c>
+      <c r="B397" s="0" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="C397" s="0" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D397" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="E397" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F397" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G397" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H397" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I397" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J397" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="K397" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L397" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M397" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="N397" s="0" t="n">
+        <v>11.3</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
         <v>46157</v>
       </c>
+      <c r="B398" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C398" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D398" s="0" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="E398" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F398" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G398" s="0" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H398" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I398" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J398" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K398" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L398" s="0" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M398" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N398" s="0" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
         <v>46158</v>
       </c>
+      <c r="B399" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="C399" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D399" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E399" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F399" s="0" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G399" s="0" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H399" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I399" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J399" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K399" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="L399" s="0" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M399" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N399" s="0" t="n">
+        <v>17.4</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
         <v>46159</v>
       </c>
+      <c r="B400" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="C400" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="D400" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E400" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F400" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G400" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H400" s="0" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I400" s="0" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J400" s="0" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K400" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L400" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M400" s="0" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N400" s="0" t="n">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
         <v>46160</v>
+      </c>
+      <c r="B401" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C401" t="n">
+        <v>12</v>
+      </c>
+      <c r="D401" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>9</v>
+      </c>
+      <c r="G401" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H401" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I401" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="J401" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K401" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L401" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M401" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N401" t="n">
+        <v>15.2</v>
       </c>
     </row>
     <row r="402">
@@ -45087,51 +45665,51 @@
       <c r="A152" s="1" t="n">
         <v>46153</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" s="0" t="n">
         <v>19.53</v>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
+      <c r="C152" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D152" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E152" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F152" s="0" t="n">
         <v>15.06</v>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
+      <c r="G152" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H152" s="0" t="n">
         <v>17.49</v>
       </c>
-      <c r="I152" t="n">
+      <c r="I152" s="0" t="n">
         <v>18.73</v>
       </c>
-      <c r="J152" t="n">
+      <c r="J152" s="0" t="n">
         <v>17.05</v>
       </c>
-      <c r="K152" t="n">
+      <c r="K152" s="0" t="n">
         <v>13.2</v>
       </c>
-      <c r="L152" t="n">
+      <c r="L152" s="0" t="n">
         <v>14.04</v>
       </c>
-      <c r="M152" t="n">
+      <c r="M152" s="0" t="n">
         <v>12.53</v>
       </c>
-      <c r="N152" t="n">
+      <c r="N152" s="0" t="n">
         <v>20.34</v>
       </c>
     </row>
@@ -45139,35 +45717,364 @@
       <c r="A153" s="1" t="n">
         <v>46154</v>
       </c>
+      <c r="B153" s="0" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="C153" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D153" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E153" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F153" s="0" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="G153" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H153" s="0" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="I153" s="0" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="J153" s="0" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K153" s="0" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="L153" s="0" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="M153" s="0" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="N153" s="0" t="n">
+        <v>21.22</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
         <v>46155</v>
       </c>
+      <c r="B154" s="0" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="C154" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D154" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E154" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F154" s="0" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="G154" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H154" s="0" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="I154" s="0" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="J154" s="0" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="K154" s="0" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="L154" s="0" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="M154" s="0" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="N154" s="0" t="n">
+        <v>9.630000000000001</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
         <v>46156</v>
       </c>
+      <c r="B155" s="0" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="C155" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D155" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E155" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F155" s="0" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G155" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H155" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I155" s="0" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J155" s="0" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="K155" s="0" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L155" s="0" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="M155" s="0" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N155" s="0" t="n">
+        <v>7.65</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
         <v>46157</v>
       </c>
+      <c r="B156" s="0" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="C156" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D156" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E156" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F156" s="0" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G156" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H156" s="0" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="I156" s="0" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="J156" s="0" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="K156" s="0" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="L156" s="0" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="M156" s="0" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N156" s="0" t="n">
+        <v>9.35</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
         <v>46158</v>
       </c>
+      <c r="B157" s="0" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="C157" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D157" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E157" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F157" s="0" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G157" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H157" s="0" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="I157" s="0" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J157" s="0" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K157" s="0" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="L157" s="0" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="M157" s="0" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="N157" s="0" t="n">
+        <v>12.51</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
         <v>46159</v>
       </c>
+      <c r="B158" s="0" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="C158" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D158" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E158" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F158" s="0" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="G158" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H158" s="0" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="I158" s="0" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="J158" s="0" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="K158" s="0" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="L158" s="0" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M158" s="0" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N158" s="0" t="n">
+        <v>10.15</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
         <v>46160</v>
+      </c>
+      <c r="B159" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="I159" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M159" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="N159" t="n">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="160">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -18735,45 +18735,45 @@
       <c r="A401" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="B401" t="n">
+      <c r="B401" s="0" t="n">
         <v>2.4</v>
       </c>
-      <c r="C401" t="n">
+      <c r="C401" s="0" t="n">
         <v>3.3</v>
       </c>
-      <c r="D401" t="n">
+      <c r="D401" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F401" t="n">
+      <c r="E401" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F401" s="0" t="n">
         <v>-6.3</v>
       </c>
-      <c r="G401" t="n">
+      <c r="G401" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="H401" t="n">
+      <c r="H401" s="0" t="n">
         <v>-0.6</v>
       </c>
-      <c r="I401" t="n">
+      <c r="I401" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="J401" t="n">
+      <c r="J401" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="K401" t="n">
+      <c r="K401" s="0" t="n">
         <v>-1.6</v>
       </c>
-      <c r="L401" t="n">
+      <c r="L401" s="0" t="n">
         <v>-0.6</v>
       </c>
-      <c r="M401" t="n">
+      <c r="M401" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="N401" t="n">
+      <c r="N401" s="0" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -18781,95 +18781,890 @@
       <c r="A402" s="1" t="n">
         <v>46161</v>
       </c>
+      <c r="B402" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C402" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D402" s="0" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E402" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F402" s="0" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="G402" s="0" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H402" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I402" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J402" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K402" s="0" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L402" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M402" s="0" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="N402" s="0" t="n">
+        <v>5.3</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
         <v>46162</v>
       </c>
+      <c r="B403" s="0" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C403" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D403" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E403" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F403" s="0" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G403" s="0" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H403" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I403" s="0" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J403" s="0" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K403" s="0" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="L403" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M403" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N403" s="0" t="n">
+        <v>10.8</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
         <v>46163</v>
       </c>
+      <c r="B404" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C404" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D404" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E404" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F404" s="0" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G404" s="0" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="H404" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="I404" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J404" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K404" s="0" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L404" s="0" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="M404" s="0" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="N404" s="0" t="n">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
         <v>46164</v>
       </c>
+      <c r="B405" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C405" s="0" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D405" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E405" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F405" s="0" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G405" s="0" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H405" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I405" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J405" s="0" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="K405" s="0" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="L405" s="0" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M405" s="0" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N405" s="0" t="n">
+        <v>4.4</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
         <v>46165</v>
       </c>
+      <c r="B406" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C406" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D406" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E406" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F406" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G406" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H406" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I406" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J406" s="0" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K406" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L406" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M406" s="0" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="N406" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
         <v>46166</v>
       </c>
+      <c r="B407" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C407" s="0" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D407" s="0" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="E407" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F407" s="0" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="G407" s="0" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="H407" s="0" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="I407" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J407" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="K407" s="0" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L407" s="0" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="M407" s="0" t="n">
+        <v>-6</v>
+      </c>
+      <c r="N407" s="0" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
         <v>46167</v>
       </c>
+      <c r="B408" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="C408" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D408" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E408" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F408" s="0" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="G408" s="0" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H408" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I408" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J408" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K408" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L408" s="0" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M408" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N408" s="0" t="n">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
         <v>46168</v>
       </c>
+      <c r="B409" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C409" s="0" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="D409" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E409" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F409" s="0" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="G409" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H409" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I409" s="0" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J409" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K409" s="0" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L409" s="0" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M409" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N409" s="0" t="n">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
         <v>46169</v>
       </c>
+      <c r="B410" s="0" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C410" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D410" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E410" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F410" s="0" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="G410" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H410" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I410" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J410" s="0" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="K410" s="0" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="L410" s="0" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="M410" s="0" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="N410" s="0" t="n">
+        <v>6.9</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
         <v>46170</v>
       </c>
+      <c r="B411" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="C411" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D411" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E411" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F411" s="0" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G411" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H411" s="0" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I411" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J411" s="0" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K411" s="0" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="L411" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M411" s="0" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N411" s="0" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
         <v>46171</v>
       </c>
+      <c r="B412" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C412" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="D412" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E412" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F412" s="0" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="G412" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H412" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I412" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J412" s="0" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K412" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L412" s="0" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M412" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N412" s="0" t="n">
+        <v>7.8</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
         <v>46172</v>
       </c>
+      <c r="B413" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="C413" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D413" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E413" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F413" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G413" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H413" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I413" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J413" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K413" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L413" s="0" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M413" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N413" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
         <v>46173</v>
       </c>
+      <c r="B414" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="C414" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D414" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E414" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F414" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G414" s="0" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H414" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I414" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J414" s="0" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K414" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L414" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="M414" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N414" s="0" t="n">
+        <v>4.9</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
         <v>46174</v>
       </c>
+      <c r="B415" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="C415" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D415" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E415" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F415" s="0" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G415" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H415" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I415" s="0" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J415" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K415" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L415" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="M415" s="0" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N415" s="0" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
         <v>46175</v>
       </c>
+      <c r="B416" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="C416" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D416" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E416" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F416" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G416" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H416" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I416" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J416" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K416" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L416" s="0" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M416" s="0" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="N416" s="0" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
         <v>46176</v>
       </c>
+      <c r="B417" s="0" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C417" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="D417" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E417" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F417" s="0" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G417" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H417" s="0" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I417" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J417" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K417" s="0" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="L417" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M417" s="0" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="N417" s="0" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
         <v>46177</v>
       </c>
+      <c r="B418" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="C418" s="0" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D418" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E418" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F418" s="0" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G418" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H418" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I418" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J418" s="0" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K418" s="0" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L418" s="0" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M418" s="0" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N418" s="0" t="n">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
         <v>46178</v>
       </c>
+      <c r="B419" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="C419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H419" s="0" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I419" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J419" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K419" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L419" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M419" s="0" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N419" s="0" t="n">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
         <v>46179</v>
+      </c>
+      <c r="B420" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="C420" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D420" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E420" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F420" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G420" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H420" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I420" t="n">
+        <v>8</v>
+      </c>
+      <c r="J420" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K420" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L420" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M420" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N420" t="n">
+        <v>6.3</v>
       </c>
     </row>
     <row r="421">
@@ -37229,45 +38024,45 @@
       <c r="A401" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="B401" t="n">
+      <c r="B401" s="0" t="n">
         <v>12.6</v>
       </c>
-      <c r="C401" t="n">
+      <c r="C401" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="D401" t="n">
+      <c r="D401" s="0" t="n">
         <v>7.8</v>
       </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F401" t="n">
+      <c r="E401" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F401" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="G401" t="n">
+      <c r="G401" s="0" t="n">
         <v>7.6</v>
       </c>
-      <c r="H401" t="n">
+      <c r="H401" s="0" t="n">
         <v>16.9</v>
       </c>
-      <c r="I401" t="n">
+      <c r="I401" s="0" t="n">
         <v>13.3</v>
       </c>
-      <c r="J401" t="n">
+      <c r="J401" s="0" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="K401" t="n">
+      <c r="K401" s="0" t="n">
         <v>4.1</v>
       </c>
-      <c r="L401" t="n">
+      <c r="L401" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="M401" t="n">
+      <c r="M401" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="N401" t="n">
+      <c r="N401" s="0" t="n">
         <v>15.2</v>
       </c>
     </row>
@@ -37275,95 +38070,896 @@
       <c r="A402" s="1" t="n">
         <v>46161</v>
       </c>
+      <c r="B402" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C402" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D402" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E402" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F402" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G402" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H402" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I402" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J402" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K402" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L402" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="M402" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N402" s="0" t="n">
+        <v>22.6</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
         <v>46162</v>
       </c>
+      <c r="B403" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C403" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D403" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E403" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F403" s="0" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="G403" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H403" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I403" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J403" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K403" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L403" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="M403" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N403" s="0" t="n">
+        <v>24.3</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
         <v>46163</v>
       </c>
+      <c r="B404" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C404" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D404" s="0" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="E404" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F404" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G404" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H404" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="I404" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="J404" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K404" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L404" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="M404" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="N404" s="0" t="n">
+        <v>20.4</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
         <v>46164</v>
       </c>
+      <c r="B405" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="C405" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="D405" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E405" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F405" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G405" s="0" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H405" s="0" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="I405" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="J405" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K405" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L405" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M405" s="0" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N405" s="0" t="n">
+        <v>16.9</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
         <v>46165</v>
       </c>
+      <c r="B406" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C406" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D406" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E406" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F406" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G406" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H406" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I406" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J406" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K406" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="L406" s="0" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M406" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="N406" s="0" t="n">
+        <v>26.1</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
         <v>46166</v>
       </c>
+      <c r="B407" s="0" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="C407" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="D407" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="E407" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F407" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G407" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H407" s="0" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I407" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J407" s="0" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K407" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L407" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M407" s="0" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N407" s="0" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
         <v>46167</v>
       </c>
+      <c r="B408" s="0" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="C408" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D408" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E408" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F408" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G408" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H408" s="0" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="I408" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J408" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K408" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L408" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M408" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="N408" s="0" t="n">
+        <v>21.7</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
         <v>46168</v>
       </c>
+      <c r="B409" s="0" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C409" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D409" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E409" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F409" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G409" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="H409" s="0" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I409" s="0" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J409" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K409" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L409" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="M409" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N409" s="0" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
         <v>46169</v>
       </c>
+      <c r="B410" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C410" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D410" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="E410" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F410" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G410" s="0" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H410" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I410" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J410" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="K410" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L410" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M410" s="0" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N410" s="0" t="n">
+        <v>16.2</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
         <v>46170</v>
       </c>
+      <c r="B411" s="0" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="C411" s="0" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="D411" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E411" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F411" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G411" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H411" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="I411" s="0" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="J411" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K411" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="L411" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="M411" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N411" s="0" t="n">
+        <v>23.1</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
         <v>46171</v>
       </c>
+      <c r="B412" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="C412" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D412" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="E412" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F412" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G412" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H412" s="0" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="I412" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J412" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K412" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="L412" s="0" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="M412" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="N412" s="0" t="n">
+        <v>28.2</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
         <v>46172</v>
       </c>
+      <c r="B413" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C413" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D413" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E413" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F413" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="G413" s="0" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H413" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I413" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="J413" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K413" s="0" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="L413" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="M413" s="0" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="N413" s="0" t="n">
+        <v>24.8</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
         <v>46173</v>
       </c>
+      <c r="B414" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C414" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D414" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E414" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F414" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G414" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H414" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="I414" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="J414" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="K414" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L414" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M414" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N414" s="0" t="n">
+        <v>16.4</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
         <v>46174</v>
       </c>
+      <c r="B415" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="C415" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D415" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E415" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F415" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G415" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H415" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I415" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J415" s="0" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K415" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L415" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="M415" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="N415" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
         <v>46175</v>
       </c>
+      <c r="B416" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C416" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="D416" s="0" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E416" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F416" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G416" s="0" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H416" s="0" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I416" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="J416" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K416" s="0" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="L416" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M416" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N416" s="0" t="n">
+        <v>13.3</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
         <v>46176</v>
       </c>
+      <c r="B417" s="0" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="C417" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="D417" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E417" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F417" s="0" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G417" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H417" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I417" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J417" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K417" s="0" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="L417" s="0" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="M417" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N417" s="0" t="n">
+        <v>12.8</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
         <v>46177</v>
       </c>
+      <c r="B418" s="0" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="C418" s="0" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D418" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E418" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F418" s="0" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G418" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H418" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I418" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="J418" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K418" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="L418" s="0" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M418" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N418" s="0" t="n">
+        <v>13.9</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
         <v>46178</v>
       </c>
+      <c r="B419" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="C419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G419" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H419" s="0" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I419" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J419" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K419" s="0" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="L419" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M419" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N419" s="0" t="n">
+        <v>16.2</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
         <v>46179</v>
+      </c>
+      <c r="B420" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="C420" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D420" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E420" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F420" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G420" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H420" t="n">
+        <v>22</v>
+      </c>
+      <c r="I420" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J420" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="K420" t="n">
+        <v>20</v>
+      </c>
+      <c r="L420" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M420" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N420" t="n">
+        <v>15.1</v>
       </c>
     </row>
     <row r="421">
@@ -46029,51 +47625,51 @@
       <c r="A159" s="1" t="n">
         <v>46160</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" s="0" t="n">
         <v>6.86</v>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
+      <c r="C159" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D159" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E159" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F159" s="0" t="n">
         <v>1.82</v>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H159" t="n">
+      <c r="G159" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H159" s="0" t="n">
         <v>9.130000000000001</v>
       </c>
-      <c r="I159" t="n">
+      <c r="I159" s="0" t="n">
         <v>7.51</v>
       </c>
-      <c r="J159" t="n">
+      <c r="J159" s="0" t="n">
         <v>3.86</v>
       </c>
-      <c r="K159" t="n">
+      <c r="K159" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="L159" t="n">
+      <c r="L159" s="0" t="n">
         <v>2.21</v>
       </c>
-      <c r="M159" t="n">
+      <c r="M159" s="0" t="n">
         <v>2.06</v>
       </c>
-      <c r="N159" t="n">
+      <c r="N159" s="0" t="n">
         <v>8.699999999999999</v>
       </c>
     </row>
@@ -46081,95 +47677,1000 @@
       <c r="A160" s="1" t="n">
         <v>46161</v>
       </c>
+      <c r="B160" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C160" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D160" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E160" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F160" s="0" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="G160" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H160" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I160" s="0" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J160" s="0" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="K160" s="0" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="L160" s="0" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="M160" s="0" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N160" s="0" t="n">
+        <v>13.36</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
         <v>46162</v>
       </c>
+      <c r="B161" s="0" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="C161" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D161" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E161" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F161" s="0" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="G161" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H161" s="0" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="I161" s="0" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="J161" s="0" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="K161" s="0" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L161" s="0" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="M161" s="0" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N161" s="0" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
         <v>46163</v>
       </c>
+      <c r="B162" s="0" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="C162" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D162" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E162" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F162" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G162" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H162" s="0" t="n">
+        <v>15.92</v>
+      </c>
+      <c r="I162" s="0" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="J162" s="0" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="K162" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L162" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M162" s="0" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N162" s="0" t="n">
+        <v>12.84</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
         <v>46164</v>
       </c>
+      <c r="B163" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C163" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D163" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E163" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F163" s="0" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G163" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H163" s="0" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="I163" s="0" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="J163" s="0" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="K163" s="0" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="L163" s="0" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="M163" s="0" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="N163" s="0" t="n">
+        <v>10.05</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
         <v>46165</v>
       </c>
+      <c r="B164" s="0" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="C164" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D164" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E164" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F164" s="0" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G164" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H164" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I164" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J164" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K164" s="0" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="L164" s="0" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="M164" s="0" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N164" s="0" t="n">
+        <v>13.88</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
         <v>46166</v>
       </c>
+      <c r="B165" s="0" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="C165" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D165" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E165" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F165" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G165" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H165" s="0" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I165" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J165" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K165" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="L165" s="0" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="M165" s="0" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="N165" s="0" t="n">
+        <v>6.29</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
         <v>46167</v>
       </c>
+      <c r="B166" s="0" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="C166" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D166" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E166" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F166" s="0" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="G166" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H166" s="0" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="I166" s="0" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="J166" s="0" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="K166" s="0" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="L166" s="0" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="M166" s="0" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="N166" s="0" t="n">
+        <v>13.21</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
         <v>46168</v>
       </c>
+      <c r="B167" s="0" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="C167" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D167" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E167" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F167" s="0" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G167" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H167" s="0" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="I167" s="0" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="J167" s="0" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="K167" s="0" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="L167" s="0" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="M167" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N167" s="0" t="n">
+        <v>12.84</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
         <v>46169</v>
       </c>
+      <c r="B168" s="0" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="C168" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D168" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E168" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F168" s="0" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G168" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H168" s="0" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="I168" s="0" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="J168" s="0" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="K168" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L168" s="0" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="M168" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N168" s="0" t="n">
+        <v>10.78</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
         <v>46170</v>
       </c>
+      <c r="B169" s="0" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="C169" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D169" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E169" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F169" s="0" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="G169" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H169" s="0" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="I169" s="0" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="J169" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K169" s="0" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="L169" s="0" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="M169" s="0" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="N169" s="0" t="n">
+        <v>13.93</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
         <v>46171</v>
       </c>
+      <c r="B170" s="0" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="C170" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D170" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E170" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F170" s="0" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="G170" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H170" s="0" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="I170" s="0" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="J170" s="0" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="K170" s="0" t="n">
+        <v>12.51</v>
+      </c>
+      <c r="L170" s="0" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="M170" s="0" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="N170" s="0" t="n">
+        <v>18.28</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
         <v>46172</v>
       </c>
+      <c r="B171" s="0" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="C171" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D171" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E171" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F171" s="0" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="G171" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H171" s="0" t="n">
+        <v>14.74</v>
+      </c>
+      <c r="I171" s="0" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="J171" s="0" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="K171" s="0" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="L171" s="0" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="M171" s="0" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="N171" s="0" t="n">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
         <v>46173</v>
       </c>
+      <c r="B172" s="0" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="C172" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D172" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E172" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F172" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G172" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H172" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="I172" s="0" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="J172" s="0" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="K172" s="0" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="L172" s="0" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="M172" s="0" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="N172" s="0" t="n">
+        <v>8.68</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
         <v>46174</v>
       </c>
+      <c r="B173" s="0" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="C173" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D173" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E173" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F173" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G173" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H173" s="0" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="I173" s="0" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="J173" s="0" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="K173" s="0" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="L173" s="0" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="M173" s="0" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="N173" s="0" t="n">
+        <v>5.96</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
         <v>46175</v>
       </c>
+      <c r="B174" s="0" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="C174" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D174" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E174" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F174" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G174" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H174" s="0" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="I174" s="0" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="J174" s="0" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="K174" s="0" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="L174" s="0" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="M174" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N174" s="0" t="n">
+        <v>6.76</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
         <v>46176</v>
       </c>
+      <c r="B175" s="0" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="C175" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D175" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E175" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F175" s="0" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="G175" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H175" s="0" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="I175" s="0" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J175" s="0" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="K175" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L175" s="0" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="M175" s="0" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="N175" s="0" t="n">
+        <v>6.85</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
         <v>46177</v>
       </c>
+      <c r="B176" s="0" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="C176" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D176" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E176" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F176" s="0" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="G176" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H176" s="0" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="I176" s="0" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="J176" s="0" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="K176" s="0" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="L176" s="0" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="M176" s="0" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N176" s="0" t="n">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
         <v>46178</v>
       </c>
+      <c r="B177" s="0" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="C177" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D177" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E177" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F177" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G177" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H177" s="0" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="I177" s="0" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="J177" s="0" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="K177" s="0" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="L177" s="0" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="M177" s="0" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="N177" s="0" t="n">
+        <v>9.06</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
         <v>46179</v>
+      </c>
+      <c r="B178" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="I178" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="J178" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="K178" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="L178" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="M178" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="N178" t="n">
+        <v>11.28</v>
       </c>
     </row>
     <row r="179">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低温存档" sheetId="1" state="visible" r:id="rId1"/>
@@ -19627,43 +19627,43 @@
       <c r="A420" s="1" t="n">
         <v>46179</v>
       </c>
-      <c r="B420" t="n">
+      <c r="B420" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="C420" t="n">
+      <c r="C420" s="0" t="n">
         <v>7.8</v>
       </c>
-      <c r="D420" t="n">
+      <c r="D420" s="0" t="n">
         <v>6.9</v>
       </c>
-      <c r="E420" t="n">
+      <c r="E420" s="0" t="n">
         <v>-1.6</v>
       </c>
-      <c r="F420" t="n">
+      <c r="F420" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="G420" t="n">
+      <c r="G420" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="H420" t="n">
+      <c r="H420" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="I420" t="n">
+      <c r="I420" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="J420" t="n">
+      <c r="J420" s="0" t="n">
         <v>4.2</v>
       </c>
-      <c r="K420" t="n">
+      <c r="K420" s="0" t="n">
         <v>-1.2</v>
       </c>
-      <c r="L420" t="n">
+      <c r="L420" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="M420" t="n">
+      <c r="M420" s="0" t="n">
         <v>1.9</v>
       </c>
-      <c r="N420" t="n">
+      <c r="N420" s="0" t="n">
         <v>6.3</v>
       </c>
     </row>
@@ -19671,85 +19671,780 @@
       <c r="A421" s="1" t="n">
         <v>46180</v>
       </c>
+      <c r="B421" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C421" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D421" s="0" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E421" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F421" s="0" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G421" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H421" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I421" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J421" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K421" s="0" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="L421" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M421" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N421" s="0" t="n">
+        <v>3.8</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
         <v>46181</v>
       </c>
+      <c r="B422" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C422" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="D422" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="E422" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F422" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G422" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H422" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I422" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J422" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K422" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L422" s="0" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M422" s="0" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N422" s="0" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
         <v>46182</v>
       </c>
+      <c r="B423" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C423" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D423" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E423" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F423" s="0" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G423" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H423" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I423" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J423" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K423" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L423" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M423" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N423" s="0" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
         <v>46183</v>
       </c>
+      <c r="B424" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C424" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D424" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="E424" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F424" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G424" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H424" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I424" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J424" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K424" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L424" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M424" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N424" s="0" t="n">
+        <v>6.8</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
         <v>46184</v>
       </c>
+      <c r="B425" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C425" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D425" s="0" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E425" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F425" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="G425" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H425" s="0" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I425" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J425" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K425" s="0" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L425" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="M425" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N425" s="0" t="n">
+        <v>10.9</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
         <v>46185</v>
       </c>
+      <c r="B426" s="0" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C426" s="0" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D426" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E426" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F426" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G426" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H426" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I426" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J426" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K426" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L426" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M426" s="0" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N426" s="0" t="n">
+        <v>12.6</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
         <v>46186</v>
       </c>
+      <c r="B427" s="0" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C427" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D427" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E427" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F427" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G427" s="0" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H427" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I427" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J427" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="K427" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L427" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M427" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="N427" s="0" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
         <v>46187</v>
       </c>
+      <c r="B428" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C428" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="D428" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E428" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F428" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G428" s="0" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H428" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I428" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J428" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K428" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L428" s="0" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M428" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N428" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
         <v>46188</v>
       </c>
+      <c r="B429" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="C429" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D429" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E429" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F429" s="0" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G429" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H429" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I429" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J429" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K429" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L429" s="0" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="M429" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N429" s="0" t="n">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
         <v>46189</v>
       </c>
+      <c r="B430" s="0" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="C430" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="D430" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="E430" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F430" s="0" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G430" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H430" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I430" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J430" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K430" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L430" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M430" s="0" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N430" s="0" t="n">
+        <v>10.7</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
         <v>46190</v>
       </c>
+      <c r="B431" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C431" s="0" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="D431" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="E431" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F431" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G431" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H431" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I431" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J431" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K431" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="L431" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="M431" s="0" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="N431" s="0" t="n">
+        <v>14.4</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
         <v>46191</v>
       </c>
+      <c r="B432" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C432" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D432" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E432" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F432" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G432" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H432" s="0" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I432" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J432" s="0" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K432" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="L432" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M432" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N432" s="0" t="n">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
         <v>46192</v>
       </c>
+      <c r="B433" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="C433" s="0" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="D433" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E433" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F433" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G433" s="0" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="H433" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I433" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J433" s="0" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K433" s="0" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L433" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M433" s="0" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="N433" s="0" t="n">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
         <v>46193</v>
       </c>
+      <c r="B434" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C434" s="0" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D434" s="0" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E434" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F434" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G434" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H434" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I434" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J434" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K434" s="0" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L434" s="0" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="M434" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N434" s="0" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
         <v>46194</v>
       </c>
+      <c r="B435" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C435" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D435" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="E435" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F435" s="0" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G435" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H435" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I435" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J435" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K435" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L435" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M435" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N435" s="0" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
         <v>46195</v>
       </c>
+      <c r="B436" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C436" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D436" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="E436" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F436" s="0" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G436" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H436" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I436" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J436" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K436" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L436" s="0" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M436" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N436" s="0" t="n">
+        <v>4.6</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
         <v>46196</v>
+      </c>
+      <c r="B437" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C437" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="D437" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G437" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H437" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I437" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J437" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K437" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L437" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M437" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N437" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="438">
@@ -38922,43 +39617,43 @@
       <c r="A420" s="1" t="n">
         <v>46179</v>
       </c>
-      <c r="B420" t="n">
+      <c r="B420" s="0" t="n">
         <v>29.1</v>
       </c>
-      <c r="C420" t="n">
+      <c r="C420" s="0" t="n">
         <v>27.5</v>
       </c>
-      <c r="D420" t="n">
+      <c r="D420" s="0" t="n">
         <v>25.2</v>
       </c>
-      <c r="E420" t="n">
+      <c r="E420" s="0" t="n">
         <v>21.5</v>
       </c>
-      <c r="F420" t="n">
+      <c r="F420" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="G420" t="n">
+      <c r="G420" s="0" t="n">
         <v>18.9</v>
       </c>
-      <c r="H420" t="n">
+      <c r="H420" s="0" t="n">
         <v>22</v>
       </c>
-      <c r="I420" t="n">
+      <c r="I420" s="0" t="n">
         <v>28.1</v>
       </c>
-      <c r="J420" t="n">
+      <c r="J420" s="0" t="n">
         <v>24.1</v>
       </c>
-      <c r="K420" t="n">
+      <c r="K420" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="L420" t="n">
+      <c r="L420" s="0" t="n">
         <v>21.8</v>
       </c>
-      <c r="M420" t="n">
+      <c r="M420" s="0" t="n">
         <v>18.8</v>
       </c>
-      <c r="N420" t="n">
+      <c r="N420" s="0" t="n">
         <v>15.1</v>
       </c>
     </row>
@@ -38966,85 +39661,780 @@
       <c r="A421" s="1" t="n">
         <v>46180</v>
       </c>
+      <c r="B421" s="0" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C421" s="0" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D421" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E421" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F421" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G421" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H421" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I421" s="0" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="J421" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K421" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="L421" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="M421" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N421" s="0" t="n">
+        <v>17.9</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
         <v>46181</v>
       </c>
+      <c r="B422" s="0" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="C422" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D422" s="0" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E422" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F422" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="G422" s="0" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H422" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I422" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="J422" s="0" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="K422" s="0" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L422" s="0" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="M422" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N422" s="0" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
         <v>46182</v>
       </c>
+      <c r="B423" s="0" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="C423" s="0" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D423" s="0" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E423" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F423" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="G423" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="H423" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I423" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J423" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="K423" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L423" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="M423" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="N423" s="0" t="n">
+        <v>20.5</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
         <v>46183</v>
       </c>
+      <c r="B424" s="0" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C424" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D424" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E424" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F424" s="0" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G424" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H424" s="0" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I424" s="0" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="J424" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="K424" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="L424" s="0" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="M424" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="N424" s="0" t="n">
+        <v>25.4</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
         <v>46184</v>
       </c>
+      <c r="B425" s="0" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="C425" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="D425" s="0" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E425" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F425" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G425" s="0" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H425" s="0" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I425" s="0" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="J425" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K425" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="L425" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="M425" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="N425" s="0" t="n">
+        <v>27.4</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
         <v>46185</v>
       </c>
+      <c r="B426" s="0" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="C426" s="0" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D426" s="0" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E426" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F426" s="0" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G426" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H426" s="0" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I426" s="0" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J426" s="0" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="K426" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L426" s="0" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M426" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="N426" s="0" t="n">
+        <v>20.7</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
         <v>46186</v>
       </c>
+      <c r="B427" s="0" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C427" s="0" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="D427" s="0" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E427" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F427" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G427" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H427" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I427" s="0" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="J427" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="K427" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L427" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="M427" s="0" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="N427" s="0" t="n">
+        <v>16.6</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
         <v>46187</v>
       </c>
+      <c r="B428" s="0" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="C428" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D428" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E428" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F428" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G428" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H428" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I428" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="J428" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="K428" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L428" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M428" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N428" s="0" t="n">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
         <v>46188</v>
       </c>
+      <c r="B429" s="0" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="C429" s="0" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="D429" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E429" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F429" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G429" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="H429" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I429" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="J429" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="K429" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L429" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="M429" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N429" s="0" t="n">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
         <v>46189</v>
       </c>
+      <c r="B430" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C430" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="D430" s="0" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E430" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F430" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="G430" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H430" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I430" s="0" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="J430" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="K430" s="0" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="L430" s="0" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="M430" s="0" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="N430" s="0" t="n">
+        <v>25.4</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
         <v>46190</v>
       </c>
+      <c r="B431" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="C431" s="0" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D431" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="E431" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F431" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G431" s="0" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H431" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="I431" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J431" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="K431" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="L431" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="M431" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N431" s="0" t="n">
+        <v>26.3</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
         <v>46191</v>
       </c>
+      <c r="B432" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="C432" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D432" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="E432" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F432" s="0" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G432" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H432" s="0" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I432" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J432" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K432" s="0" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="L432" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M432" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N432" s="0" t="n">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
         <v>46192</v>
       </c>
+      <c r="B433" s="0" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C433" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D433" s="0" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E433" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F433" s="0" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G433" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H433" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I433" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="J433" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K433" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L433" s="0" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="M433" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N433" s="0" t="n">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
         <v>46193</v>
       </c>
+      <c r="B434" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C434" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D434" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E434" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F434" s="0" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G434" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H434" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="I434" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="J434" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="K434" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="L434" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M434" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="N434" s="0" t="n">
+        <v>8.9</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
         <v>46194</v>
       </c>
+      <c r="B435" s="0" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="C435" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="D435" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E435" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F435" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G435" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H435" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I435" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J435" s="0" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="K435" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="L435" s="0" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M435" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="N435" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
         <v>46195</v>
       </c>
+      <c r="B436" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C436" s="0" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="D436" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E436" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F436" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G436" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="H436" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I436" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J436" s="0" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K436" s="0" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L436" s="0" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M436" s="0" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N436" s="0" t="n">
+        <v>12.9</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
         <v>46196</v>
+      </c>
+      <c r="B437" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="C437" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="D437" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G437" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H437" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I437" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J437" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="K437" t="n">
+        <v>21</v>
+      </c>
+      <c r="L437" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M437" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N437" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="438">
@@ -48625,51 +50015,51 @@
       <c r="A178" s="1" t="n">
         <v>46179</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="0" t="n">
         <v>18.91</v>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F178" t="n">
+      <c r="C178" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D178" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E178" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F178" s="0" t="n">
         <v>10.8</v>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H178" t="n">
+      <c r="G178" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H178" s="0" t="n">
         <v>12.66</v>
       </c>
-      <c r="I178" t="n">
+      <c r="I178" s="0" t="n">
         <v>18.68</v>
       </c>
-      <c r="J178" t="n">
+      <c r="J178" s="0" t="n">
         <v>14.91</v>
       </c>
-      <c r="K178" t="n">
+      <c r="K178" s="0" t="n">
         <v>11.97</v>
       </c>
-      <c r="L178" t="n">
+      <c r="L178" s="0" t="n">
         <v>12.24</v>
       </c>
-      <c r="M178" t="n">
+      <c r="M178" s="0" t="n">
         <v>11.97</v>
       </c>
-      <c r="N178" t="n">
+      <c r="N178" s="0" t="n">
         <v>11.28</v>
       </c>
     </row>
@@ -48677,85 +50067,884 @@
       <c r="A179" s="1" t="n">
         <v>46180</v>
       </c>
+      <c r="B179" s="0" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="C179" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D179" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E179" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F179" s="0" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="G179" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H179" s="0" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="I179" s="0" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="J179" s="0" t="n">
+        <v>17.64</v>
+      </c>
+      <c r="K179" s="0" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="L179" s="0" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="M179" s="0" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="N179" s="0" t="n">
+        <v>10.78</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
         <v>46181</v>
       </c>
+      <c r="B180" s="0" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="C180" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D180" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E180" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F180" s="0" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="G180" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H180" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I180" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="J180" s="0" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="K180" s="0" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="L180" s="0" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="M180" s="0" t="n">
+        <v>13.51</v>
+      </c>
+      <c r="N180" s="0" t="n">
+        <v>11.35</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
         <v>46182</v>
       </c>
+      <c r="B181" s="0" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="C181" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D181" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E181" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F181" s="0" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="G181" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H181" s="0" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="I181" s="0" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="J181" s="0" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="K181" s="0" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="L181" s="0" t="n">
+        <v>16.38</v>
+      </c>
+      <c r="M181" s="0" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="N181" s="0" t="n">
+        <v>14.11</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
         <v>46183</v>
       </c>
+      <c r="B182" s="0" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="C182" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D182" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E182" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F182" s="0" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="G182" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H182" s="0" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="I182" s="0" t="n">
+        <v>22.04</v>
+      </c>
+      <c r="J182" s="0" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="K182" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L182" s="0" t="n">
+        <v>14.61</v>
+      </c>
+      <c r="M182" s="0" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="N182" s="0" t="n">
+        <v>16.43</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
         <v>46184</v>
       </c>
+      <c r="B183" s="0" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="C183" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D183" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E183" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F183" s="0" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="G183" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H183" s="0" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="I183" s="0" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="J183" s="0" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="K183" s="0" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="L183" s="0" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="M183" s="0" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="N183" s="0" t="n">
+        <v>18.69</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
         <v>46185</v>
       </c>
+      <c r="B184" s="0" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="C184" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D184" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E184" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F184" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G184" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H184" s="0" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="I184" s="0" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="J184" s="0" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="K184" s="0" t="n">
+        <v>14.93</v>
+      </c>
+      <c r="L184" s="0" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="M184" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="N184" s="0" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
         <v>46186</v>
       </c>
+      <c r="B185" s="0" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="C185" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D185" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E185" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F185" s="0" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="G185" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H185" s="0" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="I185" s="0" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="J185" s="0" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="K185" s="0" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="L185" s="0" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="M185" s="0" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="N185" s="0" t="n">
+        <v>12.78</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
         <v>46187</v>
       </c>
+      <c r="B186" s="0" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="C186" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D186" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E186" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F186" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G186" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H186" s="0" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="I186" s="0" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="J186" s="0" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="K186" s="0" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="L186" s="0" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="M186" s="0" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="N186" s="0" t="n">
+        <v>16.2</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
         <v>46188</v>
       </c>
+      <c r="B187" s="0" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="C187" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D187" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E187" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F187" s="0" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="G187" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H187" s="0" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="I187" s="0" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="J187" s="0" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="K187" s="0" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="L187" s="0" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="M187" s="0" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="N187" s="0" t="n">
+        <v>15.76</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
         <v>46189</v>
       </c>
+      <c r="B188" s="0" t="n">
+        <v>22.41</v>
+      </c>
+      <c r="C188" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D188" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E188" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F188" s="0" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="G188" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H188" s="0" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="I188" s="0" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="J188" s="0" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="K188" s="0" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="L188" s="0" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="M188" s="0" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="N188" s="0" t="n">
+        <v>18.44</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
         <v>46190</v>
       </c>
+      <c r="B189" s="0" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="C189" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D189" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E189" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F189" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G189" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H189" s="0" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="I189" s="0" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="J189" s="0" t="n">
+        <v>17.71</v>
+      </c>
+      <c r="K189" s="0" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="L189" s="0" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="M189" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N189" s="0" t="n">
+        <v>20.05</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
         <v>46191</v>
       </c>
+      <c r="B190" s="0" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="C190" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D190" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E190" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F190" s="0" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="G190" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H190" s="0" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="I190" s="0" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="J190" s="0" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="K190" s="0" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="L190" s="0" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="M190" s="0" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="N190" s="0" t="n">
+        <v>16.04</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
         <v>46192</v>
       </c>
+      <c r="B191" s="0" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="C191" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D191" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E191" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F191" s="0" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G191" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H191" s="0" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="I191" s="0" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="J191" s="0" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="K191" s="0" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="L191" s="0" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="M191" s="0" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="N191" s="0" t="n">
+        <v>4.14</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
         <v>46193</v>
       </c>
+      <c r="B192" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C192" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D192" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E192" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F192" s="0" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="G192" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H192" s="0" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="I192" s="0" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="J192" s="0" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="K192" s="0" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="L192" s="0" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="M192" s="0" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="N192" s="0" t="n">
+        <v>5.08</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
         <v>46194</v>
       </c>
+      <c r="B193" s="0" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="C193" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D193" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E193" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F193" s="0" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="G193" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H193" s="0" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="I193" s="0" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="J193" s="0" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="K193" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L193" s="0" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="M193" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N193" s="0" t="n">
+        <v>5.8</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
         <v>46195</v>
       </c>
+      <c r="B194" s="0" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="C194" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D194" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E194" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F194" s="0" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="G194" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H194" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I194" s="0" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="J194" s="0" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="K194" s="0" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="L194" s="0" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="M194" s="0" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="N194" s="0" t="n">
+        <v>7.71</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
         <v>46196</v>
+      </c>
+      <c r="B195" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="I195" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="J195" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="K195" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="L195" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="M195" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="N195" t="n">
+        <v>11.18</v>
       </c>
     </row>
     <row r="196">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="低温存档" sheetId="1" state="visible" r:id="rId1"/>
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N444"/>
+  <dimension ref="A1:N722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9" outlineLevelCol="0"/>
   <cols>
     <col width="12.59765625" customWidth="1" style="2" min="1" max="1"/>
@@ -20405,45 +20405,45 @@
       <c r="A437" s="1" t="n">
         <v>46196</v>
       </c>
-      <c r="B437" t="n">
+      <c r="B437" s="0" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C437" t="n">
+      <c r="C437" s="0" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="D437" t="n">
+      <c r="D437" s="0" t="n">
         <v>9.5</v>
       </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F437" t="n">
+      <c r="E437" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F437" s="0" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="G437" t="n">
+      <c r="G437" s="0" t="n">
         <v>1.6</v>
       </c>
-      <c r="H437" t="n">
+      <c r="H437" s="0" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="I437" t="n">
+      <c r="I437" s="0" t="n">
         <v>10.4</v>
       </c>
-      <c r="J437" t="n">
+      <c r="J437" s="0" t="n">
         <v>4.2</v>
       </c>
-      <c r="K437" t="n">
+      <c r="K437" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="L437" t="n">
+      <c r="L437" s="0" t="n">
         <v>4.3</v>
       </c>
-      <c r="M437" t="n">
+      <c r="M437" s="0" t="n">
         <v>2.7</v>
       </c>
-      <c r="N437" t="n">
+      <c r="N437" s="0" t="n">
         <v>7.1</v>
       </c>
     </row>
@@ -20451,36 +20451,2851 @@
       <c r="A438" s="1" t="n">
         <v>46197</v>
       </c>
+      <c r="B438" s="0" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C438" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="D438" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="E438" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F438" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G438" s="0" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H438" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I438" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J438" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="K438" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="L438" s="0" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="M438" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N438" s="0" t="n">
+        <v>6.2</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
         <v>46198</v>
       </c>
+      <c r="B439" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C439" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D439" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E439" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F439" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G439" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H439" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I439" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J439" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K439" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L439" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M439" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="N439" s="0" t="n">
+        <v>13.4</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
         <v>46199</v>
       </c>
+      <c r="B440" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C440" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="D440" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E440" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F440" s="0" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G440" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H440" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I440" s="0" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J440" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K440" s="0" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L440" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M440" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="N440" s="0" t="n">
+        <v>12.7</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
         <v>46200</v>
       </c>
+      <c r="B441" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C441" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="D441" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="E441" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F441" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G441" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H441" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="I441" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="J441" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K441" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L441" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M441" s="0" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="N441" s="0" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
         <v>46201</v>
       </c>
+      <c r="B442" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C442" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D442" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E442" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F442" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="G442" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H442" s="0" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I442" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J442" s="0" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K442" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L442" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="M442" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N442" s="0" t="n">
+        <v>12.6</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
         <v>46202</v>
       </c>
+      <c r="B443" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C443" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D443" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E443" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F443" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G443" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H443" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="I443" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="J443" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K443" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L443" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M443" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N443" s="0" t="n">
+        <v>12.1</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
         <v>46203</v>
       </c>
+      <c r="B444" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C444" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D444" s="0" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E444" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F444" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G444" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H444" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I444" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J444" s="0" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="K444" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L444" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M444" s="0" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N444" s="0" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B445" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C445" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D445" s="0" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="E445" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F445" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G445" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H445" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I445" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="J445" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K445" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L445" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M445" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N445" s="0" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B446" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C446" s="0" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D446" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E446" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F446" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="G446" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H446" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I446" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J446" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K446" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L446" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M446" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N446" s="0" t="n">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B447" s="0" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="C447" s="0" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="D447" s="0" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E447" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F447" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="G447" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H447" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="I447" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J447" s="0" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K447" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L447" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="M447" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="N447" s="0" t="n">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B448" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C448" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D448" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E448" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F448" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G448" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H448" s="0" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I448" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J448" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K448" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="L448" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M448" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N448" s="0" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B449" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C449" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="D449" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E449" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F449" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G449" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H449" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I449" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J449" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="K449" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L449" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="M449" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N449" s="0" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B450" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="C450" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="D450" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E450" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F450" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G450" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H450" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I450" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J450" s="0" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="K450" s="0" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="L450" s="0" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M450" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N450" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B451" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="C451" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D451" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="E451" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F451" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="G451" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H451" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I451" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="J451" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="K451" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L451" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="M451" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N451" s="0" t="n">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B452" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C452" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="D452" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E452" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F452" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G452" s="0" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H452" s="0" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I452" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="J452" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="K452" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L452" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M452" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N452" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B453" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C453" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D453" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E453" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F453" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G453" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H453" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I453" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J453" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K453" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L453" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M453" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N453" s="0" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B454" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C454" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D454" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="E454" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F454" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G454" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H454" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I454" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="J454" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="K454" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L454" s="0" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M454" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N454" s="0" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B455" s="0" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C455" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="D455" s="0" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E455" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F455" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G455" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H455" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I455" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J455" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K455" s="0" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L455" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M455" s="0" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N455" s="0" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B456" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C456" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D456" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E456" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F456" s="0" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G456" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H456" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I456" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J456" s="0" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K456" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L456" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M456" s="0" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N456" s="0" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B457" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C457" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D457" s="0" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E457" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F457" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G457" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H457" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I457" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J457" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K457" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L457" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M457" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N457" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B458" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C458" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="D458" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E458" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F458" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G458" s="0" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H458" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I458" s="0" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J458" s="0" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K458" s="0" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L458" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M458" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N458" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B459" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C459" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D459" s="0" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="E459" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F459" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G459" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H459" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I459" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J459" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K459" s="0" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L459" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="M459" s="0" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="N459" s="0" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B460" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C460" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="D460" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E460" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F460" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="G460" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H460" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="I460" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J460" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K460" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L460" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="M460" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N460" s="0" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B461" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="C461" s="0" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D461" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E461" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F461" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G461" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H461" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I461" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="J461" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K461" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="L461" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M461" s="0" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N461" s="0" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B462" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C462" s="0" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D462" s="0" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E462" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F462" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G462" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="H462" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I462" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J462" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K462" s="0" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L462" s="0" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M462" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N462" s="0" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B463" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C463" s="0" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D463" s="0" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E463" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F463" s="0" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G463" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H463" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I463" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J463" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K463" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L463" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M463" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N463" s="0" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B464" s="0" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C464" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D464" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E464" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F464" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G464" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H464" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="I464" s="0" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J464" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K464" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L464" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="M464" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N464" s="0" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B465" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="C465" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D465" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="E465" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F465" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G465" s="0" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H465" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="I465" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J465" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K465" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L465" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M465" s="0" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N465" s="0" t="n">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B466" s="0" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C466" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="D466" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E466" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F466" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G466" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H466" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I466" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J466" s="0" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K466" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L466" s="0" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M466" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N466" s="0" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B467" s="0" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="C467" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="D467" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E467" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F467" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G467" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H467" s="0" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I467" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J467" s="0" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="K467" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="L467" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="M467" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N467" s="0" t="n">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B468" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C468" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D468" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E468" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F468" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G468" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H468" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="I468" s="0" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="J468" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K468" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="L468" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M468" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="N468" s="0" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B469" s="0" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="C469" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="D469" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E469" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F469" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G469" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H469" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I469" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="J469" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K469" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L469" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="M469" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N469" s="0" t="n">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B470" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C470" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D470" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="E470" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F470" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G470" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H470" s="0" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I470" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J470" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K470" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L470" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="M470" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="N470" s="0" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B471" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C471" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="D471" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="E471" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F471" s="0" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G471" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H471" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I471" s="0" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="J471" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K471" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L471" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M471" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N471" s="0" t="n">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B472" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="C472" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D472" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>9</v>
+      </c>
+      <c r="G472" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H472" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I472" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J472" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="K472" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="L472" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M472" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N472" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="n">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="n">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="n">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="n">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="n">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="n">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="n">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="n">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="n">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="n">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="n">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="n">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="n">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="n">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n">
+        <v>46305</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="n">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>46339</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>46342</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>46343</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>46344</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>46345</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>46347</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>46348</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>46349</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>46353</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>46354</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>46355</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>46362</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>46364</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>46365</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>46368</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>46370</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>46372</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>46373</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>46374</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>46375</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>46376</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="n">
+        <v>46377</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="n">
+        <v>46378</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="n">
+        <v>46379</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="n">
+        <v>46380</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="n">
+        <v>46381</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="n">
+        <v>46382</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="n">
+        <v>46383</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="n">
+        <v>46384</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="n">
+        <v>46385</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="n">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="n">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="n">
+        <v>46389</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="n">
+        <v>46390</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="n">
+        <v>46391</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="n">
+        <v>46392</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="n">
+        <v>46393</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="n">
+        <v>46394</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="n">
+        <v>46395</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="n">
+        <v>46396</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="n">
+        <v>46397</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="n">
+        <v>46398</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="n">
+        <v>46399</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="n">
+        <v>46400</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>46401</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="n">
+        <v>46402</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n">
+        <v>46403</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n">
+        <v>46404</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>46405</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
+        <v>46406</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
+        <v>46407</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n">
+        <v>46408</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>46409</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
+        <v>46410</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
+        <v>46411</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n">
+        <v>46412</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>46413</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n">
+        <v>46414</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n">
+        <v>46415</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>46416</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n">
+        <v>46417</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n">
+        <v>46419</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n">
+        <v>46420</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n">
+        <v>46421</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n">
+        <v>46422</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n">
+        <v>46423</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n">
+        <v>46424</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n">
+        <v>46425</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>46426</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>46427</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>46428</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>46429</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>46430</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>46431</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>46432</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>46433</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>46434</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>46435</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>46436</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>46437</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>46438</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>46439</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>46440</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>46441</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>46442</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>46443</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>46444</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>46445</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>46448</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>46449</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>46450</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="n">
+        <v>46451</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="n">
+        <v>46452</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="n">
+        <v>46453</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="n">
+        <v>46454</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="n">
+        <v>46455</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>46456</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>46457</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>46458</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>46459</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>46460</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>46461</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>46462</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>46463</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>46464</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="n">
+        <v>46465</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="n">
+        <v>46466</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="n">
+        <v>46467</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="n">
+        <v>46468</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="n">
+        <v>46469</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="n">
+        <v>46470</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="n">
+        <v>46471</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="n">
+        <v>46472</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="n">
+        <v>46473</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="n">
+        <v>46474</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="n">
+        <v>46475</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="n">
+        <v>46476</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" s="1" t="n"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="1" t="n"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="1" t="n"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20493,7 +23308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N444"/>
+  <dimension ref="A1:N718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9" outlineLevelCol="0"/>
   <cols>
     <col width="12.59765625" customWidth="1" style="2" min="1" max="1"/>
@@ -40395,45 +43210,45 @@
       <c r="A437" s="1" t="n">
         <v>46196</v>
       </c>
-      <c r="B437" t="n">
+      <c r="B437" s="0" t="n">
         <v>28.1</v>
       </c>
-      <c r="C437" t="n">
+      <c r="C437" s="0" t="n">
         <v>27.4</v>
       </c>
-      <c r="D437" t="n">
+      <c r="D437" s="0" t="n">
         <v>26.6</v>
       </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F437" t="n">
+      <c r="E437" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F437" s="0" t="n">
         <v>17.3</v>
       </c>
-      <c r="G437" t="n">
+      <c r="G437" s="0" t="n">
         <v>20.7</v>
       </c>
-      <c r="H437" t="n">
+      <c r="H437" s="0" t="n">
         <v>18.3</v>
       </c>
-      <c r="I437" t="n">
+      <c r="I437" s="0" t="n">
         <v>24.5</v>
       </c>
-      <c r="J437" t="n">
+      <c r="J437" s="0" t="n">
         <v>25.1</v>
       </c>
-      <c r="K437" t="n">
+      <c r="K437" s="0" t="n">
         <v>21</v>
       </c>
-      <c r="L437" t="n">
+      <c r="L437" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="M437" t="n">
+      <c r="M437" s="0" t="n">
         <v>20.2</v>
       </c>
-      <c r="N437" t="n">
+      <c r="N437" s="0" t="n">
         <v>15.4</v>
       </c>
     </row>
@@ -40441,35 +43256,2842 @@
       <c r="A438" s="1" t="n">
         <v>46197</v>
       </c>
+      <c r="B438" s="0" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="C438" s="0" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D438" s="0" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E438" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F438" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="G438" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H438" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I438" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="J438" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K438" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="L438" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M438" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="N438" s="0" t="n">
+        <v>24.2</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
         <v>46198</v>
       </c>
+      <c r="B439" s="0" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C439" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D439" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E439" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F439" s="0" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G439" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H439" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I439" s="0" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="J439" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K439" s="0" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="L439" s="0" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M439" s="0" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="N439" s="0" t="n">
+        <v>21.4</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
         <v>46199</v>
       </c>
+      <c r="B440" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="C440" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="D440" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E440" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F440" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G440" s="0" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H440" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I440" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="J440" s="0" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="K440" s="0" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="L440" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M440" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="N440" s="0" t="n">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
         <v>46200</v>
       </c>
+      <c r="B441" s="0" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="C441" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D441" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E441" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F441" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G441" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="H441" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I441" s="0" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="J441" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="K441" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="L441" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M441" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N441" s="0" t="n">
+        <v>24.7</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
         <v>46201</v>
       </c>
+      <c r="B442" s="0" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="C442" s="0" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D442" s="0" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E442" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F442" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G442" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H442" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="I442" s="0" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="J442" s="0" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K442" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L442" s="0" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M442" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N442" s="0" t="n">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
         <v>46202</v>
       </c>
+      <c r="B443" s="0" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="C443" s="0" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D443" s="0" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E443" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F443" s="0" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G443" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H443" s="0" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I443" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J443" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="K443" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L443" s="0" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M443" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="N443" s="0" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
         <v>46203</v>
+      </c>
+      <c r="B444" s="0" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="C444" s="0" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D444" s="0" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E444" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F444" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G444" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="H444" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I444" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="J444" s="0" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="K444" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="L444" s="0" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="M444" s="0" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="N444" s="0" t="n">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B445" s="0" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="C445" s="0" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="D445" s="0" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E445" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F445" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G445" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H445" s="0" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="I445" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="J445" s="0" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K445" s="0" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="L445" s="0" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="M445" s="0" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N445" s="0" t="n">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B446" s="0" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="C446" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D446" s="0" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E446" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F446" s="0" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G446" s="0" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H446" s="0" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="I446" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J446" s="0" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="K446" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="L446" s="0" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="M446" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N446" s="0" t="n">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B447" s="0" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="C447" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="D447" s="0" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E447" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F447" s="0" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G447" s="0" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="H447" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="I447" s="0" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J447" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="K447" s="0" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="L447" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="M447" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="N447" s="0" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B448" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C448" s="0" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="D448" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="E448" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F448" s="0" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="G448" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H448" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="I448" s="0" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="J448" s="0" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="K448" s="0" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L448" s="0" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="M448" s="0" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="N448" s="0" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B449" s="0" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="C449" s="0" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="D449" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="E449" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F449" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G449" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="H449" s="0" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I449" s="0" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="J449" s="0" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="K449" s="0" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="L449" s="0" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="M449" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="N449" s="0" t="n">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B450" s="0" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="C450" s="0" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="D450" s="0" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="E450" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F450" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G450" s="0" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="H450" s="0" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I450" s="0" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="J450" s="0" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="K450" s="0" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="L450" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="M450" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="N450" s="0" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B451" s="0" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="C451" s="0" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D451" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="E451" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F451" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G451" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="H451" s="0" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="I451" s="0" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J451" s="0" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K451" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="L451" s="0" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="M451" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="N451" s="0" t="n">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B452" s="0" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="C452" s="0" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="D452" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E452" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F452" s="0" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="G452" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H452" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="I452" s="0" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J452" s="0" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="K452" s="0" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="L452" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="M452" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="N452" s="0" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B453" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C453" s="0" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D453" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E453" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F453" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G453" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H453" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I453" s="0" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="J453" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K453" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="L453" s="0" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M453" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="N453" s="0" t="n">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B454" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C454" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="D454" s="0" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E454" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F454" s="0" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G454" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H454" s="0" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I454" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J454" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="K454" s="0" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="L454" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="M454" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N454" s="0" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B455" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="C455" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D455" s="0" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E455" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F455" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="G455" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H455" s="0" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I455" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J455" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K455" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L455" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M455" s="0" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="N455" s="0" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B456" s="0" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C456" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D456" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="E456" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F456" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="G456" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H456" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="I456" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J456" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K456" s="0" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L456" s="0" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M456" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N456" s="0" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B457" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C457" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D457" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E457" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F457" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G457" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H457" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="I457" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="J457" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="K457" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L457" s="0" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="M457" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="N457" s="0" t="n">
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B458" s="0" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="C458" s="0" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="D458" s="0" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E458" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F458" s="0" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G458" s="0" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H458" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I458" s="0" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J458" s="0" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="K458" s="0" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="L458" s="0" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="M458" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="N458" s="0" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B459" s="0" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="C459" s="0" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="D459" s="0" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E459" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F459" s="0" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G459" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="H459" s="0" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="I459" s="0" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J459" s="0" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="K459" s="0" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="L459" s="0" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="M459" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N459" s="0" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B460" s="0" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="C460" s="0" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="D460" s="0" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E460" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F460" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G460" s="0" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H460" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="I460" s="0" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="J460" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="K460" s="0" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L460" s="0" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="M460" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="N460" s="0" t="n">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B461" s="0" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="C461" s="0" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D461" s="0" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E461" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F461" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G461" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H461" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="I461" s="0" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="J461" s="0" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K461" s="0" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L461" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="M461" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="N461" s="0" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B462" s="0" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C462" s="0" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="D462" s="0" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E462" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F462" s="0" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G462" s="0" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H462" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="I462" s="0" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="J462" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="K462" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L462" s="0" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="M462" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N462" s="0" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B463" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="C463" s="0" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="D463" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E463" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F463" s="0" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G463" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H463" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I463" s="0" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="J463" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="K463" s="0" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="L463" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="M463" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N463" s="0" t="n">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B464" s="0" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C464" s="0" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D464" s="0" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E464" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F464" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="G464" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="H464" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I464" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J464" s="0" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="K464" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L464" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M464" s="0" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N464" s="0" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B465" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C465" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="D465" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E465" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F465" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G465" s="0" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H465" s="0" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I465" s="0" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="J465" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K465" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="L465" s="0" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M465" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="N465" s="0" t="n">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B466" s="0" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="C466" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="D466" s="0" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="E466" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F466" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G466" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H466" s="0" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="I466" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="J466" s="0" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K466" s="0" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="L466" s="0" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="M466" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="N466" s="0" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B467" s="0" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="C467" s="0" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="D467" s="0" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E467" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F467" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="G467" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H467" s="0" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="I467" s="0" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J467" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="K467" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="L467" s="0" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="M467" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="N467" s="0" t="n">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B468" s="0" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="C468" s="0" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="D468" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E468" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F468" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G468" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="H468" s="0" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="I468" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="J468" s="0" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="K468" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L468" s="0" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="M468" s="0" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N468" s="0" t="n">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B469" s="0" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="C469" s="0" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="D469" s="0" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E469" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F469" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G469" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H469" s="0" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I469" s="0" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J469" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="K469" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="L469" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="M469" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="N469" s="0" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B470" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="C470" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="D470" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E470" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F470" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G470" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="H470" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I470" s="0" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="J470" s="0" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="K470" s="0" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L470" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="M470" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="N470" s="0" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B471" s="0" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="C471" s="0" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="D471" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E471" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F471" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G471" s="0" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="H471" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I471" s="0" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J471" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K471" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L471" s="0" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="M471" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="N471" s="0" t="n">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B472" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="C472" t="n">
+        <v>27</v>
+      </c>
+      <c r="D472" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G472" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H472" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="I472" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J472" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K472" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="L472" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="M472" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N472" t="n">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="n">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="n">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="n">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="n">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="n">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="n">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="n">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="n">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="n">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="n">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="n">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="n">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="n">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="n">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n">
+        <v>46305</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="n">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>46339</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>46342</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>46343</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>46344</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>46345</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>46347</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>46348</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>46349</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>46353</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>46354</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>46355</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>46362</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>46364</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>46365</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>46368</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>46370</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>46372</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>46373</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="n">
+        <v>46374</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="n">
+        <v>46375</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="n">
+        <v>46376</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="n">
+        <v>46377</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="n">
+        <v>46378</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="n">
+        <v>46379</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="n">
+        <v>46380</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="n">
+        <v>46381</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="1" t="n">
+        <v>46382</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="1" t="n">
+        <v>46383</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="n">
+        <v>46384</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="n">
+        <v>46385</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="n">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="n">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="n">
+        <v>46389</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="n">
+        <v>46390</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="n">
+        <v>46391</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="n">
+        <v>46392</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="n">
+        <v>46393</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="n">
+        <v>46394</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="n">
+        <v>46395</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="n">
+        <v>46396</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="n">
+        <v>46397</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="n">
+        <v>46398</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="n">
+        <v>46399</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="n">
+        <v>46400</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="n">
+        <v>46401</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="n">
+        <v>46402</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="n">
+        <v>46403</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="n">
+        <v>46404</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="n">
+        <v>46405</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="n">
+        <v>46406</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="n">
+        <v>46407</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="n">
+        <v>46408</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="n">
+        <v>46409</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="n">
+        <v>46410</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="n">
+        <v>46411</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="n">
+        <v>46412</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="n">
+        <v>46413</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="n">
+        <v>46414</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="n">
+        <v>46415</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="n">
+        <v>46416</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="n">
+        <v>46417</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="n">
+        <v>46419</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="n">
+        <v>46420</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="n">
+        <v>46421</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="n">
+        <v>46422</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="n">
+        <v>46423</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="n">
+        <v>46424</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="n">
+        <v>46425</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="n">
+        <v>46426</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="n">
+        <v>46427</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="n">
+        <v>46428</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="n">
+        <v>46429</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="n">
+        <v>46430</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="n">
+        <v>46431</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="n">
+        <v>46432</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="n">
+        <v>46433</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="n">
+        <v>46434</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="n">
+        <v>46435</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="n">
+        <v>46436</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="n">
+        <v>46437</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="n">
+        <v>46438</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="n">
+        <v>46439</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="n">
+        <v>46440</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="n">
+        <v>46441</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="n">
+        <v>46442</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="n">
+        <v>46443</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="n">
+        <v>46444</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="n">
+        <v>46445</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="n">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="n">
+        <v>46448</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="n">
+        <v>46449</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="n">
+        <v>46450</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="n">
+        <v>46451</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="n">
+        <v>46452</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="n">
+        <v>46453</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="n">
+        <v>46454</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="n">
+        <v>46455</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="n">
+        <v>46456</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>46457</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>46458</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>46459</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>46460</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>46461</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>46462</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>46463</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" s="1" t="n">
+        <v>46464</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" s="1" t="n">
+        <v>46465</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" s="1" t="n">
+        <v>46466</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="n">
+        <v>46467</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="n">
+        <v>46468</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="n">
+        <v>46469</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="n">
+        <v>46470</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="n">
+        <v>46471</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="n">
+        <v>46472</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="n">
+        <v>46473</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="n">
+        <v>46474</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="n">
+        <v>46475</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="n">
+        <v>46476</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" s="1" t="n">
+        <v>46477</v>
       </c>
     </row>
   </sheetData>
@@ -40483,7 +46105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N212"/>
+  <dimension ref="A1:N551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9" outlineLevelCol="0"/>
   <cols>
     <col width="12.59765625" customWidth="1" style="2" min="1" max="1"/>
@@ -50899,51 +56521,51 @@
       <c r="A195" s="1" t="n">
         <v>46196</v>
       </c>
-      <c r="B195" t="n">
+      <c r="B195" s="0" t="n">
         <v>19.06</v>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F195" t="n">
+      <c r="C195" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D195" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E195" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F195" s="0" t="n">
         <v>11.39</v>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H195" t="n">
+      <c r="G195" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H195" s="0" t="n">
         <v>13.34</v>
       </c>
-      <c r="I195" t="n">
+      <c r="I195" s="0" t="n">
         <v>18.51</v>
       </c>
-      <c r="J195" t="n">
+      <c r="J195" s="0" t="n">
         <v>15.53</v>
       </c>
-      <c r="K195" t="n">
+      <c r="K195" s="0" t="n">
         <v>13.98</v>
       </c>
-      <c r="L195" t="n">
+      <c r="L195" s="0" t="n">
         <v>13.82</v>
       </c>
-      <c r="M195" t="n">
+      <c r="M195" s="0" t="n">
         <v>11.75</v>
       </c>
-      <c r="N195" t="n">
+      <c r="N195" s="0" t="n">
         <v>11.18</v>
       </c>
     </row>
@@ -50951,66 +56573,3280 @@
       <c r="A196" s="1" t="n">
         <v>46197</v>
       </c>
+      <c r="B196" s="0" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="C196" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D196" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E196" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F196" s="0" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="G196" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H196" s="0" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="I196" s="0" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="J196" s="0" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="K196" s="0" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="L196" s="0" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="M196" s="0" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="N196" s="0" t="n">
+        <v>15.06</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
         <v>46198</v>
       </c>
+      <c r="B197" s="0" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="C197" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D197" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E197" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F197" s="0" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="G197" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H197" s="0" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="I197" s="0" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="J197" s="0" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="K197" s="0" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="L197" s="0" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="M197" s="0" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="N197" s="0" t="n">
+        <v>15.83</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
         <v>46199</v>
       </c>
+      <c r="B198" s="0" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="C198" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D198" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E198" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F198" s="0" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="G198" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H198" s="0" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="I198" s="0" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="J198" s="0" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="K198" s="0" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="L198" s="0" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="M198" s="0" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="N198" s="0" t="n">
+        <v>15.75</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
         <v>46200</v>
       </c>
+      <c r="B199" s="0" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E199" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F199" s="0" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="G199" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H199" s="0" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="I199" s="0" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="J199" s="0" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="K199" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="L199" s="0" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="M199" s="0" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="N199" s="0" t="n">
+        <v>17.05</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
         <v>46201</v>
       </c>
+      <c r="B200" s="0" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E200" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F200" s="0" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="G200" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H200" s="0" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="I200" s="0" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="J200" s="0" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K200" s="0" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="L200" s="0" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="M200" s="0" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="N200" s="0" t="n">
+        <v>18.9</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
         <v>46202</v>
       </c>
+      <c r="B201" s="0" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E201" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F201" s="0" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G201" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H201" s="0" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="I201" s="0" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="J201" s="0" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="K201" s="0" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="L201" s="0" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="M201" s="0" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="N201" s="0" t="n">
+        <v>19.19</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
         <v>46203</v>
       </c>
+      <c r="B202" s="0" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D202" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E202" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F202" s="0" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="G202" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H202" s="0" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="I202" s="0" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="J202" s="0" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="K202" s="0" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="L202" s="0" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="M202" s="0" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="N202" s="0" t="n">
+        <v>20.13</v>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n"/>
+      <c r="A203" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B203" s="0" t="n">
+        <v>26.24</v>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D203" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E203" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F203" s="0" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="G203" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H203" s="0" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="I203" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J203" s="0" t="n">
+        <v>22.13</v>
+      </c>
+      <c r="K203" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="L203" s="0" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="M203" s="0" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="N203" s="0" t="n">
+        <v>22.09</v>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n"/>
+      <c r="A204" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B204" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D204" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E204" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F204" s="0" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G204" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H204" s="0" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="I204" s="0" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="J204" s="0" t="n">
+        <v>21.31</v>
+      </c>
+      <c r="K204" s="0" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="L204" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M204" s="0" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="N204" s="0" t="n">
+        <v>23.39</v>
+      </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n"/>
+      <c r="A205" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B205" s="0" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D205" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E205" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F205" s="0" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="G205" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H205" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I205" s="0" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="J205" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="K205" s="0" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="L205" s="0" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="M205" s="0" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="N205" s="0" t="n">
+        <v>18.25</v>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n"/>
+      <c r="A206" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B206" s="0" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E206" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F206" s="0" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="G206" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H206" s="0" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I206" s="0" t="n">
+        <v>25.69</v>
+      </c>
+      <c r="J206" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K206" s="0" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="L206" s="0" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="M206" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N206" s="0" t="n">
+        <v>16.93</v>
+      </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n"/>
+      <c r="A207" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="B207" s="0" t="n">
+        <v>30.54</v>
+      </c>
+      <c r="C207" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D207" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E207" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F207" s="0" t="n">
+        <v>20.63</v>
+      </c>
+      <c r="G207" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H207" s="0" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="I207" s="0" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="J207" s="0" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="K207" s="0" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="L207" s="0" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="M207" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N207" s="0" t="n">
+        <v>17.98</v>
+      </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n"/>
+      <c r="A208" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B208" s="0" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D208" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E208" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F208" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="G208" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H208" s="0" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="I208" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J208" s="0" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="K208" s="0" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="L208" s="0" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="M208" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N208" s="0" t="n">
+        <v>20.38</v>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n"/>
+      <c r="A209" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B209" s="0" t="n">
+        <v>23.69</v>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D209" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E209" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F209" s="0" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="G209" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H209" s="0" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="I209" s="0" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="J209" s="0" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="K209" s="0" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="L209" s="0" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="M209" s="0" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="N209" s="0" t="n">
+        <v>22.32</v>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n"/>
+      <c r="A210" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B210" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D210" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E210" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F210" s="0" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="G210" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H210" s="0" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="I210" s="0" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="J210" s="0" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="K210" s="0" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="L210" s="0" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="M210" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="N210" s="0" t="n">
+        <v>17.93</v>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n"/>
+      <c r="A211" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B211" s="0" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D211" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E211" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F211" s="0" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="G211" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H211" s="0" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="I211" s="0" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="J211" s="0" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="K211" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L211" s="0" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="M211" s="0" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="N211" s="0" t="n">
+        <v>19.04</v>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n"/>
+      <c r="A212" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B212" s="0" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="C212" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D212" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E212" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F212" s="0" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="G212" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H212" s="0" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="I212" s="0" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="J212" s="0" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="K212" s="0" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="L212" s="0" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="M212" s="0" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="N212" s="0" t="n">
+        <v>20.08</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B213" s="0" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D213" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E213" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F213" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G213" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H213" s="0" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="I213" s="0" t="n">
+        <v>16.88</v>
+      </c>
+      <c r="J213" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="K213" s="0" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="L213" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M213" s="0" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="N213" s="0" t="n">
+        <v>14.56</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B214" s="0" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D214" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E214" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F214" s="0" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="G214" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H214" s="0" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="I214" s="0" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="J214" s="0" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="K214" s="0" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="L214" s="0" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="M214" s="0" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="N214" s="0" t="n">
+        <v>11.26</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B215" s="0" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D215" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E215" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F215" s="0" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="G215" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H215" s="0" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="I215" s="0" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="J215" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K215" s="0" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="L215" s="0" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="M215" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="N215" s="0" t="n">
+        <v>14.56</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B216" s="0" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="C216" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D216" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E216" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F216" s="0" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="G216" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H216" s="0" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="I216" s="0" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="J216" s="0" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="K216" s="0" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="L216" s="0" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="M216" s="0" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="N216" s="0" t="n">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B217" s="0" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D217" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E217" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F217" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G217" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H217" s="0" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="I217" s="0" t="n">
+        <v>25.46</v>
+      </c>
+      <c r="J217" s="0" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="K217" s="0" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="L217" s="0" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="M217" s="0" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="N217" s="0" t="n">
+        <v>18.54</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B218" s="0" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D218" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E218" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F218" s="0" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="G218" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H218" s="0" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="I218" s="0" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="J218" s="0" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="K218" s="0" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="L218" s="0" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="M218" s="0" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="N218" s="0" t="n">
+        <v>17.41</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B219" s="0" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D219" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E219" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F219" s="0" t="n">
+        <v>15.36</v>
+      </c>
+      <c r="G219" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H219" s="0" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I219" s="0" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="J219" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="K219" s="0" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="L219" s="0" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="M219" s="0" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="N219" s="0" t="n">
+        <v>18.46</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B220" s="0" t="n">
+        <v>23.31</v>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D220" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E220" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F220" s="0" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="G220" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H220" s="0" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="I220" s="0" t="n">
+        <v>23.77</v>
+      </c>
+      <c r="J220" s="0" t="n">
+        <v>20.85</v>
+      </c>
+      <c r="K220" s="0" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="L220" s="0" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="M220" s="0" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="N220" s="0" t="n">
+        <v>19.76</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="B221" s="0" t="n">
+        <v>21.64</v>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D221" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E221" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F221" s="0" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="G221" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H221" s="0" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="I221" s="0" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="J221" s="0" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="K221" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L221" s="0" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="M221" s="0" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="N221" s="0" t="n">
+        <v>17.37</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B222" s="0" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D222" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E222" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F222" s="0" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="G222" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H222" s="0" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="I222" s="0" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="J222" s="0" t="n">
+        <v>16.56</v>
+      </c>
+      <c r="K222" s="0" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="L222" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="M222" s="0" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="N222" s="0" t="n">
+        <v>17.75</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B223" s="0" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D223" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E223" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F223" s="0" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="G223" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H223" s="0" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="I223" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J223" s="0" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="K223" s="0" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="L223" s="0" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="M223" s="0" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="N223" s="0" t="n">
+        <v>17.45</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B224" s="0" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D224" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E224" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F224" s="0" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="G224" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H224" s="0" t="n">
+        <v>21.82</v>
+      </c>
+      <c r="I224" s="0" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="J224" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="K224" s="0" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="L224" s="0" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="M224" s="0" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="N224" s="0" t="n">
+        <v>19.13</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B225" s="0" t="n">
+        <v>25.54</v>
+      </c>
+      <c r="C225" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D225" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E225" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F225" s="0" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="G225" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H225" s="0" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I225" s="0" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="J225" s="0" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="K225" s="0" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="L225" s="0" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="M225" s="0" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="N225" s="0" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B226" s="0" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D226" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E226" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F226" s="0" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="G226" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H226" s="0" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="I226" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J226" s="0" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="K226" s="0" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="L226" s="0" t="n">
+        <v>19.58</v>
+      </c>
+      <c r="M226" s="0" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="N226" s="0" t="n">
+        <v>24.56</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B227" s="0" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D227" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E227" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F227" s="0" t="n">
+        <v>15.97</v>
+      </c>
+      <c r="G227" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H227" s="0" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="I227" s="0" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="J227" s="0" t="n">
+        <v>16.31</v>
+      </c>
+      <c r="K227" s="0" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="L227" s="0" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="M227" s="0" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N227" s="0" t="n">
+        <v>25.74</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="B228" s="0" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D228" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E228" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F228" s="0" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="G228" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H228" s="0" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="I228" s="0" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="J228" s="0" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="K228" s="0" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="L228" s="0" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="M228" s="0" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="N228" s="0" t="n">
+        <v>23.98</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B229" s="0" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D229" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E229" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F229" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G229" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H229" s="0" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="I229" s="0" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="J229" s="0" t="n">
+        <v>18.44</v>
+      </c>
+      <c r="K229" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L229" s="0" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="M229" s="0" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="N229" s="0" t="n">
+        <v>21.06</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B230" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>15.99</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="I230" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="J230" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="K230" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="L230" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="M230" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="N230" t="n">
+        <v>21.06</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46239</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46243</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46246</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46247</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>46270</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>46272</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>46273</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>46278</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>46286</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="n">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="n">
+        <v>46289</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="n">
+        <v>46291</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="n">
+        <v>46292</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="n">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="n">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="1" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="1" t="n">
+        <v>46299</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="n">
+        <v>46300</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="n">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>46303</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>46305</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>46306</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>46307</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="n">
+        <v>46313</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="n">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
+        <v>46317</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="n">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="n">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="n">
+        <v>46320</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="n">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="n">
+        <v>46324</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="n">
+        <v>46327</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="n">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="n">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="n">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="n">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="1" t="n">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="1" t="n">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="1" t="n">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="1" t="n">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="n">
+        <v>46338</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="n">
+        <v>46339</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="n">
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="n">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="n">
+        <v>46342</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="n">
+        <v>46343</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="n">
+        <v>46344</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="n">
+        <v>46345</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="n">
+        <v>46346</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="n">
+        <v>46347</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="n">
+        <v>46348</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="n">
+        <v>46349</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="1" t="n">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="n">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="n">
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="n">
+        <v>46353</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="n">
+        <v>46354</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="n">
+        <v>46355</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="n">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="n">
+        <v>46358</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="n">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="n">
+        <v>46360</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="n">
+        <v>46361</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="n">
+        <v>46362</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="n">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="n">
+        <v>46364</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="n">
+        <v>46365</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="n">
+        <v>46366</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="n">
+        <v>46367</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="n">
+        <v>46368</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="n">
+        <v>46369</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="n">
+        <v>46370</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="n">
+        <v>46371</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="n">
+        <v>46372</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="n">
+        <v>46373</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="n">
+        <v>46374</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="n">
+        <v>46375</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="n">
+        <v>46376</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="n">
+        <v>46377</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="n">
+        <v>46378</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="n">
+        <v>46379</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="n">
+        <v>46380</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="n">
+        <v>46381</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="n">
+        <v>46382</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="n">
+        <v>46383</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>46384</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>46385</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>46386</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>46389</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>46390</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>46391</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>46392</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>46393</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>46394</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>46395</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="n">
+        <v>46396</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>46397</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>46398</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="n">
+        <v>46399</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="n">
+        <v>46400</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="n">
+        <v>46401</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="n">
+        <v>46402</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="n">
+        <v>46403</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>46404</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>46405</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>46406</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>46407</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>46408</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>46409</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>46410</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>46411</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>46412</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>46413</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>46414</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>46415</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>46416</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>46417</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>46419</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>46420</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46421</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>46422</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46423</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46424</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46425</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46426</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46427</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46428</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46429</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46430</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46431</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46432</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46433</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46434</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46435</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46436</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46437</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46438</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46439</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46440</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46441</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46442</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46443</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46444</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46445</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>46447</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>46448</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>46449</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>46450</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>46451</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>46452</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>46453</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>46454</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>46455</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>46456</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>46457</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>46458</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>46459</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>46460</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>46461</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>46462</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>46463</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>46464</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>46465</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>46466</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>46467</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>46468</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>46469</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>46470</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>46471</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46472</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46473</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46474</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46475</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46476</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="n"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="n"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="n"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="n"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="n"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="n"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="n"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="n"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -22013,45 +22013,45 @@
       <c r="A472" s="1" t="n">
         <v>46231</v>
       </c>
-      <c r="B472" t="n">
+      <c r="B472" s="0" t="n">
         <v>15.9</v>
       </c>
-      <c r="C472" t="n">
+      <c r="C472" s="0" t="n">
         <v>13.2</v>
       </c>
-      <c r="D472" t="n">
+      <c r="D472" s="0" t="n">
         <v>14.4</v>
       </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F472" t="n">
+      <c r="E472" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F472" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="G472" t="n">
+      <c r="G472" s="0" t="n">
         <v>13.4</v>
       </c>
-      <c r="H472" t="n">
+      <c r="H472" s="0" t="n">
         <v>18.3</v>
       </c>
-      <c r="I472" t="n">
+      <c r="I472" s="0" t="n">
         <v>11.3</v>
       </c>
-      <c r="J472" t="n">
+      <c r="J472" s="0" t="n">
         <v>14.3</v>
       </c>
-      <c r="K472" t="n">
+      <c r="K472" s="0" t="n">
         <v>10.7</v>
       </c>
-      <c r="L472" t="n">
+      <c r="L472" s="0" t="n">
         <v>11.9</v>
       </c>
-      <c r="M472" t="n">
+      <c r="M472" s="0" t="n">
         <v>12.3</v>
       </c>
-      <c r="N472" t="n">
+      <c r="N472" s="0" t="n">
         <v>17</v>
       </c>
     </row>
@@ -22059,120 +22059,1112 @@
       <c r="A473" s="1" t="n">
         <v>46232</v>
       </c>
+      <c r="B473" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="C473" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="D473" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E473" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F473" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="G473" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H473" s="0" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="I473" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="J473" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K473" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="L473" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M473" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N473" s="0" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
         <v>46233</v>
       </c>
+      <c r="B474" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C474" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="D474" s="0" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E474" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F474" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="G474" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H474" s="0" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I474" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J474" s="0" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="K474" s="0" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L474" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M474" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N474" s="0" t="n">
+        <v>16.6</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
         <v>46234</v>
       </c>
+      <c r="B475" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C475" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D475" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="E475" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F475" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G475" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H475" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="I475" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J475" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K475" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L475" s="0" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M475" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N475" s="0" t="n">
+        <v>12.8</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
         <v>46235</v>
       </c>
+      <c r="B476" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="C476" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="D476" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E476" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F476" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G476" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H476" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I476" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="J476" s="0" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K476" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L476" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M476" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N476" s="0" t="n">
+        <v>14.9</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
         <v>46236</v>
       </c>
+      <c r="B477" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="C477" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D477" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="E477" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F477" s="0" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G477" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H477" s="0" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="I477" s="0" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J477" s="0" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K477" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L477" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M477" s="0" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="N477" s="0" t="n">
+        <v>12.9</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
         <v>46237</v>
       </c>
+      <c r="B478" s="0" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="C478" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D478" s="0" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="E478" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F478" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="G478" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H478" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I478" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J478" s="0" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K478" s="0" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="L478" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="M478" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N478" s="0" t="n">
+        <v>13.2</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
         <v>46238</v>
       </c>
+      <c r="B479" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C479" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="D479" s="0" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="E479" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F479" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G479" s="0" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H479" s="0" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I479" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J479" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K479" s="0" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L479" s="0" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M479" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="N479" s="0" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
         <v>46239</v>
       </c>
+      <c r="B480" s="0" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C480" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="D480" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="E480" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F480" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G480" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H480" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I480" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="J480" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K480" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L480" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M480" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N480" s="0" t="n">
+        <v>15.8</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
         <v>46240</v>
       </c>
+      <c r="B481" s="0" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="C481" s="0" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D481" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="E481" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F481" s="0" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="G481" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H481" s="0" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I481" s="0" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J481" s="0" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="K481" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="L481" s="0" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="M481" s="0" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N481" s="0" t="n">
+        <v>14.6</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
         <v>46241</v>
       </c>
+      <c r="B482" s="0" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C482" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D482" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="E482" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F482" s="0" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G482" s="0" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H482" s="0" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I482" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J482" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="K482" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="L482" s="0" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M482" s="0" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="N482" s="0" t="n">
+        <v>17.3</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
         <v>46242</v>
       </c>
+      <c r="B483" s="0" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C483" s="0" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="D483" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E483" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F483" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="G483" s="0" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H483" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I483" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J483" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="K483" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="L483" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="M483" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N483" s="0" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
         <v>46243</v>
       </c>
+      <c r="B484" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="C484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H484" s="0" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I484" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J484" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="K484" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L484" s="0" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="M484" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N484" s="0" t="n">
+        <v>13.1</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
         <v>46244</v>
       </c>
+      <c r="B485" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="C485" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D485" s="0" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E485" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F485" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G485" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H485" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I485" s="0" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J485" s="0" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K485" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L485" s="0" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M485" s="0" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N485" s="0" t="n">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
         <v>46245</v>
       </c>
+      <c r="B486" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C486" s="0" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D486" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="E486" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F486" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G486" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H486" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I486" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J486" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K486" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L486" s="0" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M486" s="0" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N486" s="0" t="n">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="n">
         <v>46246</v>
       </c>
+      <c r="B487" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="C487" s="0" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D487" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="E487" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F487" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G487" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H487" s="0" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I487" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J487" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K487" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L487" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="M487" s="0" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N487" s="0" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="n">
         <v>46247</v>
       </c>
+      <c r="B488" s="0" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="C488" s="0" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="D488" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E488" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F488" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="G488" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H488" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I488" s="0" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J488" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K488" s="0" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="L488" s="0" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M488" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N488" s="0" t="n">
+        <v>13.8</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="n">
         <v>46248</v>
       </c>
+      <c r="B489" s="0" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C489" s="0" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D489" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E489" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F489" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G489" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H489" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="I489" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J489" s="0" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K489" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L489" s="0" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M489" s="0" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N489" s="0" t="n">
+        <v>11.9</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="n">
         <v>46249</v>
       </c>
+      <c r="B490" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C490" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="D490" s="0" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E490" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F490" s="0" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G490" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H490" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I490" s="0" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J490" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K490" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="L490" s="0" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="M490" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N490" s="0" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="1" t="n">
         <v>46250</v>
       </c>
+      <c r="B491" s="0" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C491" s="0" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="D491" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E491" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F491" s="0" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G491" s="0" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H491" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I491" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="J491" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K491" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L491" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M491" s="0" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N491" s="0" t="n">
+        <v>11.9</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="n">
         <v>46251</v>
       </c>
+      <c r="B492" s="0" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C492" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="D492" s="0" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="E492" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F492" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G492" s="0" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H492" s="0" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I492" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J492" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K492" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="L492" s="0" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M492" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="N492" s="0" t="n">
+        <v>14.3</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="n">
         <v>46252</v>
       </c>
+      <c r="B493" s="0" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="C493" s="0" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D493" s="0" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E493" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F493" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G493" s="0" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H493" s="0" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I493" s="0" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J493" s="0" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K493" s="0" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L493" s="0" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M493" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="N493" s="0" t="n">
+        <v>12.9</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
         <v>46253</v>
       </c>
+      <c r="B494" s="0" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C494" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D494" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E494" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F494" s="0" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G494" s="0" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H494" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="I494" s="0" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J494" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K494" s="0" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L494" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M494" s="0" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N494" s="0" t="n">
+        <v>11.2</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="n">
         <v>46254</v>
       </c>
+      <c r="B495" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C495" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="D495" s="0" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E495" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F495" s="0" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G495" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H495" s="0" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I495" s="0" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J495" s="0" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K495" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L495" s="0" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M495" s="0" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N495" s="0" t="n">
+        <v>8.800000000000001</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="n">
         <v>46255</v>
+      </c>
+      <c r="B496" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="C496" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="D496" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F496" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G496" t="n">
+        <v>7</v>
+      </c>
+      <c r="H496" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I496" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J496" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K496" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="L496" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="M496" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N496" t="n">
+        <v>12.7</v>
       </c>
     </row>
     <row r="497">
@@ -44822,45 +45814,45 @@
       <c r="A472" s="1" t="n">
         <v>46231</v>
       </c>
-      <c r="B472" t="n">
+      <c r="B472" s="0" t="n">
         <v>27.1</v>
       </c>
-      <c r="C472" t="n">
+      <c r="C472" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="D472" t="n">
+      <c r="D472" s="0" t="n">
         <v>25.7</v>
       </c>
-      <c r="E472" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F472" t="n">
+      <c r="E472" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F472" s="0" t="n">
         <v>23.9</v>
       </c>
-      <c r="G472" t="n">
+      <c r="G472" s="0" t="n">
         <v>23.6</v>
       </c>
-      <c r="H472" t="n">
+      <c r="H472" s="0" t="n">
         <v>26.6</v>
       </c>
-      <c r="I472" t="n">
+      <c r="I472" s="0" t="n">
         <v>27.8</v>
       </c>
-      <c r="J472" t="n">
+      <c r="J472" s="0" t="n">
         <v>24.2</v>
       </c>
-      <c r="K472" t="n">
+      <c r="K472" s="0" t="n">
         <v>21.7</v>
       </c>
-      <c r="L472" t="n">
+      <c r="L472" s="0" t="n">
         <v>26.3</v>
       </c>
-      <c r="M472" t="n">
+      <c r="M472" s="0" t="n">
         <v>23.7</v>
       </c>
-      <c r="N472" t="n">
+      <c r="N472" s="0" t="n">
         <v>28.8</v>
       </c>
     </row>
@@ -44868,120 +45860,1114 @@
       <c r="A473" s="1" t="n">
         <v>46232</v>
       </c>
+      <c r="B473" s="0" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C473" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D473" s="0" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E473" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F473" s="0" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G473" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H473" s="0" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I473" s="0" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="J473" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="K473" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="L473" s="0" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="M473" s="0" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="N473" s="0" t="n">
+        <v>22.9</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
         <v>46233</v>
       </c>
+      <c r="B474" s="0" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="C474" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D474" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E474" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F474" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G474" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H474" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I474" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J474" s="0" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K474" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="L474" s="0" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="M474" s="0" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N474" s="0" t="n">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
         <v>46234</v>
       </c>
+      <c r="B475" s="0" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="C475" s="0" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="D475" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="E475" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F475" s="0" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G475" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H475" s="0" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="I475" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="J475" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="K475" s="0" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L475" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="M475" s="0" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="N475" s="0" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
         <v>46235</v>
       </c>
+      <c r="B476" s="0" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="C476" s="0" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D476" s="0" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E476" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F476" s="0" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G476" s="0" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H476" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="I476" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J476" s="0" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K476" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="L476" s="0" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M476" s="0" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N476" s="0" t="n">
+        <v>25.9</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
         <v>46236</v>
       </c>
+      <c r="B477" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C477" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="D477" s="0" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E477" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F477" s="0" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="G477" s="0" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="H477" s="0" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I477" s="0" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J477" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K477" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L477" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="M477" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="N477" s="0" t="n">
+        <v>23.1</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
         <v>46237</v>
       </c>
+      <c r="B478" s="0" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C478" s="0" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="D478" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E478" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F478" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G478" s="0" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H478" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="I478" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J478" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K478" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="L478" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="M478" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="N478" s="0" t="n">
+        <v>25.9</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
         <v>46238</v>
       </c>
+      <c r="B479" s="0" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="C479" s="0" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="D479" s="0" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E479" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F479" s="0" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G479" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H479" s="0" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I479" s="0" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J479" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="K479" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="L479" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="M479" s="0" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="N479" s="0" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
         <v>46239</v>
       </c>
+      <c r="B480" s="0" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="C480" s="0" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D480" s="0" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E480" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F480" s="0" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G480" s="0" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H480" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I480" s="0" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="J480" s="0" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K480" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="L480" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="M480" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="N480" s="0" t="n">
+        <v>26.2</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
         <v>46240</v>
       </c>
+      <c r="B481" s="0" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C481" s="0" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D481" s="0" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E481" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F481" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G481" s="0" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H481" s="0" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="I481" s="0" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J481" s="0" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="K481" s="0" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="L481" s="0" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="M481" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="N481" s="0" t="n">
+        <v>28.4</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
         <v>46241</v>
       </c>
+      <c r="B482" s="0" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="C482" s="0" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="D482" s="0" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E482" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F482" s="0" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G482" s="0" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="H482" s="0" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I482" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J482" s="0" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K482" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="L482" s="0" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="M482" s="0" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="N482" s="0" t="n">
+        <v>27.3</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
         <v>46242</v>
       </c>
+      <c r="B483" s="0" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="C483" s="0" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D483" s="0" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E483" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F483" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G483" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H483" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="I483" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="J483" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K483" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="L483" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M483" s="0" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N483" s="0" t="n">
+        <v>30.3</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
         <v>46243</v>
       </c>
+      <c r="B484" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G484" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H484" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I484" s="0" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="J484" s="0" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K484" s="0" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="L484" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="M484" s="0" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N484" s="0" t="n">
+        <v>27.8</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
         <v>46244</v>
       </c>
+      <c r="B485" s="0" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C485" s="0" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D485" s="0" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E485" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F485" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G485" s="0" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H485" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="I485" s="0" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="J485" s="0" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="K485" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="L485" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="M485" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N485" s="0" t="n">
+        <v>18.3</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
         <v>46245</v>
       </c>
+      <c r="B486" s="0" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="C486" s="0" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D486" s="0" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E486" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F486" s="0" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G486" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="H486" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="I486" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="J486" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="K486" s="0" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="L486" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="M486" s="0" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="N486" s="0" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="n">
         <v>46246</v>
       </c>
+      <c r="B487" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="C487" s="0" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D487" s="0" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E487" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F487" s="0" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G487" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H487" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="I487" s="0" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J487" s="0" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="K487" s="0" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="L487" s="0" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="M487" s="0" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="N487" s="0" t="n">
+        <v>25.9</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="n">
         <v>46247</v>
       </c>
+      <c r="B488" s="0" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="C488" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="D488" s="0" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E488" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F488" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="G488" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="H488" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I488" s="0" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="J488" s="0" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="K488" s="0" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="L488" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M488" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="N488" s="0" t="n">
+        <v>28.6</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="n">
         <v>46248</v>
       </c>
+      <c r="B489" s="0" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="C489" s="0" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="D489" s="0" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E489" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F489" s="0" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G489" s="0" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H489" s="0" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I489" s="0" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="J489" s="0" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K489" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="L489" s="0" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="M489" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N489" s="0" t="n">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="n">
         <v>46249</v>
       </c>
+      <c r="B490" s="0" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C490" s="0" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D490" s="0" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E490" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F490" s="0" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G490" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H490" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I490" s="0" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="J490" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K490" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="L490" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="M490" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N490" s="0" t="n">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="1" t="n">
         <v>46250</v>
       </c>
+      <c r="B491" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="C491" s="0" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D491" s="0" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E491" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F491" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G491" s="0" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H491" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="I491" s="0" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="J491" s="0" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="K491" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="L491" s="0" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M491" s="0" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="N491" s="0" t="n">
+        <v>27</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="n">
         <v>46251</v>
       </c>
+      <c r="B492" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="C492" s="0" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="D492" s="0" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E492" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F492" s="0" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G492" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H492" s="0" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I492" s="0" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="J492" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K492" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L492" s="0" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="M492" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N492" s="0" t="n">
+        <v>24.6</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="n">
         <v>46252</v>
       </c>
+      <c r="B493" s="0" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="C493" s="0" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D493" s="0" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E493" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F493" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G493" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="H493" s="0" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="I493" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J493" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="K493" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="L493" s="0" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M493" s="0" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N493" s="0" t="n">
+        <v>24.4</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
         <v>46253</v>
       </c>
+      <c r="B494" s="0" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="C494" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="D494" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E494" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F494" s="0" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G494" s="0" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H494" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="I494" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="J494" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K494" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="L494" s="0" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="M494" s="0" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N494" s="0" t="n">
+        <v>17.3</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="n">
         <v>46254</v>
       </c>
+      <c r="B495" s="0" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="C495" s="0" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D495" s="0" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E495" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F495" s="0" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G495" s="0" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H495" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I495" s="0" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="J495" s="0" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="K495" s="0" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L495" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="M495" s="0" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N495" s="0" t="n">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="n">
         <v>46255</v>
+      </c>
+      <c r="B496" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="C496" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="D496" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F496" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G496" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H496" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="I496" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J496" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="K496" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L496" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M496" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="N496" t="n">
+        <v>24.3</v>
       </c>
     </row>
     <row r="497">
@@ -58345,51 +60331,51 @@
       <c r="A230" s="1" t="n">
         <v>46231</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B230" s="0" t="n">
         <v>20.4</v>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F230" t="n">
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E230" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F230" s="0" t="n">
         <v>15.99</v>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H230" t="n">
+      <c r="G230" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H230" s="0" t="n">
         <v>21.16</v>
       </c>
-      <c r="I230" t="n">
+      <c r="I230" s="0" t="n">
         <v>19.64</v>
       </c>
-      <c r="J230" t="n">
+      <c r="J230" s="0" t="n">
         <v>18.24</v>
       </c>
-      <c r="K230" t="n">
+      <c r="K230" s="0" t="n">
         <v>16.04</v>
       </c>
-      <c r="L230" t="n">
+      <c r="L230" s="0" t="n">
         <v>18.43</v>
       </c>
-      <c r="M230" t="n">
+      <c r="M230" s="0" t="n">
         <v>17.36</v>
       </c>
-      <c r="N230" t="n">
+      <c r="N230" s="0" t="n">
         <v>21.06</v>
       </c>
     </row>
@@ -58397,120 +60383,1252 @@
       <c r="A231" s="1" t="n">
         <v>46232</v>
       </c>
+      <c r="B231" s="0" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D231" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E231" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F231" s="0" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="G231" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H231" s="0" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="I231" s="0" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="J231" s="0" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="K231" s="0" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="L231" s="0" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="M231" s="0" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="N231" s="0" t="n">
+        <v>20.36</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
         <v>46233</v>
       </c>
+      <c r="B232" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D232" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E232" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F232" s="0" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="G232" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H232" s="0" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="I232" s="0" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="J232" s="0" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="K232" s="0" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="L232" s="0" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="M232" s="0" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="N232" s="0" t="n">
+        <v>17.88</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
         <v>46234</v>
       </c>
+      <c r="B233" s="0" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D233" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E233" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F233" s="0" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="G233" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H233" s="0" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="I233" s="0" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J233" s="0" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="K233" s="0" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L233" s="0" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="M233" s="0" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N233" s="0" t="n">
+        <v>18.94</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
         <v>46235</v>
       </c>
+      <c r="B234" s="0" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="C234" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D234" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E234" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F234" s="0" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="G234" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H234" s="0" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="I234" s="0" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="J234" s="0" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K234" s="0" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="L234" s="0" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="M234" s="0" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="N234" s="0" t="n">
+        <v>19.01</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
         <v>46236</v>
       </c>
+      <c r="B235" s="0" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D235" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E235" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F235" s="0" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="G235" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H235" s="0" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="I235" s="0" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="J235" s="0" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="K235" s="0" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="L235" s="0" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="M235" s="0" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="N235" s="0" t="n">
+        <v>17.81</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
         <v>46237</v>
       </c>
+      <c r="B236" s="0" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D236" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E236" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F236" s="0" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="G236" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H236" s="0" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="I236" s="0" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="J236" s="0" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="K236" s="0" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="L236" s="0" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="M236" s="0" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="N236" s="0" t="n">
+        <v>19.48</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
         <v>46238</v>
       </c>
+      <c r="B237" s="0" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D237" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E237" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F237" s="0" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="G237" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H237" s="0" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="I237" s="0" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="J237" s="0" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="K237" s="0" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="L237" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="M237" s="0" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="N237" s="0" t="n">
+        <v>20.86</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
         <v>46239</v>
       </c>
+      <c r="B238" s="0" t="n">
+        <v>25.28</v>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D238" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E238" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F238" s="0" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G238" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H238" s="0" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="I238" s="0" t="n">
+        <v>22.81</v>
+      </c>
+      <c r="J238" s="0" t="n">
+        <v>22.02</v>
+      </c>
+      <c r="K238" s="0" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="L238" s="0" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="M238" s="0" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="N238" s="0" t="n">
+        <v>21.16</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
         <v>46240</v>
       </c>
+      <c r="B239" s="0" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D239" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E239" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F239" s="0" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="G239" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H239" s="0" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="I239" s="0" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="J239" s="0" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="K239" s="0" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="L239" s="0" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M239" s="0" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="N239" s="0" t="n">
+        <v>21.44</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
         <v>46241</v>
       </c>
+      <c r="B240" s="0" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D240" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E240" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F240" s="0" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="G240" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H240" s="0" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="I240" s="0" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="J240" s="0" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="K240" s="0" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="L240" s="0" t="n">
+        <v>20.65</v>
+      </c>
+      <c r="M240" s="0" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="N240" s="0" t="n">
+        <v>22.13</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
         <v>46242</v>
       </c>
+      <c r="B241" s="0" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D241" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E241" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F241" s="0" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="G241" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H241" s="0" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="I241" s="0" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="J241" s="0" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="K241" s="0" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="L241" s="0" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="M241" s="0" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="N241" s="0" t="n">
+        <v>24.06</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
         <v>46243</v>
       </c>
+      <c r="B242" s="0" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D242" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E242" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F242" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G242" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H242" s="0" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="I242" s="0" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="J242" s="0" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="K242" s="0" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="L242" s="0" t="n">
+        <v>15.19</v>
+      </c>
+      <c r="M242" s="0" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="N242" s="0" t="n">
+        <v>18.96</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
         <v>46244</v>
       </c>
+      <c r="B243" s="0" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="C243" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D243" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E243" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F243" s="0" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="G243" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H243" s="0" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="I243" s="0" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="J243" s="0" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="K243" s="0" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="L243" s="0" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="M243" s="0" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="N243" s="0" t="n">
+        <v>14.36</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
         <v>46245</v>
       </c>
+      <c r="B244" s="0" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D244" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E244" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F244" s="0" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="G244" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H244" s="0" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="I244" s="0" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="J244" s="0" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="K244" s="0" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="L244" s="0" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="M244" s="0" t="n">
+        <v>15.54</v>
+      </c>
+      <c r="N244" s="0" t="n">
+        <v>14.88</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
         <v>46246</v>
       </c>
+      <c r="B245" s="0" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D245" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E245" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F245" s="0" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="G245" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H245" s="0" t="n">
+        <v>17.59</v>
+      </c>
+      <c r="I245" s="0" t="n">
+        <v>23.49</v>
+      </c>
+      <c r="J245" s="0" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="K245" s="0" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="L245" s="0" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="M245" s="0" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="N245" s="0" t="n">
+        <v>17.52</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
         <v>46247</v>
       </c>
+      <c r="B246" s="0" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D246" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E246" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F246" s="0" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="G246" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H246" s="0" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="I246" s="0" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="J246" s="0" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="K246" s="0" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="L246" s="0" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="M246" s="0" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="N246" s="0" t="n">
+        <v>20.71</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
         <v>46248</v>
       </c>
+      <c r="B247" s="0" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E247" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F247" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G247" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H247" s="0" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="I247" s="0" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="J247" s="0" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="K247" s="0" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="L247" s="0" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="M247" s="0" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="N247" s="0" t="n">
+        <v>17.19</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
         <v>46249</v>
       </c>
+      <c r="B248" s="0" t="n">
+        <v>21.79</v>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E248" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F248" s="0" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G248" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H248" s="0" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I248" s="0" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="J248" s="0" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="K248" s="0" t="n">
+        <v>15.81</v>
+      </c>
+      <c r="L248" s="0" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M248" s="0" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="N248" s="0" t="n">
+        <v>15.99</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
         <v>46250</v>
       </c>
+      <c r="B249" s="0" t="n">
+        <v>20.55</v>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D249" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E249" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F249" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G249" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H249" s="0" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="I249" s="0" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="J249" s="0" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="K249" s="0" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="L249" s="0" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="M249" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N249" s="0" t="n">
+        <v>17.85</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
         <v>46251</v>
       </c>
+      <c r="B250" s="0" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D250" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E250" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F250" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G250" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H250" s="0" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="I250" s="0" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="J250" s="0" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="K250" s="0" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="L250" s="0" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M250" s="0" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="N250" s="0" t="n">
+        <v>18.74</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
         <v>46252</v>
       </c>
+      <c r="B251" s="0" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D251" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E251" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F251" s="0" t="n">
+        <v>15.43</v>
+      </c>
+      <c r="G251" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H251" s="0" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="I251" s="0" t="n">
+        <v>19.16</v>
+      </c>
+      <c r="J251" s="0" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="K251" s="0" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="L251" s="0" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="M251" s="0" t="n">
+        <v>14.41</v>
+      </c>
+      <c r="N251" s="0" t="n">
+        <v>17.04</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
         <v>46253</v>
       </c>
+      <c r="B252" s="0" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="C252" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D252" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E252" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F252" s="0" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="G252" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H252" s="0" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="I252" s="0" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="J252" s="0" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="K252" s="0" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="L252" s="0" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="M252" s="0" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="N252" s="0" t="n">
+        <v>14.36</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
         <v>46254</v>
       </c>
+      <c r="B253" s="0" t="n">
+        <v>18.36</v>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D253" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E253" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F253" s="0" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="G253" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H253" s="0" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="I253" s="0" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="J253" s="0" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="K253" s="0" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L253" s="0" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="M253" s="0" t="n">
+        <v>13.56</v>
+      </c>
+      <c r="N253" s="0" t="n">
+        <v>15.5</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
         <v>46255</v>
+      </c>
+      <c r="B254" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>19.01</v>
+      </c>
+      <c r="I254" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="J254" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="K254" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="L254" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="M254" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="N254" t="n">
+        <v>18.19</v>
       </c>
     </row>
     <row r="255">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -23125,51 +23125,92 @@
       <c r="A496" s="1" t="n">
         <v>46255</v>
       </c>
-      <c r="B496" t="n">
+      <c r="B496" s="0" t="n">
         <v>12.4</v>
       </c>
-      <c r="C496" t="n">
+      <c r="C496" s="0" t="n">
         <v>12.7</v>
       </c>
-      <c r="D496" t="n">
+      <c r="D496" s="0" t="n">
         <v>10.7</v>
       </c>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F496" t="n">
+      <c r="E496" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F496" s="0" t="n">
         <v>9.9</v>
       </c>
-      <c r="G496" t="n">
+      <c r="G496" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="H496" t="n">
+      <c r="H496" s="0" t="n">
         <v>10.6</v>
       </c>
-      <c r="I496" t="n">
+      <c r="I496" s="0" t="n">
         <v>11.5</v>
       </c>
-      <c r="J496" t="n">
+      <c r="J496" s="0" t="n">
         <v>12.8</v>
       </c>
-      <c r="K496" t="n">
+      <c r="K496" s="0" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="L496" t="n">
+      <c r="L496" s="0" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="M496" t="n">
+      <c r="M496" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="N496" t="n">
+      <c r="N496" s="0" t="n">
         <v>12.7</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="n">
         <v>46256</v>
+      </c>
+      <c r="B497" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C497" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="D497" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F497" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="G497" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H497" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I497" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J497" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K497" t="n">
+        <v>6</v>
+      </c>
+      <c r="L497" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="M497" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N497" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="498">
@@ -46928,51 +46969,92 @@
       <c r="A496" s="1" t="n">
         <v>46255</v>
       </c>
-      <c r="B496" t="n">
+      <c r="B496" s="0" t="n">
         <v>25.5</v>
       </c>
-      <c r="C496" t="n">
+      <c r="C496" s="0" t="n">
         <v>26.6</v>
       </c>
-      <c r="D496" t="n">
+      <c r="D496" s="0" t="n">
         <v>27.7</v>
       </c>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F496" t="n">
+      <c r="E496" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F496" s="0" t="n">
         <v>23.3</v>
       </c>
-      <c r="G496" t="n">
+      <c r="G496" s="0" t="n">
         <v>21.7</v>
       </c>
-      <c r="H496" t="n">
+      <c r="H496" s="0" t="n">
         <v>28.2</v>
       </c>
-      <c r="I496" t="n">
+      <c r="I496" s="0" t="n">
         <v>24.4</v>
       </c>
-      <c r="J496" t="n">
+      <c r="J496" s="0" t="n">
         <v>26.8</v>
       </c>
-      <c r="K496" t="n">
+      <c r="K496" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="L496" t="n">
+      <c r="L496" s="0" t="n">
         <v>24.9</v>
       </c>
-      <c r="M496" t="n">
+      <c r="M496" s="0" t="n">
         <v>24.1</v>
       </c>
-      <c r="N496" t="n">
+      <c r="N496" s="0" t="n">
         <v>24.3</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="n">
         <v>46256</v>
+      </c>
+      <c r="B497" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C497" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D497" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F497" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G497" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H497" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I497" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J497" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K497" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="L497" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="M497" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="N497" t="n">
+        <v>24.8</v>
       </c>
     </row>
     <row r="498">
@@ -61583,57 +61665,104 @@
       <c r="A254" s="1" t="n">
         <v>46255</v>
       </c>
-      <c r="B254" t="n">
+      <c r="B254" s="0" t="n">
         <v>19.7</v>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F254" t="n">
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D254" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E254" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F254" s="0" t="n">
         <v>17.3</v>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H254" t="n">
+      <c r="G254" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H254" s="0" t="n">
         <v>19.01</v>
       </c>
-      <c r="I254" t="n">
+      <c r="I254" s="0" t="n">
         <v>17.76</v>
       </c>
-      <c r="J254" t="n">
+      <c r="J254" s="0" t="n">
         <v>18.89</v>
       </c>
-      <c r="K254" t="n">
+      <c r="K254" s="0" t="n">
         <v>15.05</v>
       </c>
-      <c r="L254" t="n">
+      <c r="L254" s="0" t="n">
         <v>16.84</v>
       </c>
-      <c r="M254" t="n">
+      <c r="M254" s="0" t="n">
         <v>15.12</v>
       </c>
-      <c r="N254" t="n">
+      <c r="N254" s="0" t="n">
         <v>18.19</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
         <v>46256</v>
+      </c>
+      <c r="B255" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="I255" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="J255" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="K255" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L255" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="M255" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="N255" t="n">
+        <v>17.82</v>
       </c>
     </row>
     <row r="256">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -23497,51 +23497,92 @@
       <c r="A504" s="1" t="n">
         <v>46263</v>
       </c>
-      <c r="B504" t="n">
+      <c r="B504" s="0" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="C504" t="n">
+      <c r="C504" s="0" t="n">
         <v>6.5</v>
       </c>
-      <c r="D504" t="n">
+      <c r="D504" s="0" t="n">
         <v>5.4</v>
       </c>
-      <c r="E504" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F504" t="n">
+      <c r="E504" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F504" s="0" t="n">
         <v>-1.1</v>
       </c>
-      <c r="G504" t="n">
+      <c r="G504" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="H504" t="n">
+      <c r="H504" s="0" t="n">
         <v>4.5</v>
       </c>
-      <c r="I504" t="n">
+      <c r="I504" s="0" t="n">
         <v>7.8</v>
       </c>
-      <c r="J504" t="n">
+      <c r="J504" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="K504" t="n">
+      <c r="K504" s="0" t="n">
         <v>-0.8</v>
       </c>
-      <c r="L504" t="n">
+      <c r="L504" s="0" t="n">
         <v>1.5</v>
       </c>
-      <c r="M504" t="n">
+      <c r="M504" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="N504" t="n">
+      <c r="N504" s="0" t="n">
         <v>5.4</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="1" t="n">
         <v>46264</v>
+      </c>
+      <c r="B505" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="C505" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="D505" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F505" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="G505" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H505" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I505" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J505" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K505" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L505" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M505" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="N505" t="n">
+        <v>6.1</v>
       </c>
     </row>
     <row r="506">
@@ -47628,51 +47669,92 @@
       <c r="A504" s="1" t="n">
         <v>46263</v>
       </c>
-      <c r="B504" t="n">
+      <c r="B504" s="0" t="n">
         <v>26.4</v>
       </c>
-      <c r="C504" t="n">
+      <c r="C504" s="0" t="n">
         <v>26.1</v>
       </c>
-      <c r="D504" t="n">
+      <c r="D504" s="0" t="n">
         <v>24.3</v>
       </c>
-      <c r="E504" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F504" t="n">
+      <c r="E504" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F504" s="0" t="n">
         <v>20.5</v>
       </c>
-      <c r="G504" t="n">
+      <c r="G504" s="0" t="n">
         <v>16.2</v>
       </c>
-      <c r="H504" t="n">
+      <c r="H504" s="0" t="n">
         <v>22.3</v>
       </c>
-      <c r="I504" t="n">
+      <c r="I504" s="0" t="n">
         <v>24.5</v>
       </c>
-      <c r="J504" t="n">
+      <c r="J504" s="0" t="n">
         <v>22.8</v>
       </c>
-      <c r="K504" t="n">
+      <c r="K504" s="0" t="n">
         <v>19.3</v>
       </c>
-      <c r="L504" t="n">
+      <c r="L504" s="0" t="n">
         <v>19.1</v>
       </c>
-      <c r="M504" t="n">
+      <c r="M504" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="N504" t="n">
+      <c r="N504" s="0" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="1" t="n">
         <v>46264</v>
+      </c>
+      <c r="B505" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="C505" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D505" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F505" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G505" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H505" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I505" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J505" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K505" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L505" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="M505" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N505" t="n">
+        <v>21.6</v>
       </c>
     </row>
     <row r="506">
@@ -62661,57 +62743,104 @@
       <c r="A262" s="1" t="n">
         <v>46263</v>
       </c>
-      <c r="B262" t="n">
+      <c r="B262" s="0" t="n">
         <v>16.69</v>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F262" t="n">
+      <c r="C262" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D262" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E262" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F262" s="0" t="n">
         <v>9.24</v>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H262" t="n">
+      <c r="G262" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H262" s="0" t="n">
         <v>13.61</v>
       </c>
-      <c r="I262" t="n">
+      <c r="I262" s="0" t="n">
         <v>16.16</v>
       </c>
-      <c r="J262" t="n">
+      <c r="J262" s="0" t="n">
         <v>12.32</v>
       </c>
-      <c r="K262" t="n">
+      <c r="K262" s="0" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="L262" t="n">
+      <c r="L262" s="0" t="n">
         <v>10.4</v>
       </c>
-      <c r="M262" t="n">
+      <c r="M262" s="0" t="n">
         <v>8.84</v>
       </c>
-      <c r="N262" t="n">
+      <c r="N262" s="0" t="n">
         <v>12.28</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
         <v>46264</v>
+      </c>
+      <c r="B263" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="I263" t="n">
+        <v>17.44</v>
+      </c>
+      <c r="J263" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K263" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="L263" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="M263" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="N263" t="n">
+        <v>13.56</v>
       </c>
     </row>
     <row r="264">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -23543,45 +23543,45 @@
       <c r="A505" s="1" t="n">
         <v>46264</v>
       </c>
-      <c r="B505" t="n">
+      <c r="B505" s="0" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="C505" t="n">
+      <c r="C505" s="0" t="n">
         <v>10.5</v>
       </c>
-      <c r="D505" t="n">
+      <c r="D505" s="0" t="n">
         <v>5.5</v>
       </c>
-      <c r="E505" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F505" t="n">
+      <c r="E505" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F505" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G505" t="n">
+      <c r="G505" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="H505" t="n">
+      <c r="H505" s="0" t="n">
         <v>4.7</v>
       </c>
-      <c r="I505" t="n">
+      <c r="I505" s="0" t="n">
         <v>9.6</v>
       </c>
-      <c r="J505" t="n">
+      <c r="J505" s="0" t="n">
         <v>2.2</v>
       </c>
-      <c r="K505" t="n">
+      <c r="K505" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="L505" t="n">
+      <c r="L505" s="0" t="n">
         <v>2.1</v>
       </c>
-      <c r="M505" t="n">
+      <c r="M505" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="N505" t="n">
+      <c r="N505" s="0" t="n">
         <v>6.1</v>
       </c>
     </row>
@@ -23589,10 +23589,94 @@
       <c r="A506" s="1" t="n">
         <v>46265</v>
       </c>
+      <c r="B506" s="0" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="C506" s="0" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="D506" s="0" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E506" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F506" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G506" s="0" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H506" s="0" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I506" s="0" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J506" s="0" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K506" s="0" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L506" s="0" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M506" s="0" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N506" s="0" t="n">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="1" t="n">
         <v>46266</v>
+      </c>
+      <c r="B507" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="C507" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D507" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F507" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H507" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I507" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="J507" t="n">
+        <v>12</v>
+      </c>
+      <c r="K507" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L507" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M507" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N507" t="n">
+        <v>14.7</v>
       </c>
     </row>
     <row r="508">
@@ -47715,45 +47799,45 @@
       <c r="A505" s="1" t="n">
         <v>46264</v>
       </c>
-      <c r="B505" t="n">
+      <c r="B505" s="0" t="n">
         <v>27.7</v>
       </c>
-      <c r="C505" t="n">
+      <c r="C505" s="0" t="n">
         <v>28.2</v>
       </c>
-      <c r="D505" t="n">
+      <c r="D505" s="0" t="n">
         <v>27.8</v>
       </c>
-      <c r="E505" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F505" t="n">
+      <c r="E505" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F505" s="0" t="n">
         <v>22.9</v>
       </c>
-      <c r="G505" t="n">
+      <c r="G505" s="0" t="n">
         <v>21.8</v>
       </c>
-      <c r="H505" t="n">
+      <c r="H505" s="0" t="n">
         <v>23.3</v>
       </c>
-      <c r="I505" t="n">
+      <c r="I505" s="0" t="n">
         <v>26.3</v>
       </c>
-      <c r="J505" t="n">
+      <c r="J505" s="0" t="n">
         <v>26.5</v>
       </c>
-      <c r="K505" t="n">
+      <c r="K505" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="L505" t="n">
+      <c r="L505" s="0" t="n">
         <v>24.9</v>
       </c>
-      <c r="M505" t="n">
+      <c r="M505" s="0" t="n">
         <v>22.3</v>
       </c>
-      <c r="N505" t="n">
+      <c r="N505" s="0" t="n">
         <v>21.6</v>
       </c>
     </row>
@@ -47761,10 +47845,94 @@
       <c r="A506" s="1" t="n">
         <v>46265</v>
       </c>
+      <c r="B506" s="0" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="C506" s="0" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="D506" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="E506" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F506" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="G506" s="0" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="H506" s="0" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I506" s="0" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J506" s="0" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="K506" s="0" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L506" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="M506" s="0" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="N506" s="0" t="n">
+        <v>26.5</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="1" t="n">
         <v>46266</v>
+      </c>
+      <c r="B507" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="C507" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D507" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F507" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H507" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I507" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="J507" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="K507" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="L507" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="M507" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="N507" t="n">
+        <v>30.1</v>
       </c>
     </row>
     <row r="508">
@@ -62795,51 +62963,51 @@
       <c r="A263" s="1" t="n">
         <v>46264</v>
       </c>
-      <c r="B263" t="n">
+      <c r="B263" s="0" t="n">
         <v>17.35</v>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F263" t="n">
+      <c r="C263" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D263" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E263" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F263" s="0" t="n">
         <v>11.2</v>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H263" t="n">
+      <c r="G263" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H263" s="0" t="n">
         <v>13.81</v>
       </c>
-      <c r="I263" t="n">
+      <c r="I263" s="0" t="n">
         <v>17.44</v>
       </c>
-      <c r="J263" t="n">
+      <c r="J263" s="0" t="n">
         <v>14.9</v>
       </c>
-      <c r="K263" t="n">
+      <c r="K263" s="0" t="n">
         <v>12.16</v>
       </c>
-      <c r="L263" t="n">
+      <c r="L263" s="0" t="n">
         <v>12.07</v>
       </c>
-      <c r="M263" t="n">
+      <c r="M263" s="0" t="n">
         <v>10.45</v>
       </c>
-      <c r="N263" t="n">
+      <c r="N263" s="0" t="n">
         <v>13.56</v>
       </c>
     </row>
@@ -62847,10 +63015,104 @@
       <c r="A264" s="1" t="n">
         <v>46265</v>
       </c>
+      <c r="B264" s="0" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="C264" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D264" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E264" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F264" s="0" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="G264" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H264" s="0" t="n">
+        <v>16.24</v>
+      </c>
+      <c r="I264" s="0" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="J264" s="0" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="K264" s="0" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="L264" s="0" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="M264" s="0" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="N264" s="0" t="n">
+        <v>17.2</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
         <v>46266</v>
+      </c>
+      <c r="B265" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="I265" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="J265" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="K265" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="L265" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="M265" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N265" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="266">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -23635,47 +23635,47 @@
       <c r="A507" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B507" t="n">
+      <c r="B507" s="0" t="n">
         <v>13.3</v>
       </c>
-      <c r="C507" t="n">
+      <c r="C507" s="0" t="n">
         <v>15.2</v>
       </c>
-      <c r="D507" t="n">
+      <c r="D507" s="0" t="n">
         <v>13.5</v>
       </c>
-      <c r="E507" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F507" t="n">
+      <c r="E507" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F507" s="0" t="n">
         <v>2.6</v>
       </c>
-      <c r="G507" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H507" t="n">
+      <c r="G507" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H507" s="0" t="n">
         <v>7.9</v>
       </c>
-      <c r="I507" t="n">
+      <c r="I507" s="0" t="n">
         <v>13.4</v>
       </c>
-      <c r="J507" t="n">
+      <c r="J507" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="K507" t="n">
+      <c r="K507" s="0" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="L507" t="n">
+      <c r="L507" s="0" t="n">
         <v>6.2</v>
       </c>
-      <c r="M507" t="n">
+      <c r="M507" s="0" t="n">
         <v>4.6</v>
       </c>
-      <c r="N507" t="n">
+      <c r="N507" s="0" t="n">
         <v>14.7</v>
       </c>
     </row>
@@ -23683,10 +23683,96 @@
       <c r="A508" s="1" t="n">
         <v>46267</v>
       </c>
+      <c r="B508" s="0" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C508" s="0" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D508" s="0" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E508" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F508" s="0" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G508" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H508" s="0" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="I508" s="0" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J508" s="0" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K508" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L508" s="0" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M508" s="0" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N508" s="0" t="n">
+        <v>18.9</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="1" t="n">
         <v>46268</v>
+      </c>
+      <c r="B509" t="n">
+        <v>6</v>
+      </c>
+      <c r="C509" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D509" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>9</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H509" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I509" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J509" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K509" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L509" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="M509" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N509" t="n">
+        <v>14.2</v>
       </c>
     </row>
     <row r="510">
@@ -47891,47 +47977,47 @@
       <c r="A507" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B507" t="n">
+      <c r="B507" s="0" t="n">
         <v>24.5</v>
       </c>
-      <c r="C507" t="n">
+      <c r="C507" s="0" t="n">
         <v>25.7</v>
       </c>
-      <c r="D507" t="n">
+      <c r="D507" s="0" t="n">
         <v>26.1</v>
       </c>
-      <c r="E507" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F507" t="n">
+      <c r="E507" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F507" s="0" t="n">
         <v>26.7</v>
       </c>
-      <c r="G507" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H507" t="n">
+      <c r="G507" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H507" s="0" t="n">
         <v>31.4</v>
       </c>
-      <c r="I507" t="n">
+      <c r="I507" s="0" t="n">
         <v>24.3</v>
       </c>
-      <c r="J507" t="n">
+      <c r="J507" s="0" t="n">
         <v>26.8</v>
       </c>
-      <c r="K507" t="n">
+      <c r="K507" s="0" t="n">
         <v>24.1</v>
       </c>
-      <c r="L507" t="n">
+      <c r="L507" s="0" t="n">
         <v>29.4</v>
       </c>
-      <c r="M507" t="n">
+      <c r="M507" s="0" t="n">
         <v>27.9</v>
       </c>
-      <c r="N507" t="n">
+      <c r="N507" s="0" t="n">
         <v>30.1</v>
       </c>
     </row>
@@ -47939,10 +48025,96 @@
       <c r="A508" s="1" t="n">
         <v>46267</v>
       </c>
+      <c r="B508" s="0" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="C508" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="D508" s="0" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E508" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F508" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G508" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H508" s="0" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I508" s="0" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J508" s="0" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="K508" s="0" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L508" s="0" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M508" s="0" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="N508" s="0" t="n">
+        <v>30.9</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="1" t="n">
         <v>46268</v>
+      </c>
+      <c r="B509" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="C509" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="D509" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H509" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="I509" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="J509" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="K509" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="L509" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="M509" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N509" t="n">
+        <v>30.4</v>
       </c>
     </row>
     <row r="510">
@@ -63067,51 +63239,51 @@
       <c r="A265" s="1" t="n">
         <v>46266</v>
       </c>
-      <c r="B265" t="n">
+      <c r="B265" s="0" t="n">
         <v>17.88</v>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F265" t="n">
+      <c r="C265" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D265" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E265" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F265" s="0" t="n">
         <v>14.1</v>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H265" t="n">
+      <c r="G265" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H265" s="0" t="n">
         <v>18.91</v>
       </c>
-      <c r="I265" t="n">
+      <c r="I265" s="0" t="n">
         <v>18.06</v>
       </c>
-      <c r="J265" t="n">
+      <c r="J265" s="0" t="n">
         <v>17.72</v>
       </c>
-      <c r="K265" t="n">
+      <c r="K265" s="0" t="n">
         <v>16.82</v>
       </c>
-      <c r="L265" t="n">
+      <c r="L265" s="0" t="n">
         <v>16.07</v>
       </c>
-      <c r="M265" t="n">
+      <c r="M265" s="0" t="n">
         <v>15.8</v>
       </c>
-      <c r="N265" t="n">
+      <c r="N265" s="0" t="n">
         <v>22</v>
       </c>
     </row>
@@ -63119,10 +63291,104 @@
       <c r="A266" s="1" t="n">
         <v>46267</v>
       </c>
+      <c r="B266" s="0" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="C266" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D266" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E266" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F266" s="0" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="G266" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H266" s="0" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="I266" s="0" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="J266" s="0" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="K266" s="0" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="L266" s="0" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="M266" s="0" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N266" s="0" t="n">
+        <v>23.56</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
         <v>46268</v>
+      </c>
+      <c r="B267" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="I267" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="J267" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="K267" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="L267" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="M267" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="N267" t="n">
+        <v>22.59</v>
       </c>
     </row>
     <row r="268">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -23731,53 +23731,98 @@
       <c r="A509" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B509" t="n">
+      <c r="B509" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="C509" t="n">
+      <c r="C509" s="0" t="n">
         <v>7.2</v>
       </c>
-      <c r="D509" t="n">
+      <c r="D509" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="E509" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F509" t="n">
+      <c r="E509" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F509" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="G509" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H509" t="n">
+      <c r="G509" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H509" s="0" t="n">
         <v>10.7</v>
       </c>
-      <c r="I509" t="n">
+      <c r="I509" s="0" t="n">
         <v>7.4</v>
       </c>
-      <c r="J509" t="n">
+      <c r="J509" s="0" t="n">
         <v>6.8</v>
       </c>
-      <c r="K509" t="n">
+      <c r="K509" s="0" t="n">
         <v>4.8</v>
       </c>
-      <c r="L509" t="n">
+      <c r="L509" s="0" t="n">
         <v>9.4</v>
       </c>
-      <c r="M509" t="n">
+      <c r="M509" s="0" t="n">
         <v>5.9</v>
       </c>
-      <c r="N509" t="n">
+      <c r="N509" s="0" t="n">
         <v>14.2</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="1" t="n">
         <v>46269</v>
+      </c>
+      <c r="B510" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C510" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F510" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H510" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I510" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J510" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="K510" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="L510" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="M510" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="N510" t="n">
+        <v>10.5</v>
       </c>
     </row>
     <row r="511">
@@ -48073,53 +48118,96 @@
       <c r="A509" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B509" t="n">
+      <c r="B509" s="0" t="n">
         <v>19.2</v>
       </c>
-      <c r="C509" t="n">
+      <c r="C509" s="0" t="n">
         <v>18.7</v>
       </c>
-      <c r="D509" t="n">
+      <c r="D509" s="0" t="n">
         <v>20.3</v>
       </c>
-      <c r="E509" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F509" t="n">
+      <c r="E509" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F509" s="0" t="n">
         <v>18.4</v>
       </c>
-      <c r="G509" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H509" t="n">
+      <c r="G509" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H509" s="0" t="n">
         <v>23.3</v>
       </c>
-      <c r="I509" t="n">
+      <c r="I509" s="0" t="n">
         <v>17.1</v>
       </c>
-      <c r="J509" t="n">
+      <c r="J509" s="0" t="n">
         <v>19.3</v>
       </c>
-      <c r="K509" t="n">
+      <c r="K509" s="0" t="n">
         <v>11.9</v>
       </c>
-      <c r="L509" t="n">
+      <c r="L509" s="0" t="n">
         <v>19.3</v>
       </c>
-      <c r="M509" t="n">
+      <c r="M509" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="N509" t="n">
+      <c r="N509" s="0" t="n">
         <v>30.4</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="1" t="n">
         <v>46269</v>
+      </c>
+      <c r="B510" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C510" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D510" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F510" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H510" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="I510" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="J510" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K510" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L510" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="M510" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="N510" t="n">
+        <v>26.7</v>
       </c>
     </row>
     <row r="511">
@@ -63343,57 +63431,104 @@
       <c r="A267" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B267" t="n">
+      <c r="B267" s="0" t="n">
         <v>11.99</v>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F267" t="n">
+      <c r="C267" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D267" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E267" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F267" s="0" t="n">
         <v>12.09</v>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H267" t="n">
+      <c r="G267" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H267" s="0" t="n">
         <v>16.54</v>
       </c>
-      <c r="I267" t="n">
+      <c r="I267" s="0" t="n">
         <v>11.78</v>
       </c>
-      <c r="J267" t="n">
+      <c r="J267" s="0" t="n">
         <v>10.31</v>
       </c>
-      <c r="K267" t="n">
+      <c r="K267" s="0" t="n">
         <v>8.85</v>
       </c>
-      <c r="L267" t="n">
+      <c r="L267" s="0" t="n">
         <v>11.38</v>
       </c>
-      <c r="M267" t="n">
+      <c r="M267" s="0" t="n">
         <v>10.58</v>
       </c>
-      <c r="N267" t="n">
+      <c r="N267" s="0" t="n">
         <v>22.59</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
         <v>46269</v>
+      </c>
+      <c r="B268" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="I268" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="J268" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="K268" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="L268" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="M268" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N268" t="n">
+        <v>13.17</v>
       </c>
     </row>
     <row r="269">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -23779,55 +23779,100 @@
       <c r="A510" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B510" t="n">
+      <c r="B510" s="0" t="n">
         <v>-0.2</v>
       </c>
-      <c r="C510" t="n">
+      <c r="C510" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E510" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F510" t="n">
+      <c r="D510" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E510" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F510" s="0" t="n">
         <v>-5</v>
       </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H510" t="n">
+      <c r="G510" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H510" s="0" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I510" t="n">
+      <c r="I510" s="0" t="n">
         <v>4.7</v>
       </c>
-      <c r="J510" t="n">
+      <c r="J510" s="0" t="n">
         <v>-5.2</v>
       </c>
-      <c r="K510" t="n">
+      <c r="K510" s="0" t="n">
         <v>-6.3</v>
       </c>
-      <c r="L510" t="n">
+      <c r="L510" s="0" t="n">
         <v>-2.8</v>
       </c>
-      <c r="M510" t="n">
+      <c r="M510" s="0" t="n">
         <v>-6.3</v>
       </c>
-      <c r="N510" t="n">
+      <c r="N510" s="0" t="n">
         <v>10.5</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="1" t="n">
         <v>46270</v>
+      </c>
+      <c r="B511" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C511" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F511" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H511" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I511" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J511" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="K511" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="L511" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M511" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="N511" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="512">
@@ -48166,53 +48211,96 @@
       <c r="A510" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B510" t="n">
+      <c r="B510" s="0" t="n">
         <v>19.8</v>
       </c>
-      <c r="C510" t="n">
+      <c r="C510" s="0" t="n">
         <v>18.2</v>
       </c>
-      <c r="D510" t="n">
+      <c r="D510" s="0" t="n">
         <v>17.6</v>
       </c>
-      <c r="E510" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F510" t="n">
+      <c r="E510" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F510" s="0" t="n">
         <v>17.3</v>
       </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H510" t="n">
+      <c r="G510" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H510" s="0" t="n">
         <v>16.4</v>
       </c>
-      <c r="I510" t="n">
+      <c r="I510" s="0" t="n">
         <v>17.2</v>
       </c>
-      <c r="J510" t="n">
+      <c r="J510" s="0" t="n">
         <v>16.8</v>
       </c>
-      <c r="K510" t="n">
+      <c r="K510" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="L510" t="n">
+      <c r="L510" s="0" t="n">
         <v>15.3</v>
       </c>
-      <c r="M510" t="n">
+      <c r="M510" s="0" t="n">
         <v>12.6</v>
       </c>
-      <c r="N510" t="n">
+      <c r="N510" s="0" t="n">
         <v>26.7</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="1" t="n">
         <v>46270</v>
+      </c>
+      <c r="B511" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="C511" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D511" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F511" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H511" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="I511" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="J511" t="n">
+        <v>17</v>
+      </c>
+      <c r="K511" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="L511" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="M511" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N511" t="n">
+        <v>17.2</v>
       </c>
     </row>
     <row r="512">
@@ -63483,57 +63571,104 @@
       <c r="A268" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B268" t="n">
+      <c r="B268" s="0" t="n">
         <v>9.68</v>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F268" t="n">
+      <c r="C268" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D268" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E268" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F268" s="0" t="n">
         <v>5.94</v>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H268" t="n">
+      <c r="G268" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H268" s="0" t="n">
         <v>11.76</v>
       </c>
-      <c r="I268" t="n">
+      <c r="I268" s="0" t="n">
         <v>10.42</v>
       </c>
-      <c r="J268" t="n">
+      <c r="J268" s="0" t="n">
         <v>6.39</v>
       </c>
-      <c r="K268" t="n">
+      <c r="K268" s="0" t="n">
         <v>4.76</v>
       </c>
-      <c r="L268" t="n">
+      <c r="L268" s="0" t="n">
         <v>6.09</v>
       </c>
-      <c r="M268" t="n">
+      <c r="M268" s="0" t="n">
         <v>3.41</v>
       </c>
-      <c r="N268" t="n">
+      <c r="N268" s="0" t="n">
         <v>13.17</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
         <v>46270</v>
+      </c>
+      <c r="B269" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="I269" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="J269" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K269" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="L269" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="M269" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="N269" t="n">
+        <v>10.64</v>
       </c>
     </row>
     <row r="270">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -23829,55 +23829,98 @@
       <c r="A511" s="1" t="n">
         <v>46270</v>
       </c>
-      <c r="B511" t="n">
+      <c r="B511" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="C511" t="n">
+      <c r="C511" s="0" t="n">
         <v>1.7</v>
       </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E511" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F511" t="n">
+      <c r="D511" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E511" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F511" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H511" t="n">
+      <c r="G511" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H511" s="0" t="n">
         <v>1.1</v>
       </c>
-      <c r="I511" t="n">
+      <c r="I511" s="0" t="n">
         <v>4.1</v>
       </c>
-      <c r="J511" t="n">
+      <c r="J511" s="0" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K511" t="n">
+      <c r="K511" s="0" t="n">
         <v>-3.2</v>
       </c>
-      <c r="L511" t="n">
+      <c r="L511" s="0" t="n">
         <v>1.2</v>
       </c>
-      <c r="M511" t="n">
+      <c r="M511" s="0" t="n">
         <v>-2.8</v>
       </c>
-      <c r="N511" t="n">
+      <c r="N511" s="0" t="n">
         <v>5.5</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="1" t="n">
         <v>46271</v>
+      </c>
+      <c r="B512" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C512" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D512" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F512" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H512" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I512" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J512" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="K512" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="L512" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="M512" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="N512" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="513">
@@ -48259,53 +48302,96 @@
       <c r="A511" s="1" t="n">
         <v>46270</v>
       </c>
-      <c r="B511" t="n">
+      <c r="B511" s="0" t="n">
         <v>20.7</v>
       </c>
-      <c r="C511" t="n">
+      <c r="C511" s="0" t="n">
         <v>19.6</v>
       </c>
-      <c r="D511" t="n">
+      <c r="D511" s="0" t="n">
         <v>17.6</v>
       </c>
-      <c r="E511" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F511" t="n">
+      <c r="E511" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F511" s="0" t="n">
         <v>15.7</v>
       </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H511" t="n">
+      <c r="G511" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H511" s="0" t="n">
         <v>14.7</v>
       </c>
-      <c r="I511" t="n">
+      <c r="I511" s="0" t="n">
         <v>19.8</v>
       </c>
-      <c r="J511" t="n">
+      <c r="J511" s="0" t="n">
         <v>17</v>
       </c>
-      <c r="K511" t="n">
+      <c r="K511" s="0" t="n">
         <v>13.6</v>
       </c>
-      <c r="L511" t="n">
+      <c r="L511" s="0" t="n">
         <v>16.9</v>
       </c>
-      <c r="M511" t="n">
+      <c r="M511" s="0" t="n">
         <v>13.5</v>
       </c>
-      <c r="N511" t="n">
+      <c r="N511" s="0" t="n">
         <v>17.2</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="1" t="n">
         <v>46271</v>
+      </c>
+      <c r="B512" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="C512" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D512" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F512" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H512" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I512" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J512" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="K512" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L512" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M512" t="n">
+        <v>14</v>
+      </c>
+      <c r="N512" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="513">
@@ -63623,57 +63709,104 @@
       <c r="A269" s="1" t="n">
         <v>46270</v>
       </c>
-      <c r="B269" t="n">
+      <c r="B269" s="0" t="n">
         <v>11.1</v>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F269" t="n">
+      <c r="C269" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D269" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E269" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F269" s="0" t="n">
         <v>6.71</v>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H269" t="n">
+      <c r="G269" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H269" s="0" t="n">
         <v>8.51</v>
       </c>
-      <c r="I269" t="n">
+      <c r="I269" s="0" t="n">
         <v>11.38</v>
       </c>
-      <c r="J269" t="n">
+      <c r="J269" s="0" t="n">
         <v>8.9</v>
       </c>
-      <c r="K269" t="n">
+      <c r="K269" s="0" t="n">
         <v>5.96</v>
       </c>
-      <c r="L269" t="n">
+      <c r="L269" s="0" t="n">
         <v>8.65</v>
       </c>
-      <c r="M269" t="n">
+      <c r="M269" s="0" t="n">
         <v>5.99</v>
       </c>
-      <c r="N269" t="n">
+      <c r="N269" s="0" t="n">
         <v>10.64</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
         <v>46271</v>
+      </c>
+      <c r="B270" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I270" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="J270" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="K270" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="L270" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="M270" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="N270" t="n">
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="271">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -23879,53 +23879,96 @@
       <c r="A512" s="1" t="n">
         <v>46271</v>
       </c>
-      <c r="B512" t="n">
+      <c r="B512" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="C512" t="n">
+      <c r="C512" s="0" t="n">
         <v>4.2</v>
       </c>
-      <c r="D512" t="n">
+      <c r="D512" s="0" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E512" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F512" t="n">
+      <c r="E512" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F512" s="0" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H512" t="n">
+      <c r="G512" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H512" s="0" t="n">
         <v>1.3</v>
       </c>
-      <c r="I512" t="n">
+      <c r="I512" s="0" t="n">
         <v>3.4</v>
       </c>
-      <c r="J512" t="n">
+      <c r="J512" s="0" t="n">
         <v>-3.9</v>
       </c>
-      <c r="K512" t="n">
+      <c r="K512" s="0" t="n">
         <v>-3.7</v>
       </c>
-      <c r="L512" t="n">
+      <c r="L512" s="0" t="n">
         <v>-2.1</v>
       </c>
-      <c r="M512" t="n">
+      <c r="M512" s="0" t="n">
         <v>-3.5</v>
       </c>
-      <c r="N512" t="n">
+      <c r="N512" s="0" t="n">
         <v>4.8</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="1" t="n">
         <v>46272</v>
+      </c>
+      <c r="B513" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C513" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D513" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F513" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H513" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I513" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J513" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="K513" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="L513" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="M513" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N513" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="514">
@@ -48350,53 +48393,96 @@
       <c r="A512" s="1" t="n">
         <v>46271</v>
       </c>
-      <c r="B512" t="n">
+      <c r="B512" s="0" t="n">
         <v>21.8</v>
       </c>
-      <c r="C512" t="n">
+      <c r="C512" s="0" t="n">
         <v>20.5</v>
       </c>
-      <c r="D512" t="n">
+      <c r="D512" s="0" t="n">
         <v>18.7</v>
       </c>
-      <c r="E512" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F512" t="n">
+      <c r="E512" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F512" s="0" t="n">
         <v>14.7</v>
       </c>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H512" t="n">
+      <c r="G512" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H512" s="0" t="n">
         <v>16.8</v>
       </c>
-      <c r="I512" t="n">
+      <c r="I512" s="0" t="n">
         <v>20.6</v>
       </c>
-      <c r="J512" t="n">
+      <c r="J512" s="0" t="n">
         <v>16.9</v>
       </c>
-      <c r="K512" t="n">
+      <c r="K512" s="0" t="n">
         <v>14.8</v>
       </c>
-      <c r="L512" t="n">
+      <c r="L512" s="0" t="n">
         <v>15.1</v>
       </c>
-      <c r="M512" t="n">
+      <c r="M512" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="N512" t="n">
+      <c r="N512" s="0" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="1" t="n">
         <v>46272</v>
+      </c>
+      <c r="B513" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C513" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D513" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F513" t="n">
+        <v>16</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H513" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I513" t="n">
+        <v>21</v>
+      </c>
+      <c r="J513" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="K513" t="n">
+        <v>17</v>
+      </c>
+      <c r="L513" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M513" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N513" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="514">
@@ -63761,57 +63847,104 @@
       <c r="A270" s="1" t="n">
         <v>46271</v>
       </c>
-      <c r="B270" t="n">
+      <c r="B270" s="0" t="n">
         <v>12.08</v>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F270" t="n">
+      <c r="C270" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D270" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E270" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F270" s="0" t="n">
         <v>7.2</v>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H270" t="n">
+      <c r="G270" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H270" s="0" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="I270" t="n">
+      <c r="I270" s="0" t="n">
         <v>11.76</v>
       </c>
-      <c r="J270" t="n">
+      <c r="J270" s="0" t="n">
         <v>8.380000000000001</v>
       </c>
-      <c r="K270" t="n">
+      <c r="K270" s="0" t="n">
         <v>6.42</v>
       </c>
-      <c r="L270" t="n">
+      <c r="L270" s="0" t="n">
         <v>7.09</v>
       </c>
-      <c r="M270" t="n">
+      <c r="M270" s="0" t="n">
         <v>5.86</v>
       </c>
-      <c r="N270" t="n">
+      <c r="N270" s="0" t="n">
         <v>9.630000000000001</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
         <v>46272</v>
+      </c>
+      <c r="B271" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="I271" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="J271" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="K271" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="L271" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="M271" t="n">
+        <v>7.24</v>
+      </c>
+      <c r="N271" t="n">
+        <v>8.85</v>
       </c>
     </row>
     <row r="272">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24023,53 +24023,96 @@
       <c r="A515" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="B515" t="n">
+      <c r="B515" s="0" t="n">
         <v>1.9</v>
       </c>
-      <c r="C515" t="n">
+      <c r="C515" s="0" t="n">
         <v>3.5</v>
       </c>
-      <c r="D515" t="n">
+      <c r="D515" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="E515" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F515" t="n">
+      <c r="E515" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F515" s="0" t="n">
         <v>-4.4</v>
       </c>
-      <c r="G515" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H515" t="n">
+      <c r="G515" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H515" s="0" t="n">
         <v>3.9</v>
       </c>
-      <c r="I515" t="n">
+      <c r="I515" s="0" t="n">
         <v>4.9</v>
       </c>
-      <c r="J515" t="n">
+      <c r="J515" s="0" t="n">
         <v>-0.7</v>
       </c>
-      <c r="K515" t="n">
+      <c r="K515" s="0" t="n">
         <v>-6.4</v>
       </c>
-      <c r="L515" t="n">
+      <c r="L515" s="0" t="n">
         <v>-1.6</v>
       </c>
-      <c r="M515" t="n">
+      <c r="M515" s="0" t="n">
         <v>-3.4</v>
       </c>
-      <c r="N515" t="n">
+      <c r="N515" s="0" t="n">
         <v>4.6</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="1" t="n">
         <v>46275</v>
+      </c>
+      <c r="B516" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C516" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D516" t="n">
+        <v>0</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F516" t="n">
+        <v>-4</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I516" t="n">
+        <v>3</v>
+      </c>
+      <c r="J516" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K516" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="L516" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="M516" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="N516" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="517">
@@ -48623,53 +48666,96 @@
       <c r="A515" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="B515" t="n">
+      <c r="B515" s="0" t="n">
         <v>25.1</v>
       </c>
-      <c r="C515" t="n">
+      <c r="C515" s="0" t="n">
         <v>24.3</v>
       </c>
-      <c r="D515" t="n">
+      <c r="D515" s="0" t="n">
         <v>23.3</v>
       </c>
-      <c r="E515" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F515" t="n">
+      <c r="E515" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F515" s="0" t="n">
         <v>18.1</v>
       </c>
-      <c r="G515" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H515" t="n">
+      <c r="G515" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H515" s="0" t="n">
         <v>20.5</v>
       </c>
-      <c r="I515" t="n">
+      <c r="I515" s="0" t="n">
         <v>23.8</v>
       </c>
-      <c r="J515" t="n">
+      <c r="J515" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="K515" t="n">
+      <c r="K515" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="L515" t="n">
+      <c r="L515" s="0" t="n">
         <v>22.2</v>
       </c>
-      <c r="M515" t="n">
+      <c r="M515" s="0" t="n">
         <v>19.8</v>
       </c>
-      <c r="N515" t="n">
+      <c r="N515" s="0" t="n">
         <v>16.5</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="1" t="n">
         <v>46275</v>
+      </c>
+      <c r="B516" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="C516" t="n">
+        <v>26</v>
+      </c>
+      <c r="D516" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F516" t="n">
+        <v>19</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I516" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="J516" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="K516" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="L516" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="M516" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N516" t="n">
+        <v>21.9</v>
       </c>
     </row>
     <row r="517">
@@ -64175,57 +64261,104 @@
       <c r="A273" s="1" t="n">
         <v>46274</v>
       </c>
-      <c r="B273" t="n">
+      <c r="B273" s="0" t="n">
         <v>14.04</v>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F273" t="n">
+      <c r="C273" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D273" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E273" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F273" s="0" t="n">
         <v>6.99</v>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H273" t="n">
+      <c r="G273" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H273" s="0" t="n">
         <v>12.65</v>
       </c>
-      <c r="I273" t="n">
+      <c r="I273" s="0" t="n">
         <v>13.86</v>
       </c>
-      <c r="J273" t="n">
+      <c r="J273" s="0" t="n">
         <v>13.86</v>
       </c>
-      <c r="K273" t="n">
+      <c r="K273" s="0" t="n">
         <v>13.86</v>
       </c>
-      <c r="L273" t="n">
+      <c r="L273" s="0" t="n">
         <v>13.86</v>
       </c>
-      <c r="M273" t="n">
+      <c r="M273" s="0" t="n">
         <v>7.87</v>
       </c>
-      <c r="N273" t="n">
+      <c r="N273" s="0" t="n">
         <v>10.75</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
         <v>46275</v>
+      </c>
+      <c r="B274" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>10.63</v>
+      </c>
+      <c r="I274" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="J274" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="K274" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="L274" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="M274" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="N274" t="n">
+        <v>12.21</v>
       </c>
     </row>
     <row r="275">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24071,53 +24071,96 @@
       <c r="A516" s="1" t="n">
         <v>46275</v>
       </c>
-      <c r="B516" t="n">
+      <c r="B516" s="0" t="n">
         <v>1.8</v>
       </c>
-      <c r="C516" t="n">
+      <c r="C516" s="0" t="n">
         <v>2.8</v>
       </c>
-      <c r="D516" t="n">
+      <c r="D516" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="E516" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F516" t="n">
+      <c r="E516" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F516" s="0" t="n">
         <v>-4</v>
       </c>
-      <c r="G516" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H516" t="n">
+      <c r="G516" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H516" s="0" t="n">
         <v>2.3</v>
       </c>
-      <c r="I516" t="n">
+      <c r="I516" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="J516" t="n">
+      <c r="J516" s="0" t="n">
         <v>-2</v>
       </c>
-      <c r="K516" t="n">
+      <c r="K516" s="0" t="n">
         <v>-5.1</v>
       </c>
-      <c r="L516" t="n">
+      <c r="L516" s="0" t="n">
         <v>-1.4</v>
       </c>
-      <c r="M516" t="n">
+      <c r="M516" s="0" t="n">
         <v>-2.1</v>
       </c>
-      <c r="N516" t="n">
+      <c r="N516" s="0" t="n">
         <v>3.9</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="1" t="n">
         <v>46276</v>
+      </c>
+      <c r="B517" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C517" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D517" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F517" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I517" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J517" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K517" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="L517" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="M517" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="N517" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="518">
@@ -48714,53 +48757,96 @@
       <c r="A516" s="1" t="n">
         <v>46275</v>
       </c>
-      <c r="B516" t="n">
+      <c r="B516" s="0" t="n">
         <v>25.5</v>
       </c>
-      <c r="C516" t="n">
+      <c r="C516" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="D516" t="n">
+      <c r="D516" s="0" t="n">
         <v>24.2</v>
       </c>
-      <c r="E516" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F516" t="n">
+      <c r="E516" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F516" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="G516" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H516" t="n">
+      <c r="G516" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H516" s="0" t="n">
         <v>22.6</v>
       </c>
-      <c r="I516" t="n">
+      <c r="I516" s="0" t="n">
         <v>24.9</v>
       </c>
-      <c r="J516" t="n">
+      <c r="J516" s="0" t="n">
         <v>23.1</v>
       </c>
-      <c r="K516" t="n">
+      <c r="K516" s="0" t="n">
         <v>19.1</v>
       </c>
-      <c r="L516" t="n">
+      <c r="L516" s="0" t="n">
         <v>22.5</v>
       </c>
-      <c r="M516" t="n">
+      <c r="M516" s="0" t="n">
         <v>21.4</v>
       </c>
-      <c r="N516" t="n">
+      <c r="N516" s="0" t="n">
         <v>21.9</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="1" t="n">
         <v>46276</v>
+      </c>
+      <c r="B517" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="C517" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="D517" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F517" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I517" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J517" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K517" t="n">
+        <v>19</v>
+      </c>
+      <c r="L517" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M517" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="N517" t="n">
+        <v>23.2</v>
       </c>
     </row>
     <row r="518">
@@ -64313,57 +64399,104 @@
       <c r="A274" s="1" t="n">
         <v>46275</v>
       </c>
-      <c r="B274" t="n">
+      <c r="B274" s="0" t="n">
         <v>13.93</v>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F274" t="n">
+      <c r="C274" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D274" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E274" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F274" s="0" t="n">
         <v>7.29</v>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H274" t="n">
+      <c r="G274" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H274" s="0" t="n">
         <v>10.63</v>
       </c>
-      <c r="I274" t="n">
+      <c r="I274" s="0" t="n">
         <v>11.13</v>
       </c>
-      <c r="J274" t="n">
+      <c r="J274" s="0" t="n">
         <v>11.53</v>
       </c>
-      <c r="K274" t="n">
+      <c r="K274" s="0" t="n">
         <v>8.35</v>
       </c>
-      <c r="L274" t="n">
+      <c r="L274" s="0" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="M274" t="n">
+      <c r="M274" s="0" t="n">
         <v>9.050000000000001</v>
       </c>
-      <c r="N274" t="n">
+      <c r="N274" s="0" t="n">
         <v>12.21</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
         <v>46276</v>
+      </c>
+      <c r="B275" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="I275" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="J275" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="K275" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="L275" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="M275" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="N275" t="n">
+        <v>14.75</v>
       </c>
     </row>
     <row r="276">

--- a/气象/蒙古存档.xlsx
+++ b/气象/蒙古存档.xlsx
@@ -24119,53 +24119,96 @@
       <c r="A517" s="1" t="n">
         <v>46276</v>
       </c>
-      <c r="B517" t="n">
+      <c r="B517" s="0" t="n">
         <v>3.2</v>
       </c>
-      <c r="C517" t="n">
+      <c r="C517" s="0" t="n">
         <v>4.2</v>
       </c>
-      <c r="D517" t="n">
+      <c r="D517" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F517" t="n">
+      <c r="E517" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F517" s="0" t="n">
         <v>-2.2</v>
       </c>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H517" t="n">
+      <c r="G517" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H517" s="0" t="n">
         <v>5.2</v>
       </c>
-      <c r="I517" t="n">
+      <c r="I517" s="0" t="n">
         <v>6.8</v>
       </c>
-      <c r="J517" t="n">
+      <c r="J517" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="K517" t="n">
+      <c r="K517" s="0" t="n">
         <v>-4.2</v>
       </c>
-      <c r="L517" t="n">
+      <c r="L517" s="0" t="n">
         <v>-0.6</v>
       </c>
-      <c r="M517" t="n">
+      <c r="M517" s="0" t="n">
         <v>-1.1</v>
       </c>
-      <c r="N517" t="n">
+      <c r="N517" s="0" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="1" t="n">
         <v>46277</v>
+      </c>
+      <c r="B518" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C518" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D518" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I518" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J518" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K518" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="L518" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M518" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="N518" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="519">
@@ -48805,53 +48848,96 @@
       <c r="A517" s="1" t="n">
         <v>46276</v>
       </c>
-      <c r="B517" t="n">
+      <c r="B517" s="0" t="n">
         <v>26.8</v>
       </c>
-      <c r="C517" t="n">
+      <c r="C517" s="0" t="n">
         <v>25.6</v>
       </c>
-      <c r="D517" t="n">
+      <c r="D517" s="0" t="n">
         <v>23.7</v>
       </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F517" t="n">
+      <c r="E517" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F517" s="0" t="n">
         <v>19.6</v>
       </c>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H517" t="n">
+      <c r="G517" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H517" s="0" t="n">
         <v>23.1</v>
       </c>
-      <c r="I517" t="n">
+      <c r="I517" s="0" t="n">
         <v>27.3</v>
       </c>
-      <c r="J517" t="n">
+      <c r="J517" s="0" t="n">
         <v>22.5</v>
       </c>
-      <c r="K517" t="n">
+      <c r="K517" s="0" t="n">
         <v>19</v>
       </c>
-      <c r="L517" t="n">
+      <c r="L517" s="0" t="n">
         <v>22.1</v>
       </c>
-      <c r="M517" t="n">
+      <c r="M517" s="0" t="n">
         <v>20.3</v>
       </c>
-      <c r="N517" t="n">
+      <c r="N517" s="0" t="n">
         <v>23.2</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="1" t="n">
         <v>46277</v>
+      </c>
+      <c r="B518" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="C518" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="D518" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F518" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I518" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J518" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="K518" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L518" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="M518" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N518" t="n">
+        <v>15.4</v>
       </c>
     </row>
     <row r="519">
@@ -64451,57 +64537,104 @@
       <c r="A275" s="1" t="n">
         <v>46276</v>
       </c>
-      <c r="B275" t="n">
+      <c r="B275" s="0" t="n">
         <v>14.51</v>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F275" t="n">
+      <c r="C275" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D275" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E275" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F275" s="0" t="n">
         <v>8.76</v>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="H275" t="n">
+      <c r="G275" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H275" s="0" t="n">
         <v>12.75</v>
       </c>
-      <c r="I275" t="n">
+      <c r="I275" s="0" t="n">
         <v>16.09</v>
       </c>
-      <c r="J275" t="n">
+      <c r="J275" s="0" t="n">
         <v>12.46</v>
       </c>
-      <c r="K275" t="n">
+      <c r="K275" s="0" t="n">
         <v>8.76</v>
       </c>
-      <c r="L275" t="n">
+      <c r="L275" s="0" t="n">
         <v>10.29</v>
       </c>
-      <c r="M275" t="n">
+      <c r="M275" s="0" t="n">
         <v>10.44</v>
       </c>
-      <c r="N275" t="n">
+      <c r="N275" s="0" t="n">
         <v>14.75</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
         <v>46277</v>
+      </c>
+      <c r="B276" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="I276" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="J276" t="n">
+        <v>12.39</v>
+      </c>
+      <c r="K276" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="L276" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="M276" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="N276" t="n">
+        <v>10.96</v>
       </c>
     </row>
     <row r="277">
